--- a/run/full data unflattened.xlsx
+++ b/run/full data unflattened.xlsx
@@ -716,7 +716,7 @@
         <v>[]</v>
       </c>
       <c r="AO2" t="str">
-        <v>[{"'Employee Competencies Rating'[Competancy Name]":"Facilitates Collaboration and Influence","'Employee Competencies Rating'[Employee Rating]":"5","'Employee Competencies Rating'[Supervisor Rating]":"5","'Employee Competencies Rating'[Employee Rating Description]":"Role Model","'Employee Competencies Rating'[Supervisor Rating Description]":"Role Model"},{"'Employee Competencies Rating'[Competancy Name]":"Public Service Excellence","'Employee Competencies Rating'[Employee Rating]":"5","'Employee Competencies Rating'[Supervisor Rating]":"5","'Employee Competencies Rating'[Employee Rating Description]":"Role Model","'Employee Competencies Rating'[Supervisor Rating Description]":"Role Model"},{"'Employee Competencies Rating'[Competancy Name]":"Learning Agility","'Employee Competencies Rating'[Employee Rating]":"5","'Employee Competencies Rating'[Supervisor Rating]":"5","'Employee Competencies Rating'[Employee Rating Description]":"Role Model","'Employee Competencies Rating'[Supervisor Rating Description]":"Role Model"},{"'Employee Competencies Rating'[Competancy Name]":"Digital Savviness","'Employee Competencies Rating'[Employee Rating]":"5","'Employee Competencies Rating'[Supervisor Rating]":"5","'Employee Competencies Rating'[Employee Rating Description]":"Role Model","'Employee Competencies Rating'[Supervisor Rating Description]":"Role Model"},{"'Employee Competencies Rating'[Competancy Name]":"Strategic and Visionary Foresight","'Employee Competencies Rating'[Employee Rating]":"4","'Employee Competencies Rating'[Supervisor Rating]":"5","'Employee Competencies Rating'[Employee Rating Description]":"Champion","'Employee Competencies Rating'[Supervisor Rating Description]":"Role Model"},{"'Employee Competencies Rating'[Competancy Name]":"Results-Driven Outcomes","'Employee Competencies Rating'[Employee Rating]":"5","'Employee Competencies Rating'[Supervisor Rating]":"5","'Employee Competencies Rating'[Employee Rating Description]":"Role Model","'Employee Competencies Rating'[Supervisor Rating Description]":"Role Model"},{"'Employee Competencies Rating'[Competancy Name]":"Critical Thinking and Data-Driven Decision Making","'Employee Competencies Rating'[Employee Rating]":"5","'Employee Competencies Rating'[Supervisor Rating]":"5","'Employee Competencies Rating'[Employee Rating Description]":"Role Model","'Employee Competencies Rating'[Supervisor Rating Description]":"Role Model"},{"'Employee Competencies Rating'[Competancy Name]":"Intrapreneurship","'Employee Competencies Rating'[Employee Rating]":"5","'Employee Competencies Rating'[Supervisor Rating]":"5","'Employee Competencies Rating'[Employee Rating Description]":"Role Model","'Employee Competencies Rating'[Supervisor Rating Description]":"Role Model"},{"'Employee Competencies Rating'[Competancy Name]":"Leading Change","'Employee Competencies Rating'[Employee Rating]":"4","'Employee Competencies Rating'[Supervisor Rating]":"5","'Employee Competencies Rating'[Employee Rating Description]":"Champion","'Employee Competencies Rating'[Supervisor Rating Description]":"Role Model"},{"'Employee Competencies Rating'[Competancy Name]":"Fostering Well-Being and Coaching","'Employee Competencies Rating'[Employee Rating]":"4","'Employee Competencies Rating'[Supervisor Rating]":"5","'Employee Competencies Rating'[Employee Rating Description]":"Champion","'Employee Competencies Rating'[Supervisor Rating Description]":"Role Model"}]</v>
+        <v>[{"Employee Competencies Rating[Competancy Name]":"Facilitates Collaboration and Influence","Employee Competencies Rating[Employee Rating]":"5","Employee Competencies Rating[Supervisor Rating]":"5","Employee Competencies Rating[Employee Rating Description]":"Role Model","Employee Competencies Rating[Supervisor Rating Description]":"Role Model"},{"Employee Competencies Rating[Competancy Name]":"Public Service Excellence","Employee Competencies Rating[Employee Rating]":"5","Employee Competencies Rating[Supervisor Rating]":"5","Employee Competencies Rating[Employee Rating Description]":"Role Model","Employee Competencies Rating[Supervisor Rating Description]":"Role Model"},{"Employee Competencies Rating[Competancy Name]":"Learning Agility","Employee Competencies Rating[Employee Rating]":"5","Employee Competencies Rating[Supervisor Rating]":"5","Employee Competencies Rating[Employee Rating Description]":"Role Model","Employee Competencies Rating[Supervisor Rating Description]":"Role Model"},{"Employee Competencies Rating[Competancy Name]":"Digital Savviness","Employee Competencies Rating[Employee Rating]":"5","Employee Competencies Rating[Supervisor Rating]":"5","Employee Competencies Rating[Employee Rating Description]":"Role Model","Employee Competencies Rating[Supervisor Rating Description]":"Role Model"},{"Employee Competencies Rating[Competancy Name]":"Strategic and Visionary Foresight","Employee Competencies Rating[Employee Rating]":"4","Employee Competencies Rating[Supervisor Rating]":"5","Employee Competencies Rating[Employee Rating Description]":"Champion","Employee Competencies Rating[Supervisor Rating Description]":"Role Model"},{"Employee Competencies Rating[Competancy Name]":"Results-Driven Outcomes","Employee Competencies Rating[Employee Rating]":"5","Employee Competencies Rating[Supervisor Rating]":"5","Employee Competencies Rating[Employee Rating Description]":"Role Model","Employee Competencies Rating[Supervisor Rating Description]":"Role Model"},{"Employee Competencies Rating[Competancy Name]":"Critical Thinking and Data-Driven Decision Making","Employee Competencies Rating[Employee Rating]":"5","Employee Competencies Rating[Supervisor Rating]":"5","Employee Competencies Rating[Employee Rating Description]":"Role Model","Employee Competencies Rating[Supervisor Rating Description]":"Role Model"},{"Employee Competencies Rating[Competancy Name]":"Intrapreneurship","Employee Competencies Rating[Employee Rating]":"5","Employee Competencies Rating[Supervisor Rating]":"5","Employee Competencies Rating[Employee Rating Description]":"Role Model","Employee Competencies Rating[Supervisor Rating Description]":"Role Model"},{"Employee Competencies Rating[Competancy Name]":"Leading Change","Employee Competencies Rating[Employee Rating]":"4","Employee Competencies Rating[Supervisor Rating]":"5","Employee Competencies Rating[Employee Rating Description]":"Champion","Employee Competencies Rating[Supervisor Rating Description]":"Role Model"},{"Employee Competencies Rating[Competancy Name]":"Fostering Well-Being and Coaching","Employee Competencies Rating[Employee Rating]":"4","Employee Competencies Rating[Supervisor Rating]":"5","Employee Competencies Rating[Employee Rating Description]":"Champion","Employee Competencies Rating[Supervisor Rating Description]":"Role Model"}]</v>
       </c>
       <c r="AP2" t="str">
         <v>[]</v>
@@ -728,13 +728,13 @@
         <v>[]</v>
       </c>
       <c r="AS2" t="str">
-        <v>[{"'Employee Performance'[Performance Review Period]":"2023 Review Period","'Employee Performance'[Calculated Rating]":"5","'Employee Performance'[Normalized Performance Rating]":"Consistently Exceeds Expectations"},{"'Employee Performance'[Performance Review Period]":"2024 Review Period","'Employee Performance'[Calculated Rating]":"5","'Employee Performance'[Normalized Performance Rating]":"Consistently Exceeds Expectations"}]</v>
+        <v>[{"Employee Performance[Performance Review Period]":"2023 Review Period","Employee Performance[Calculated Rating]":"5","Employee Performance[Normalized Performance Rating]":"Consistently Exceeds Expectations"},{"Employee Performance[Performance Review Period]":"2024 Review Period","Employee Performance[Calculated Rating]":"5","Employee Performance[Normalized Performance Rating]":"Consistently Exceeds Expectations"}]</v>
       </c>
       <c r="AT2" t="str">
-        <v>[{"'Employee Achievements'[Customary Name]":"2023 Annual Appraisal","'Employee Achievements'[Manager OA Comments]":"","'Employee Achievements'[Employee OA Comments]":""},{"'Employee Achievements'[Customary Name]":"2024 Annual Appraisal","'Employee Achievements'[Manager OA Comments]":".","'Employee Achievements'[Employee OA Comments]":"."}]</v>
+        <v>[{"Employee Achievements[Customary Name]":"2023 Annual Appraisal","Employee Achievements[Manager OA Comments]":"","Employee Achievements[Employee OA Comments]":""},{"Employee Achievements[Customary Name]":"2024 Annual Appraisal","Employee Achievements[Manager OA Comments]":".","Employee Achievements[Employee OA Comments]":"."}]</v>
       </c>
       <c r="AU2" t="str">
-        <v>[{"'Employee Objectives'[Objective Name]":"أرشيف البيانات و التقارير الخاصة بسموه","'Employee Objectives'[Goal Plan Name]":"2023 Performance Objectives","'Employee Objectives'[Objective Description]":"أرشيف البيانات و التقارير الخاصة بسموه","'Employee Objectives'[Goal Weighting]":"25","'Employee Objectives'[Goal Status]":"Approved","'Employee Objectives'[Objective Status]":"","'Employee Objectives'[Workflow State]":""},{"'Employee Objectives'[Objective Name]":"التعاون مع الشركاء لتوفير كافة المعلومات للدعوات الخاصة بسموه و المؤتمرات و الفعاليات الخارجية","'Employee Objectives'[Goal Plan Name]":"2023 Performance Objectives","'Employee Objectives'[Objective Description]":"التعاون مع الشركاء لتوفير كافة المعلومات للدعوات الخاصة بسموه و المؤتمرات و الفعاليات الخارجية","'Employee Objectives'[Goal Weighting]":"25","'Employee Objectives'[Goal Status]":"Approved","'Employee Objectives'[Objective Status]":"","'Employee Objectives'[Workflow State]":""},{"'Employee Objectives'[Objective Name]":"تجهيز التقارير / العروض التقديمية أو أية أمور أخرى يتم عرضها على سموه بشكل واضح و محتوى فعال","'Employee Objectives'[Goal Plan Name]":"2023 Performance Objectives","'Employee Objectives'[Objective Description]":"تجهيز التقارير / العروض التقديمية أو أية أمور أخرى يتم عرضها على سموه بشكل واضح و محتوى فعال","'Employee Objectives'[Goal Weighting]":"25","'Employee Objectives'[Goal Status]":"Approved","'Employee Objectives'[Objective Status]":"","'Employee Objectives'[Workflow State]":""},{"'Employee Objectives'[Objective Name]":"متابعة احتياجات المهام الخاصة و طاقم العمل الخاص بمكتب سموه من تأشيرات أو جوازات","'Employee Objectives'[Goal Plan Name]":"2023 Performance Objectives","'Employee Objectives'[Objective Description]":"متابعة احتياجات المهام الخاصة و طاقم العمل الخاص بمكتب سموه من تأشيرات أو جوازات","'Employee Objectives'[Goal Weighting]":"25","'Employee Objectives'[Goal Status]":"Approved","'Employee Objectives'[Objective Status]":"","'Employee Objectives'[Workflow State]":""}]</v>
+        <v>[{"Employee Objectives[Objective Name]":"أرشيف البيانات و التقارير الخاصة بسموه","Employee Objectives[Goal Plan Name]":"2023 Performance Objectives","Employee Objectives[Objective Description]":"أرشيف البيانات و التقارير الخاصة بسموه","Employee Objectives[Goal Weighting]":"25","Employee Objectives[Goal Status]":"Approved","Employee Objectives[Objective Status]":"","Employee Objectives[Workflow State]":""},{"Employee Objectives[Objective Name]":"التعاون مع الشركاء لتوفير كافة المعلومات للدعوات الخاصة بسموه و المؤتمرات و الفعاليات الخارجية","Employee Objectives[Goal Plan Name]":"2023 Performance Objectives","Employee Objectives[Objective Description]":"التعاون مع الشركاء لتوفير كافة المعلومات للدعوات الخاصة بسموه و المؤتمرات و الفعاليات الخارجية","Employee Objectives[Goal Weighting]":"25","Employee Objectives[Goal Status]":"Approved","Employee Objectives[Objective Status]":"","Employee Objectives[Workflow State]":""},{"Employee Objectives[Objective Name]":"تجهيز التقارير / العروض التقديمية أو أية أمور أخرى يتم عرضها على سموه بشكل واضح و محتوى فعال","Employee Objectives[Goal Plan Name]":"2023 Performance Objectives","Employee Objectives[Objective Description]":"تجهيز التقارير / العروض التقديمية أو أية أمور أخرى يتم عرضها على سموه بشكل واضح و محتوى فعال","Employee Objectives[Goal Weighting]":"25","Employee Objectives[Goal Status]":"Approved","Employee Objectives[Objective Status]":"","Employee Objectives[Workflow State]":""},{"Employee Objectives[Objective Name]":"متابعة احتياجات المهام الخاصة و طاقم العمل الخاص بمكتب سموه من تأشيرات أو جوازات","Employee Objectives[Goal Plan Name]":"2023 Performance Objectives","Employee Objectives[Objective Description]":"متابعة احتياجات المهام الخاصة و طاقم العمل الخاص بمكتب سموه من تأشيرات أو جوازات","Employee Objectives[Goal Weighting]":"25","Employee Objectives[Goal Status]":"Approved","Employee Objectives[Objective Status]":"","Employee Objectives[Workflow State]":""}]</v>
       </c>
       <c r="AV2" t="str">
         <v>2025-05-01T00:00:00</v>
@@ -746,16 +746,16 @@
         <v>Financial Increase</v>
       </c>
       <c r="AY2" t="str">
-        <v>[{"'Employee Qualification'[Qualification Title]":"Bachelor of Mass Communication and Media (Public Relations)","'Employee Qualification'[Educational Institute]":"Alain University","'Employee Qualification'[GPA (Grade Point Average)]":"3.38","'Employee Qualification'[Study Start Date]":"2017-09-01","'Employee Qualification'[Study End Date]":"2021-06-01"},{"'Employee Qualification'[Qualification Title]":"Master of Business Administration","'Employee Qualification'[Educational Institute]":"Abu Dhabi School of Management","'Employee Qualification'[GPA (Grade Point Average)]":"3.35","'Employee Qualification'[Study Start Date]":"2021-09-01","'Employee Qualification'[Study End Date]":"2023-03-15"}]</v>
+        <v>[{"Employee Qualification[Qualification Title]":"Bachelor of Mass Communication and Media (Public Relations)","Employee Qualification[Educational Institute]":"Alain University","Employee Qualification[GPA (Grade Point Average)]":"3.38","Employee Qualification[Study Start Date]":"2017-09-01","Employee Qualification[Study End Date]":"2021-06-01"},{"Employee Qualification[Qualification Title]":"Master of Business Administration","Employee Qualification[Educational Institute]":"Abu Dhabi School of Management","Employee Qualification[GPA (Grade Point Average)]":"3.35","Employee Qualification[Study Start Date]":"2021-09-01","Employee Qualification[Study End Date]":"2023-03-15"}]</v>
       </c>
       <c r="AZ2" t="str">
         <v>[]</v>
       </c>
       <c r="BA2" t="str">
-        <v>[{"'Employee Assignment History'[Assignment Name]":"Manager, Public Relations","'Employee Assignment History'[Position Title]":"Manager, Public Relations","'Employee Assignment History'[Employee Grade]":"2A","'Employee Assignment History'[Assignment Start Date]":"2023-05-09","'Employee Assignment History'[Assignment End Date]":"","'Employee Assignment History'[Assignment Experience (Years &amp; Months)]":""}]</v>
+        <v>[{"Employee Assignment History[Assignment Name]":"Manager, Public Relations","Employee Assignment History[Position Title]":"Manager, Public Relations","Employee Assignment History[Employee Grade]":"2A","Employee Assignment History[Assignment Start Date]":"2023-05-09","Employee Assignment History[Assignment End Date]":"","Employee Assignment History[Assignment Experience (Years &amp; Months)]":""}]</v>
       </c>
       <c r="BB2" t="str">
-        <v>[{"'Employee Previous Employer'[Previous Employer Name]":"Ministry of Interior","'Employee Previous Employer'[Previous Job Title]":"Officier","'Employee Previous Employer'[Start Date]":"2007-01-01","'Employee Previous Employer'[End Date]":"2012-01-01"},{"'Employee Previous Employer'[Previous Employer Name]":"Ministry of Interior","'Employee Previous Employer'[Previous Job Title]":"Correspondence Officer","'Employee Previous Employer'[Start Date]":"2012-01-01","'Employee Previous Employer'[End Date]":"2017-01-01"},{"'Employee Previous Employer'[Previous Employer Name]":"The Supreme Council for National Security","'Employee Previous Employer'[Previous Job Title]":"Officer - Office of the Deputy National Security Advisor","'Employee Previous Employer'[Start Date]":"2017-02-01","'Employee Previous Employer'[End Date]":"2018-02-01"},{"'Employee Previous Employer'[Previous Employer Name]":"The Supreme Council for National Security","'Employee Previous Employer'[Previous Job Title]":"Head of Export Unit - Office of the Deputy National Security Advisor","'Employee Previous Employer'[Start Date]":"2018-01-01","'Employee Previous Employer'[End Date]":"2020-01-01"}]</v>
+        <v>[{"Employee Previous Employer[Previous Employer Name]":"Ministry of Interior","Employee Previous Employer[Previous Job Title]":"Officier","Employee Previous Employer[Start Date]":"2007-01-01","Employee Previous Employer[End Date]":"2012-01-01"},{"Employee Previous Employer[Previous Employer Name]":"Ministry of Interior","Employee Previous Employer[Previous Job Title]":"Correspondence Officer","Employee Previous Employer[Start Date]":"2012-01-01","Employee Previous Employer[End Date]":"2017-01-01"},{"Employee Previous Employer[Previous Employer Name]":"The Supreme Council for National Security","Employee Previous Employer[Previous Job Title]":"Officer - Office of the Deputy National Security Advisor","Employee Previous Employer[Start Date]":"2017-02-01","Employee Previous Employer[End Date]":"2018-02-01"},{"Employee Previous Employer[Previous Employer Name]":"The Supreme Council for National Security","Employee Previous Employer[Previous Job Title]":"Head of Export Unit - Office of the Deputy National Security Advisor","Employee Previous Employer[Start Date]":"2018-01-01","Employee Previous Employer[End Date]":"2020-01-01"}]</v>
       </c>
       <c r="BC2" t="str">
         <v>[]</v>
@@ -880,7 +880,7 @@
         <v>0</v>
       </c>
       <c r="AN3" t="str">
-        <v>[{"'CV Employee Competencies'[Technical Competency Name]":"QGIS"},{"'CV Employee Competencies'[Technical Competency Name]":"R"},{"'CV Employee Competencies'[Technical Competency Name]":"Arabic"},{"'CV Employee Competencies'[Technical Competency Name]":"English"},{"'CV Employee Competencies'[Technical Competency Name]":"French"},{"'CV Employee Competencies'[Technical Competency Name]":"Economics"},{"'CV Employee Competencies'[Technical Competency Name]":"Social Research and Public Policy"},{"'CV Employee Competencies'[Technical Competency Name]":"Financial Planning"},{"'CV Employee Competencies'[Technical Competency Name]":"Bookkeeping"},{"'CV Employee Competencies'[Technical Competency Name]":"Policy Implementation"},{"'CV Employee Competencies'[Technical Competency Name]":"Diversity Research"},{"'CV Employee Competencies'[Technical Competency Name]":"Logistical Coordination"},{"'CV Employee Competencies'[Technical Competency Name]":"Archival Analysis"},{"'CV Employee Competencies'[Technical Competency Name]":"Demographic Research"},{"'CV Employee Competencies'[Technical Competency Name]":"Economic &amp; Financial Analysis"},{"'CV Employee Competencies'[Technical Competency Name]":"Analysis and Reporting"},{"'CV Employee Competencies'[Technical Competency Name]":"Bloomberg Market Concepts"},{"'CV Employee Competencies'[Technical Competency Name]":"Budget and Resource Management"},{"'CV Employee Competencies'[Technical Competency Name]":"Economic Forecasting and Trend Analysis"},{"'CV Employee Competencies'[Technical Competency Name]":"Data Analysis"},{"'CV Employee Competencies'[Technical Competency Name]":"Procurement"},{"'CV Employee Competencies'[Technical Competency Name]":"Resource Coordination"},{"'CV Employee Competencies'[Technical Competency Name]":"Sponsorship Development"}]</v>
+        <v>[{"CV Employee Competencies[Technical Competency Name]":"QGIS"},{"CV Employee Competencies[Technical Competency Name]":"R"},{"CV Employee Competencies[Technical Competency Name]":"Arabic"},{"CV Employee Competencies[Technical Competency Name]":"English"},{"CV Employee Competencies[Technical Competency Name]":"French"},{"CV Employee Competencies[Technical Competency Name]":"Economics"},{"CV Employee Competencies[Technical Competency Name]":"Social Research and Public Policy"},{"CV Employee Competencies[Technical Competency Name]":"Financial Planning"},{"CV Employee Competencies[Technical Competency Name]":"Bookkeeping"},{"CV Employee Competencies[Technical Competency Name]":"Policy Implementation"},{"CV Employee Competencies[Technical Competency Name]":"Diversity Research"},{"CV Employee Competencies[Technical Competency Name]":"Logistical Coordination"},{"CV Employee Competencies[Technical Competency Name]":"Archival Analysis"},{"CV Employee Competencies[Technical Competency Name]":"Demographic Research"},{"CV Employee Competencies[Technical Competency Name]":"Economic &amp; Financial Analysis"},{"CV Employee Competencies[Technical Competency Name]":"Analysis and Reporting"},{"CV Employee Competencies[Technical Competency Name]":"Bloomberg Market Concepts"},{"CV Employee Competencies[Technical Competency Name]":"Budget and Resource Management"},{"CV Employee Competencies[Technical Competency Name]":"Economic Forecasting and Trend Analysis"},{"CV Employee Competencies[Technical Competency Name]":"Data Analysis"},{"CV Employee Competencies[Technical Competency Name]":"Procurement"},{"CV Employee Competencies[Technical Competency Name]":"Resource Coordination"},{"CV Employee Competencies[Technical Competency Name]":"Sponsorship Development"}]</v>
       </c>
       <c r="AO3" t="str">
         <v>[]</v>
@@ -889,7 +889,7 @@
         <v>[]</v>
       </c>
       <c r="AQ3" t="str">
-        <v>[{"'CV Employee Achievements and Awards'[CV Title]":"NYUAD Shukran Cultural Appreciation Award","'CV Employee Achievements and Awards'[CV Achievement Description]":"","'CV Employee Achievements and Awards'[CV Issue Date]":"2022-01-01"},{"'CV Employee Achievements and Awards'[CV Title]":"Bloomberg Market Concepts Certificate","'CV Employee Achievements and Awards'[CV Achievement Description]":"","'CV Employee Achievements and Awards'[CV Issue Date]":"2021-01-01"},{"'CV Employee Achievements and Awards'[CV Title]":"IMFs MDXs: Macroeconomics Diagnostics Certificate","'CV Employee Achievements and Awards'[CV Achievement Description]":"","'CV Employee Achievements and Awards'[CV Issue Date]":"2021-01-01"}]</v>
+        <v>[{"CV Employee Achievements and Awards[CV Title]":"NYUAD Shukran Cultural Appreciation Award","CV Employee Achievements and Awards[CV Achievement Description]":"","CV Employee Achievements and Awards[CV Issue Date]":"2022-01-01"},{"CV Employee Achievements and Awards[CV Title]":"Bloomberg Market Concepts Certificate","CV Employee Achievements and Awards[CV Achievement Description]":"","CV Employee Achievements and Awards[CV Issue Date]":"2021-01-01"},{"CV Employee Achievements and Awards[CV Title]":"IMFs MDXs: Macroeconomics Diagnostics Certificate","CV Employee Achievements and Awards[CV Achievement Description]":"","CV Employee Achievements and Awards[CV Issue Date]":"2021-01-01"}]</v>
       </c>
       <c r="AR3" t="str">
         <v>[]</v>
@@ -907,19 +907,19 @@
         <v/>
       </c>
       <c r="AY3" t="str">
-        <v>[{"'Employee Qualification'[Qualification Title]":"Bachelor of Arts","'Employee Qualification'[Educational Institute]":"NYU Abu Dhabi","'Employee Qualification'[GPA (Grade Point Average)]":"3.44","'Employee Qualification'[Study Start Date]":"2019-09-01","'Employee Qualification'[Study End Date]":""}]</v>
+        <v>[{"Employee Qualification[Qualification Title]":"Bachelor of Arts","Employee Qualification[Educational Institute]":"NYU Abu Dhabi","Employee Qualification[GPA (Grade Point Average)]":"3.44","Employee Qualification[Study Start Date]":"2019-09-01","Employee Qualification[Study End Date]":""}]</v>
       </c>
       <c r="AZ3" t="str">
-        <v>[{"'CV Employee Education'[CV Institution Name]":"New York University Abu Dhabi","'CV Employee Education'[CV Degree Name]":"BA","'CV Employee Education'[CV Start Date]":"2019-09-01","'CV Employee Education'[CV End Date]":"2023-05-31"}]</v>
+        <v>[{"CV Employee Education[CV Institution Name]":"New York University Abu Dhabi","CV Employee Education[CV Degree Name]":"BA","CV Employee Education[CV Start Date]":"2019-09-01","CV Employee Education[CV End Date]":"2023-05-31"}]</v>
       </c>
       <c r="BA3" t="str">
-        <v>[{"'Employee Assignment History'[Assignment Name]":"Junior Specialist","'Employee Assignment History'[Position Title]":"Junior Specialist, Business Environment and Investment Affairs","'Employee Assignment History'[Employee Grade]":"4C","'Employee Assignment History'[Assignment Start Date]":"2024-10-01","'Employee Assignment History'[Assignment End Date]":"2025-09-21","'Employee Assignment History'[Assignment Experience (Years &amp; Months)]":"0 Years, 11 Months"},{"'Employee Assignment History'[Assignment Name]":"Junior Specialist, Business Environment and Investment Affairs","'Employee Assignment History'[Position Title]":"Junior Specialist, Business Environment and Investment Affairs","'Employee Assignment History'[Employee Grade]":"4C","'Employee Assignment History'[Assignment Start Date]":"2025-09-22","'Employee Assignment History'[Assignment End Date]":"","'Employee Assignment History'[Assignment Experience (Years &amp; Months)]":""}]</v>
+        <v>[{"Employee Assignment History[Assignment Name]":"Junior Specialist","Employee Assignment History[Position Title]":"Junior Specialist, Business Environment and Investment Affairs","Employee Assignment History[Employee Grade]":"4C","Employee Assignment History[Assignment Start Date]":"2024-10-01","Employee Assignment History[Assignment End Date]":"2025-09-21","Employee Assignment History[Assignment Experience (Years &amp; Months)]":"0 Years, 11 Months"},{"Employee Assignment History[Assignment Name]":"Junior Specialist, Business Environment and Investment Affairs","Employee Assignment History[Position Title]":"Junior Specialist, Business Environment and Investment Affairs","Employee Assignment History[Employee Grade]":"4C","Employee Assignment History[Assignment Start Date]":"2025-09-22","Employee Assignment History[Assignment End Date]":"","Employee Assignment History[Assignment Experience (Years &amp; Months)]":""}]</v>
       </c>
       <c r="BB3" t="str">
-        <v>[{"'Employee Previous Employer'[Previous Employer Name]":"Abu Dhabi Investment Council","'Employee Previous Employer'[Previous Job Title]":"Trainee","'Employee Previous Employer'[Start Date]":"2024-06-02","'Employee Previous Employer'[End Date]":"2024-09-01"}]</v>
+        <v>[{"Employee Previous Employer[Previous Employer Name]":"Abu Dhabi Investment Council","Employee Previous Employer[Previous Job Title]":"Trainee","Employee Previous Employer[Start Date]":"2024-06-02","Employee Previous Employer[End Date]":"2024-09-01"}]</v>
       </c>
       <c r="BC3" t="str">
-        <v>[{"'CV Employee Work Experience'[CV Company Name]":"Domestic Students Advisory Board, NYU Abu Dhabi","'CV Employee Work Experience'[CV Job Title]":"Co-Chair","'CV Employee Work Experience'[CV Responsibilities Summary]":"Implemented policy change concerning the domestic student community at NYUAD alongside the Senior Leadership Team. Researched and measured diversity satisfaction amongst the domestic student community through “The Pulse Initiative”.","'CV Employee Work Experience'[CV Start Date]":"2021-01-01","'CV Employee Work Experience'[CV End Date]":"2022-06-30"},{"'CV Employee Work Experience'[CV Company Name]":"The Family Business Histories Project NYUAD X Tharawat Business Forum","'CV Employee Work Experience'[CV Job Title]":"Research Assistant","'CV Employee Work Experience'[CV Responsibilities Summary]":"Analyzed acquired family business archival collections and primary resources for to-be-published case studies. Researched demographics and investment philosophies of MENA-based family businesses from the 20th century to launch the initiative's first digital database.","'CV Employee Work Experience'[CV Start Date]":"2021-02-01","'CV Employee Work Experience'[CV End Date]":"2021-05-31"},{"'CV Employee Work Experience'[CV Company Name]":"Society of International Affairs, NYU Abu Dhabi","'CV Employee Work Experience'[CV Job Title]":"Treasurer","'CV Employee Work Experience'[CV Responsibilities Summary]":"Administered financial planning, budgeting, and bookkeeping of the Society of International Affairs Student-Interest Group in coordination with the NYUAD Student Affairs Office.","'CV Employee Work Experience'[CV Start Date]":"2021-08-01","'CV Employee Work Experience'[CV End Date]":"2022-12-31"},{"'CV Employee Work Experience'[CV Company Name]":"Salama Bint Hamdan Al Nahyan Foundation","'CV Employee Work Experience'[CV Job Title]":"Consultancy Intern","'CV Employee Work Experience'[CV Responsibilities Summary]":"","'CV Employee Work Experience'[CV Start Date]":"2022-05-01","'CV Employee Work Experience'[CV End Date]":""},{"'CV Employee Work Experience'[CV Company Name]":"Community-Based Learning Office, NYU Abu Dhabi","'CV Employee Work Experience'[CV Job Title]":"Local Educational Officer","'CV Employee Work Experience'[CV Responsibilities Summary]":"Assisted Professor John DeFterios in the logistical coordination of the June term class, The Gulf: A 21st Century Hub for Trade, Finance, and Energy. Delivered weekly analysis reports of experiential learning class engagements with multiple UAE Ministers and Industry leaders for the Community-Based Learning Office.","'CV Employee Work Experience'[CV Start Date]":"2022-06-01","'CV Employee Work Experience'[CV End Date]":"2022-06-30"},{"'CV Employee Work Experience'[CV Company Name]":"Student Energy","'CV Employee Work Experience'[CV Job Title]":"Director of Finance for the 2023 Summit Organizing Team","'CV Employee Work Experience'[CV Responsibilities Summary]":"Oversee accounting operations, data analysis, procurement, and resource coordination for the largest youth-led Energy Summit in the MENA region with the Student Energy Global Chapter and NYUAD Finance. Expand prospective sponsor bases through engagement in local and international energy-related conferences like ADIPEC 2022, IEA Global Conference on Energy Efficiency 2023, etc.","'CV Employee Work Experience'[CV Start Date]":"2022-09-01","'CV Employee Work Experience'[CV End Date]":""}]</v>
+        <v>[{"CV Employee Work Experience[CV Company Name]":"Domestic Students Advisory Board, NYU Abu Dhabi","CV Employee Work Experience[CV Job Title]":"Co-Chair","CV Employee Work Experience[CV Responsibilities Summary]":"Implemented policy change concerning the domestic student community at NYUAD alongside the Senior Leadership Team. Researched and measured diversity satisfaction amongst the domestic student community through “The Pulse Initiative”.","CV Employee Work Experience[CV Start Date]":"2021-01-01","CV Employee Work Experience[CV End Date]":"2022-06-30"},{"CV Employee Work Experience[CV Company Name]":"The Family Business Histories Project NYUAD X Tharawat Business Forum","CV Employee Work Experience[CV Job Title]":"Research Assistant","CV Employee Work Experience[CV Responsibilities Summary]":"Analyzed acquired family business archival collections and primary resources for to-be-published case studies. Researched demographics and investment philosophies of MENA-based family businesses from the 20th century to launch the initiative's first digital database.","CV Employee Work Experience[CV Start Date]":"2021-02-01","CV Employee Work Experience[CV End Date]":"2021-05-31"},{"CV Employee Work Experience[CV Company Name]":"Society of International Affairs, NYU Abu Dhabi","CV Employee Work Experience[CV Job Title]":"Treasurer","CV Employee Work Experience[CV Responsibilities Summary]":"Administered financial planning, budgeting, and bookkeeping of the Society of International Affairs Student-Interest Group in coordination with the NYUAD Student Affairs Office.","CV Employee Work Experience[CV Start Date]":"2021-08-01","CV Employee Work Experience[CV End Date]":"2022-12-31"},{"CV Employee Work Experience[CV Company Name]":"Salama Bint Hamdan Al Nahyan Foundation","CV Employee Work Experience[CV Job Title]":"Consultancy Intern","CV Employee Work Experience[CV Responsibilities Summary]":"","CV Employee Work Experience[CV Start Date]":"2022-05-01","CV Employee Work Experience[CV End Date]":""},{"CV Employee Work Experience[CV Company Name]":"Community-Based Learning Office, NYU Abu Dhabi","CV Employee Work Experience[CV Job Title]":"Local Educational Officer","CV Employee Work Experience[CV Responsibilities Summary]":"Assisted Professor John DeFterios in the logistical coordination of the June term class, The Gulf: A 21st Century Hub for Trade, Finance, and Energy. Delivered weekly analysis reports of experiential learning class engagements with multiple UAE Ministers and Industry leaders for the Community-Based Learning Office.","CV Employee Work Experience[CV Start Date]":"2022-06-01","CV Employee Work Experience[CV End Date]":"2022-06-30"},{"CV Employee Work Experience[CV Company Name]":"Student Energy","CV Employee Work Experience[CV Job Title]":"Director of Finance for the 2023 Summit Organizing Team","CV Employee Work Experience[CV Responsibilities Summary]":"Oversee accounting operations, data analysis, procurement, and resource coordination for the largest youth-led Energy Summit in the MENA region with the Student Energy Global Chapter and NYUAD Finance. Expand prospective sponsor bases through engagement in local and international energy-related conferences like ADIPEC 2022, IEA Global Conference on Energy Efficiency 2023, etc.","CV Employee Work Experience[CV Start Date]":"2022-09-01","CV Employee Work Experience[CV End Date]":""}]</v>
       </c>
       <c r="BD3" t="str">
         <v>Shamma Al Dhaheri brings 5.1 years of progressive experience in financial management, resource coordination, and policy implementation across academic, nonprofit, and student leadership roles. She has demonstrated intermediate proficiency in budgeting, economic forecasting, and data analysis through positions such as Director of Finance for the 2023 Student Energy Summit and Research Assistant for the Family Business Histories Project. Her foundational expertise in economic and financial analysis is reinforced by certifications from Bloomberg and the IMF, alongside recognition with NYUAD’s Shukran Cultural Appreciation Award. She holds a BA in Economics with a minor in Social Research and Public Policy from New York University Abu Dhabi.</v>
@@ -1047,25 +1047,25 @@
         <v>0</v>
       </c>
       <c r="AN4" t="str">
-        <v>[{"'CV Employee Competencies'[Technical Competency Name]":"Arabic"},{"'CV Employee Competencies'[Technical Competency Name]":"English"},{"'CV Employee Competencies'[Technical Competency Name]":"German"},{"'CV Employee Competencies'[Technical Competency Name]":"Team Leadership"},{"'CV Employee Competencies'[Technical Competency Name]":"Delegation"},{"'CV Employee Competencies'[Technical Competency Name]":"Performance Evaluation"},{"'CV Employee Competencies'[Technical Competency Name]":"Health Insurance Regulations"},{"'CV Employee Competencies'[Technical Competency Name]":"Data Analysis and Reporting"},{"'CV Employee Competencies'[Technical Competency Name]":"Project Management"},{"'CV Employee Competencies'[Technical Competency Name]":"Healthcare Facility Design"},{"'CV Employee Competencies'[Technical Competency Name]":"Healthcare Facility Management"},{"'CV Employee Competencies'[Technical Competency Name]":"Strategic Planning"},{"'CV Employee Competencies'[Technical Competency Name]":"Policy analysis"},{"'CV Employee Competencies'[Technical Competency Name]":"Social Policy"},{"'CV Employee Competencies'[Technical Competency Name]":"Quality Assurance"},{"'CV Employee Competencies'[Technical Competency Name]":"Customer Service"},{"'CV Employee Competencies'[Technical Competency Name]":"Leadership"},{"'CV Employee Competencies'[Technical Competency Name]":"Communication"},{"'CV Employee Competencies'[Technical Competency Name]":"Problem-solving"},{"'CV Employee Competencies'[Technical Competency Name]":"Employee Development"},{"'CV Employee Competencies'[Technical Competency Name]":"Research"},{"'CV Employee Competencies'[Technical Competency Name]":"Health System Financing"},{"'CV Employee Competencies'[Technical Competency Name]":"JCIA Standards"},{"'CV Employee Competencies'[Technical Competency Name]":"Organizational Leadership"},{"'CV Employee Competencies'[Technical Competency Name]":"Change Management"}]</v>
+        <v>[{"CV Employee Competencies[Technical Competency Name]":"Arabic"},{"CV Employee Competencies[Technical Competency Name]":"English"},{"CV Employee Competencies[Technical Competency Name]":"German"},{"CV Employee Competencies[Technical Competency Name]":"Team Leadership"},{"CV Employee Competencies[Technical Competency Name]":"Delegation"},{"CV Employee Competencies[Technical Competency Name]":"Performance Evaluation"},{"CV Employee Competencies[Technical Competency Name]":"Health Insurance Regulations"},{"CV Employee Competencies[Technical Competency Name]":"Data Analysis and Reporting"},{"CV Employee Competencies[Technical Competency Name]":"Project Management"},{"CV Employee Competencies[Technical Competency Name]":"Healthcare Facility Design"},{"CV Employee Competencies[Technical Competency Name]":"Healthcare Facility Management"},{"CV Employee Competencies[Technical Competency Name]":"Strategic Planning"},{"CV Employee Competencies[Technical Competency Name]":"Policy analysis"},{"CV Employee Competencies[Technical Competency Name]":"Social Policy"},{"CV Employee Competencies[Technical Competency Name]":"Quality Assurance"},{"CV Employee Competencies[Technical Competency Name]":"Customer Service"},{"CV Employee Competencies[Technical Competency Name]":"Leadership"},{"CV Employee Competencies[Technical Competency Name]":"Communication"},{"CV Employee Competencies[Technical Competency Name]":"Problem-solving"},{"CV Employee Competencies[Technical Competency Name]":"Employee Development"},{"CV Employee Competencies[Technical Competency Name]":"Research"},{"CV Employee Competencies[Technical Competency Name]":"Health System Financing"},{"CV Employee Competencies[Technical Competency Name]":"JCIA Standards"},{"CV Employee Competencies[Technical Competency Name]":"Organizational Leadership"},{"CV Employee Competencies[Technical Competency Name]":"Change Management"}]</v>
       </c>
       <c r="AO4" t="str">
-        <v>[{"'Employee Competencies Rating'[Competancy Name]":"Facilitates Collaboration and Influence","'Employee Competencies Rating'[Employee Rating]":"5","'Employee Competencies Rating'[Supervisor Rating]":"4","'Employee Competencies Rating'[Employee Rating Description]":"Role Model","'Employee Competencies Rating'[Supervisor Rating Description]":"Champion"},{"'Employee Competencies Rating'[Competancy Name]":"Leading Change","'Employee Competencies Rating'[Employee Rating]":"5","'Employee Competencies Rating'[Supervisor Rating]":"3","'Employee Competencies Rating'[Employee Rating Description]":"Role Model","'Employee Competencies Rating'[Supervisor Rating Description]":"Solid Performer"},{"'Employee Competencies Rating'[Competancy Name]":"Learning Agility","'Employee Competencies Rating'[Employee Rating]":"5","'Employee Competencies Rating'[Supervisor Rating]":"4","'Employee Competencies Rating'[Employee Rating Description]":"Role Model","'Employee Competencies Rating'[Supervisor Rating Description]":"Champion"},{"'Employee Competencies Rating'[Competancy Name]":"Intrapreneurship","'Employee Competencies Rating'[Employee Rating]":"5","'Employee Competencies Rating'[Supervisor Rating]":"4","'Employee Competencies Rating'[Employee Rating Description]":"Role Model","'Employee Competencies Rating'[Supervisor Rating Description]":"Champion"},{"'Employee Competencies Rating'[Competancy Name]":"Strategic and Visionary Foresight","'Employee Competencies Rating'[Employee Rating]":"5","'Employee Competencies Rating'[Supervisor Rating]":"4","'Employee Competencies Rating'[Employee Rating Description]":"Role Model","'Employee Competencies Rating'[Supervisor Rating Description]":"Champion"},{"'Employee Competencies Rating'[Competancy Name]":"Results-Driven Outcomes","'Employee Competencies Rating'[Employee Rating]":"5","'Employee Competencies Rating'[Supervisor Rating]":"4","'Employee Competencies Rating'[Employee Rating Description]":"Role Model","'Employee Competencies Rating'[Supervisor Rating Description]":"Champion"},{"'Employee Competencies Rating'[Competancy Name]":"Critical Thinking and Data-Driven Decision Making","'Employee Competencies Rating'[Employee Rating]":"4","'Employee Competencies Rating'[Supervisor Rating]":"4","'Employee Competencies Rating'[Employee Rating Description]":"Champion","'Employee Competencies Rating'[Supervisor Rating Description]":"Champion"},{"'Employee Competencies Rating'[Competancy Name]":"Digital Savviness","'Employee Competencies Rating'[Employee Rating]":"5","'Employee Competencies Rating'[Supervisor Rating]":"4","'Employee Competencies Rating'[Employee Rating Description]":"Role Model","'Employee Competencies Rating'[Supervisor Rating Description]":"Champion"},{"'Employee Competencies Rating'[Competancy Name]":"Fostering Well-Being and Coaching","'Employee Competencies Rating'[Employee Rating]":"5","'Employee Competencies Rating'[Supervisor Rating]":"4","'Employee Competencies Rating'[Employee Rating Description]":"Role Model","'Employee Competencies Rating'[Supervisor Rating Description]":"Champion"},{"'Employee Competencies Rating'[Competancy Name]":"Public Service Excellence","'Employee Competencies Rating'[Employee Rating]":"5","'Employee Competencies Rating'[Supervisor Rating]":"3","'Employee Competencies Rating'[Employee Rating Description]":"Role Model","'Employee Competencies Rating'[Supervisor Rating Description]":"Solid Performer"}]</v>
+        <v>[{"Employee Competencies Rating[Competancy Name]":"Facilitates Collaboration and Influence","Employee Competencies Rating[Employee Rating]":"5","Employee Competencies Rating[Supervisor Rating]":"4","Employee Competencies Rating[Employee Rating Description]":"Role Model","Employee Competencies Rating[Supervisor Rating Description]":"Champion"},{"Employee Competencies Rating[Competancy Name]":"Leading Change","Employee Competencies Rating[Employee Rating]":"5","Employee Competencies Rating[Supervisor Rating]":"3","Employee Competencies Rating[Employee Rating Description]":"Role Model","Employee Competencies Rating[Supervisor Rating Description]":"Solid Performer"},{"Employee Competencies Rating[Competancy Name]":"Learning Agility","Employee Competencies Rating[Employee Rating]":"5","Employee Competencies Rating[Supervisor Rating]":"4","Employee Competencies Rating[Employee Rating Description]":"Role Model","Employee Competencies Rating[Supervisor Rating Description]":"Champion"},{"Employee Competencies Rating[Competancy Name]":"Intrapreneurship","Employee Competencies Rating[Employee Rating]":"5","Employee Competencies Rating[Supervisor Rating]":"4","Employee Competencies Rating[Employee Rating Description]":"Role Model","Employee Competencies Rating[Supervisor Rating Description]":"Champion"},{"Employee Competencies Rating[Competancy Name]":"Strategic and Visionary Foresight","Employee Competencies Rating[Employee Rating]":"5","Employee Competencies Rating[Supervisor Rating]":"4","Employee Competencies Rating[Employee Rating Description]":"Role Model","Employee Competencies Rating[Supervisor Rating Description]":"Champion"},{"Employee Competencies Rating[Competancy Name]":"Results-Driven Outcomes","Employee Competencies Rating[Employee Rating]":"5","Employee Competencies Rating[Supervisor Rating]":"4","Employee Competencies Rating[Employee Rating Description]":"Role Model","Employee Competencies Rating[Supervisor Rating Description]":"Champion"},{"Employee Competencies Rating[Competancy Name]":"Critical Thinking and Data-Driven Decision Making","Employee Competencies Rating[Employee Rating]":"4","Employee Competencies Rating[Supervisor Rating]":"4","Employee Competencies Rating[Employee Rating Description]":"Champion","Employee Competencies Rating[Supervisor Rating Description]":"Champion"},{"Employee Competencies Rating[Competancy Name]":"Digital Savviness","Employee Competencies Rating[Employee Rating]":"5","Employee Competencies Rating[Supervisor Rating]":"4","Employee Competencies Rating[Employee Rating Description]":"Role Model","Employee Competencies Rating[Supervisor Rating Description]":"Champion"},{"Employee Competencies Rating[Competancy Name]":"Fostering Well-Being and Coaching","Employee Competencies Rating[Employee Rating]":"5","Employee Competencies Rating[Supervisor Rating]":"4","Employee Competencies Rating[Employee Rating Description]":"Role Model","Employee Competencies Rating[Supervisor Rating Description]":"Champion"},{"Employee Competencies Rating[Competancy Name]":"Public Service Excellence","Employee Competencies Rating[Employee Rating]":"5","Employee Competencies Rating[Supervisor Rating]":"3","Employee Competencies Rating[Employee Rating Description]":"Role Model","Employee Competencies Rating[Supervisor Rating Description]":"Solid Performer"}]</v>
       </c>
       <c r="AP4" t="str">
         <v>[]</v>
       </c>
       <c r="AQ4" t="str">
-        <v>[{"'CV Employee Achievements and Awards'[CV Title]":"Oxford Diploma in Organizational Leadership","'CV Employee Achievements and Awards'[CV Achievement Description]":"","'CV Employee Achievements and Awards'[CV Issue Date]":"2014-02-01"}]</v>
+        <v>[{"CV Employee Achievements and Awards[CV Title]":"Oxford Diploma in Organizational Leadership","CV Employee Achievements and Awards[CV Achievement Description]":"","CV Employee Achievements and Awards[CV Issue Date]":"2014-02-01"}]</v>
       </c>
       <c r="AR4" t="str">
         <v>[]</v>
       </c>
       <c r="AS4" t="str">
-        <v>[{"'Employee Performance'[Performance Review Period]":"2024 Review Period","'Employee Performance'[Calculated Rating]":"3.53","'Employee Performance'[Normalized Performance Rating]":"Meets Expectations"}]</v>
+        <v>[{"Employee Performance[Performance Review Period]":"2024 Review Period","Employee Performance[Calculated Rating]":"3.53","Employee Performance[Normalized Performance Rating]":"Meets Expectations"}]</v>
       </c>
       <c r="AT4" t="str">
-        <v>[{"'Employee Achievements'[Customary Name]":"2024 Annual Appraisal","'Employee Achievements'[Manager OA Comments]":"Afra has demonstrated that she meets expectations in her performance management, effectively leading her team in case management and stakeholder engagement. While some challenges required executive intervention, the division successfully managed and maintained strong stakeholder relationships. Overall, Afra and the team demonstrated on-target effective cases management with some difficulties during the year that required the intervention of the ED and DG. During the year of 2024, the division managed 10 sizable entities request with sizable additional internal opinion requests, special requests, and directives.Health Division faced difficulties in meeting their KPIs the entity’s request timeliness is Strength Areas:Entity Requests:The team with the leadership of Afra managed to delivered most of the ADGE’s requests presented to the committee with the highest quality of presentation and analysis. Stakeholder Management &amp; CollaborationFostered positive relationships with internal and external stakeholders, enhancing collaboration and improving coordination across entities.Commitment to Leadership &amp; Committee SupportDemonstrated dedication to meeting committee expectations by adhering to processes, timelines, and delivering high-quality outcomes. &lt;span style=\"font-family:&amp;","'Employee Achievements'[Employee OA Comments]":"Despite the ups and downs we went through since I joined in February 2024, I'm so proud of myself and the team.What we went through together and what we learned in this journey impacted our strength and confidence positively and pushed our capabilities to a higher level. And we wouldn't be able to push through without the trust and the support we received from you all the way. We thank you for your trust and support and we look forward to your feedback to start our 2025 with great achievements inshallah."}]</v>
+        <v>[{"Employee Achievements[Customary Name]":"2024 Annual Appraisal","Employee Achievements[Manager OA Comments]":"Afra has demonstrated that she meets expectations in her performance management, effectively leading her team in case management and stakeholder engagement. While some challenges required executive intervention, the division successfully managed and maintained strong stakeholder relationships. Overall, Afra and the team demonstrated on-target effective cases management with some difficulties during the year that required the intervention of the ED and DG. During the year of 2024, the division managed 10 sizable entities request with sizable additional internal opinion requests, special requests, and directives.Health Division faced difficulties in meeting their KPIs the entity’s request timeliness is Strength Areas:Entity Requests:The team with the leadership of Afra managed to delivered most of the ADGE’s requests presented to the committee with the highest quality of presentation and analysis. Stakeholder Management &amp; CollaborationFostered positive relationships with internal and external stakeholders, enhancing collaboration and improving coordination across entities.Commitment to Leadership &amp; Committee SupportDemonstrated dedication to meeting committee expectations by adhering to processes, timelines, and delivering high-quality outcomes. &lt;span style=\"font-family:&amp;","Employee Achievements[Employee OA Comments]":"Despite the ups and downs we went through since I joined in February 2024, I'm so proud of myself and the team.What we went through together and what we learned in this journey impacted our strength and confidence positively and pushed our capabilities to a higher level. And we wouldn't be able to push through without the trust and the support we received from you all the way. We thank you for your trust and support and we look forward to your feedback to start our 2025 with great achievements inshallah."}]</v>
       </c>
       <c r="AU4" t="str">
         <v>[]</v>
@@ -1074,19 +1074,19 @@
         <v/>
       </c>
       <c r="AY4" t="str">
-        <v>[{"'Employee Qualification'[Qualification Title]":"Applied Sciences in Health Information Management","'Employee Qualification'[Educational Institute]":"Higher Colleges of Technology","'Employee Qualification'[GPA (Grade Point Average)]":"3.84","'Employee Qualification'[Study Start Date]":"","'Employee Qualification'[Study End Date]":"2006-02-14"},{"'Employee Qualification'[Qualification Title]":"Higher Diploma in Health Information Management","'Employee Qualification'[Educational Institute]":"Higher Colleges of Technology","'Employee Qualification'[GPA (Grade Point Average)]":"3.46","'Employee Qualification'[Study Start Date]":"","'Employee Qualification'[Study End Date]":"2004-08-08"},{"'Employee Qualification'[Qualification Title]":"MBA in International Hospital and Healthcare Management","'Employee Qualification'[Educational Institute]":"Frankfurt School of Finance &amp; Management","'Employee Qualification'[GPA (Grade Point Average)]":"","'Employee Qualification'[Study Start Date]":"2007-05-04","'Employee Qualification'[Study End Date]":"2008-10-30"}]</v>
+        <v>[{"Employee Qualification[Qualification Title]":"Applied Sciences in Health Information Management","Employee Qualification[Educational Institute]":"Higher Colleges of Technology","Employee Qualification[GPA (Grade Point Average)]":"3.84","Employee Qualification[Study Start Date]":"","Employee Qualification[Study End Date]":"2006-02-14"},{"Employee Qualification[Qualification Title]":"Higher Diploma in Health Information Management","Employee Qualification[Educational Institute]":"Higher Colleges of Technology","Employee Qualification[GPA (Grade Point Average)]":"3.46","Employee Qualification[Study Start Date]":"","Employee Qualification[Study End Date]":"2004-08-08"},{"Employee Qualification[Qualification Title]":"MBA in International Hospital and Healthcare Management","Employee Qualification[Educational Institute]":"Frankfurt School of Finance &amp; Management","Employee Qualification[GPA (Grade Point Average)]":"","Employee Qualification[Study Start Date]":"2007-05-04","Employee Qualification[Study End Date]":"2008-10-30"}]</v>
       </c>
       <c r="AZ4" t="str">
-        <v>[{"'CV Employee Education'[CV Institution Name]":"Higher Colleges of Technology","'CV Employee Education'[CV Degree Name]":"Bachelor’s Degree in health information management","'CV Employee Education'[CV Start Date]":"2002-01-01","'CV Employee Education'[CV End Date]":"2006-07-31"},{"'CV Employee Education'[CV Institution Name]":"Higher Colleges of Technology","'CV Employee Education'[CV Degree Name]":"Higher Diploma Degree in Health Information Management","'CV Employee Education'[CV Start Date]":"2002-01-01","'CV Employee Education'[CV End Date]":"2004-06-30"},{"'CV Employee Education'[CV Institution Name]":"Frankfurt School of Finance and Management","'CV Employee Education'[CV Degree Name]":"MBA - International Hospital &amp; Healthcare Management","'CV Employee Education'[CV Start Date]":"2010-10-01","'CV Employee Education'[CV End Date]":"2010-12-31"},{"'CV Employee Education'[CV Institution Name]":"Said Business School, Oxford","'CV Employee Education'[CV Degree Name]":"Oxford Diploma in Organizational Leadership","'CV Employee Education'[CV Start Date]":"2014-02-01","'CV Employee Education'[CV End Date]":"2014-02-28"}]</v>
+        <v>[{"CV Employee Education[CV Institution Name]":"Higher Colleges of Technology","CV Employee Education[CV Degree Name]":"Bachelor’s Degree in health information management","CV Employee Education[CV Start Date]":"2002-01-01","CV Employee Education[CV End Date]":"2006-07-31"},{"CV Employee Education[CV Institution Name]":"Higher Colleges of Technology","CV Employee Education[CV Degree Name]":"Higher Diploma Degree in Health Information Management","CV Employee Education[CV Start Date]":"2002-01-01","CV Employee Education[CV End Date]":"2004-06-30"},{"CV Employee Education[CV Institution Name]":"Frankfurt School of Finance and Management","CV Employee Education[CV Degree Name]":"MBA - International Hospital &amp; Healthcare Management","CV Employee Education[CV Start Date]":"2010-10-01","CV Employee Education[CV End Date]":"2010-12-31"},{"CV Employee Education[CV Institution Name]":"Said Business School, Oxford","CV Employee Education[CV Degree Name]":"Oxford Diploma in Organizational Leadership","CV Employee Education[CV Start Date]":"2014-02-01","CV Employee Education[CV End Date]":"2014-02-28"}]</v>
       </c>
       <c r="BA4" t="str">
-        <v>[{"'Employee Assignment History'[Assignment Name]":"Director","'Employee Assignment History'[Position Title]":"Director, Health Operations","'Employee Assignment History'[Employee Grade]":"1C","'Employee Assignment History'[Assignment Start Date]":"2024-02-06","'Employee Assignment History'[Assignment End Date]":"2024-03-06","'Employee Assignment History'[Assignment Experience (Years &amp; Months)]":"0 Years, 1 Months"},{"'Employee Assignment History'[Assignment Name]":"Director, Health Department","'Employee Assignment History'[Position Title]":"Director, Health Department","'Employee Assignment History'[Employee Grade]":"1C","'Employee Assignment History'[Assignment Start Date]":"2024-03-07","'Employee Assignment History'[Assignment End Date]":"","'Employee Assignment History'[Assignment Experience (Years &amp; Months)]":""}]</v>
+        <v>[{"Employee Assignment History[Assignment Name]":"Director","Employee Assignment History[Position Title]":"Director, Health Operations","Employee Assignment History[Employee Grade]":"1C","Employee Assignment History[Assignment Start Date]":"2024-02-06","Employee Assignment History[Assignment End Date]":"2024-03-06","Employee Assignment History[Assignment Experience (Years &amp; Months)]":"0 Years, 1 Months"},{"Employee Assignment History[Assignment Name]":"Director, Health Department","Employee Assignment History[Position Title]":"Director, Health Department","Employee Assignment History[Employee Grade]":"1C","Employee Assignment History[Assignment Start Date]":"2024-03-07","Employee Assignment History[Assignment End Date]":"","Employee Assignment History[Assignment Experience (Years &amp; Months)]":""}]</v>
       </c>
       <c r="BB4" t="str">
-        <v>[{"'Employee Previous Employer'[Previous Employer Name]":"HAAD","'Employee Previous Employer'[Previous Job Title]":"Section Head - Quality &amp; Excellence","'Employee Previous Employer'[Start Date]":"2005-04-23","'Employee Previous Employer'[End Date]":"2009-01-29"},{"'Employee Previous Employer'[Previous Employer Name]":"General Secretariat of Executive Council","'Employee Previous Employer'[Previous Job Title]":"Senior Project Manager","'Employee Previous Employer'[Start Date]":"2009-05-31","'Employee Previous Employer'[End Date]":"2016-06-30"},{"'Employee Previous Employer'[Previous Employer Name]":"Nickl &amp; Partner","'Employee Previous Employer'[Previous Job Title]":"CEO of Nickl","'Employee Previous Employer'[Start Date]":"2017-11-01","'Employee Previous Employer'[End Date]":"2021-12-01"},{"'Employee Previous Employer'[Previous Employer Name]":"National Health Insurance Daman","'Employee Previous Employer'[Previous Job Title]":"Vice President - Regulatory Affairs","'Employee Previous Employer'[Start Date]":"2023-05-01","'Employee Previous Employer'[End Date]":""}]</v>
+        <v>[{"Employee Previous Employer[Previous Employer Name]":"HAAD","Employee Previous Employer[Previous Job Title]":"Section Head - Quality &amp; Excellence","Employee Previous Employer[Start Date]":"2005-04-23","Employee Previous Employer[End Date]":"2009-01-29"},{"Employee Previous Employer[Previous Employer Name]":"General Secretariat of Executive Council","Employee Previous Employer[Previous Job Title]":"Senior Project Manager","Employee Previous Employer[Start Date]":"2009-05-31","Employee Previous Employer[End Date]":"2016-06-30"},{"Employee Previous Employer[Previous Employer Name]":"Nickl &amp; Partner","Employee Previous Employer[Previous Job Title]":"CEO of Nickl","Employee Previous Employer[Start Date]":"2017-11-01","Employee Previous Employer[End Date]":"2021-12-01"},{"Employee Previous Employer[Previous Employer Name]":"National Health Insurance Daman","Employee Previous Employer[Previous Job Title]":"Vice President - Regulatory Affairs","Employee Previous Employer[Start Date]":"2023-05-01","Employee Previous Employer[End Date]":""}]</v>
       </c>
       <c r="BC4" t="str">
-        <v>[{"'CV Employee Work Experience'[CV Company Name]":"The Health Authority - HAAD","'CV Employee Work Experience'[CV Job Title]":"Quality Officer","'CV Employee Work Experience'[CV Responsibilities Summary]":"Led evaluation study of Abu Dhabi’s public clinics, used in improving the services. Led clinical investigation committee into malpractice incidents. Supported implementation of patients’ clinical complaints system. Supported implementation of JCIA standards in 2 Abu Dhabi public hospitals. Compiled quarterly and annually statistics and completed general studies.","'CV Employee Work Experience'[CV Start Date]":"2005-01-01","'CV Employee Work Experience'[CV End Date]":"2007-12-31"},{"'CV Employee Work Experience'[CV Company Name]":"The Health Authority - HAAD","'CV Employee Work Experience'[CV Job Title]":"Coordinator &amp; Judicial Inspector","'CV Employee Work Experience'[CV Responsibilities Summary]":"Judicial Inspector authorized by both Health Authority and Judicial Department in Abu Dhabi. Supported implementation of Abu Dhabi’s health insurance laws and regulations. Chaired the committee standardized tri and bipartite contracts in Abu Dhabi’s Health Insurance Scheme. Supported establishment of HAAD’s Health System Financing Department.","'CV Employee Work Experience'[CV Start Date]":"2007-01-01","'CV Employee Work Experience'[CV End Date]":"2009-12-31"},{"'CV Employee Work Experience'[CV Company Name]":"The Health Authority - HAAD","'CV Employee Work Experience'[CV Job Title]":"Head of Quality &amp; Excellent and Acting Head of Customer Services Center","'CV Employee Work Experience'[CV Responsibilities Summary]":"Review, compile and submit quality reports on internal progress related to developing human resources, policies, strategies, partnerships and resources, and the consequent results for customers, partners, society, and key organizational outcomes. Collaborated with corporate and operational teams to improve HAAD’s internal processes, services and customer relations, and supported establishment of Abu Dhabi’s Communication Centre. Initiated, implemented, and led HAAD’s Customer Service Centre (including migration from manual drop-in boxes to automated system). Recruited and trained and supervised seven Customer Service Representatives.","'CV Employee Work Experience'[CV Start Date]":"2008-01-01","'CV Employee Work Experience'[CV End Date]":"2009-12-31"},{"'CV Employee Work Experience'[CV Company Name]":"General Secretariat of Abu Dhabi Executive Council","'CV Employee Work Experience'[CV Job Title]":"Senior Specialist at the Strategy &amp; Policy Division","'CV Employee Work Experience'[CV Responsibilities Summary]":"Senior researcher, analyst, and project member in the social policy project. Senior analyst in the first CAPEX review and evaluation cycle of 2010/2011. Team lead in operational requests for entities mapped under the social sector. Senior member in the project of restructuring social services sector [2011-2012].","'CV Employee Work Experience'[CV Start Date]":"2009-01-01","'CV Employee Work Experience'[CV End Date]":"2011-12-31"},{"'CV Employee Work Experience'[CV Company Name]":"General Secretariat of Abu Dhabi Executive Council","'CV Employee Work Experience'[CV Job Title]":"Head of Social Policy &amp; Research Section","'CV Employee Work Experience'[CV Responsibilities Summary]":"Member of the Abu Dhabi Advising Committee for Social Services. Member of Prisoners Care Working Group in Abu Dhabi. Leading major projects: e.g., poverty study, baseline of social assistance system, baseline of social development sector, prisoners care, inclusion policy, social policy, social service evaluation, child protection system. Team responsibilities: delegating, following up, reviewing, editing, finalizing, evaluating progress and performance, and executing employees’ development plans.","'CV Employee Work Experience'[CV Start Date]":"2011-01-01","'CV Employee Work Experience'[CV End Date]":"2013-12-31"},{"'CV Employee Work Experience'[CV Company Name]":"General Secretariat of Abu Dhabi Executive Council","'CV Employee Work Experience'[CV Job Title]":"Senior Projects Manager","'CV Employee Work Experience'[CV Responsibilities Summary]":"Leading a number of special projects: e.g. GSEC IT Strategy, OCSA Initiatives 2014, and Demography Development in Emirate of Abu Dhabi.","'CV Employee Work Experience'[CV Start Date]":"2013-06-01","'CV Employee Work Experience'[CV End Date]":"2016-12-31"},{"'CV Employee Work Experience'[CV Company Name]":"German Federal Ministry of Health – BMG","'CV Employee Work Experience'[CV Job Title]":"2-months work placement","'CV Employee Work Experience'[CV Responsibilities Summary]":"","'CV Employee Work Experience'[CV Start Date]":"2014-08-01","'CV Employee Work Experience'[CV End Date]":"2014-09-30"},{"'CV Employee Work Experience'[CV Company Name]":"General Secretariat of Abu Dhabi Executive Council","'CV Employee Work Experience'[CV Job Title]":"Acting Head of Health Systems Section","'CV Employee Work Experience'[CV Responsibilities Summary]":"Managing daily operations related to the executive committees’ tasks. Analysis of daily requests received from entities in the healthcare sector. Managing special projects related to healthcare sector.","'CV Employee Work Experience'[CV Start Date]":"2015-01-01","'CV Employee Work Experience'[CV End Date]":"2016-03-31"},{"'CV Employee Work Experience'[CV Company Name]":"Nickl Academy GmbH","'CV Employee Work Experience'[CV Job Title]":"CEO &amp; Founder","'CV Employee Work Experience'[CV Responsibilities Summary]":"Founded an Academy in Munich focusing on delivering training programs for young professionals directly involved in designing and managing healthcare facilities.","'CV Employee Work Experience'[CV Start Date]":"2017-01-01","'CV Employee Work Experience'[CV End Date]":"2021-12-31"},{"'CV Employee Work Experience'[CV Company Name]":"Charitable Foundation","'CV Employee Work Experience'[CV Job Title]":"CEO","'CV Employee Work Experience'[CV Responsibilities Summary]":"Developed the foundation’s vision, mission, and its goals. Developed the foundation’s corporate design and website. Leading its daily operations and annual reviews and submissions. Represented the foundation in a 40th establishment celebration.","'CV Employee Work Experience'[CV Start Date]":"2017-11-01","'CV Employee Work Experience'[CV End Date]":""},{"'CV Employee Work Experience'[CV Company Name]":"Nickl &amp; Partner Architecture Company","'CV Employee Work Experience'[CV Job Title]":"consultant in healthcare facility design and management","'CV Employee Work Experience'[CV Responsibilities Summary]":"Worked closely in several investment opportunities mainly in healthcare facility design and management. Participated in several projects, cooperation, and investment initiatives in several cities across China (those were led by the Germany Company and its Chinese Partners).","'CV Employee Work Experience'[CV Start Date]":"2019-01-01","'CV Employee Work Experience'[CV End Date]":"2021-12-31"}]</v>
+        <v>[{"CV Employee Work Experience[CV Company Name]":"The Health Authority - HAAD","CV Employee Work Experience[CV Job Title]":"Quality Officer","CV Employee Work Experience[CV Responsibilities Summary]":"Led evaluation study of Abu Dhabi’s public clinics, used in improving the services. Led clinical investigation committee into malpractice incidents. Supported implementation of patients’ clinical complaints system. Supported implementation of JCIA standards in 2 Abu Dhabi public hospitals. Compiled quarterly and annually statistics and completed general studies.","CV Employee Work Experience[CV Start Date]":"2005-01-01","CV Employee Work Experience[CV End Date]":"2007-12-31"},{"CV Employee Work Experience[CV Company Name]":"The Health Authority - HAAD","CV Employee Work Experience[CV Job Title]":"Coordinator &amp; Judicial Inspector","CV Employee Work Experience[CV Responsibilities Summary]":"Judicial Inspector authorized by both Health Authority and Judicial Department in Abu Dhabi. Supported implementation of Abu Dhabi’s health insurance laws and regulations. Chaired the committee standardized tri and bipartite contracts in Abu Dhabi’s Health Insurance Scheme. Supported establishment of HAAD’s Health System Financing Department.","CV Employee Work Experience[CV Start Date]":"2007-01-01","CV Employee Work Experience[CV End Date]":"2009-12-31"},{"CV Employee Work Experience[CV Company Name]":"The Health Authority - HAAD","CV Employee Work Experience[CV Job Title]":"Head of Quality &amp; Excellent and Acting Head of Customer Services Center","CV Employee Work Experience[CV Responsibilities Summary]":"Review, compile and submit quality reports on internal progress related to developing human resources, policies, strategies, partnerships and resources, and the consequent results for customers, partners, society, and key organizational outcomes. Collaborated with corporate and operational teams to improve HAAD’s internal processes, services and customer relations, and supported establishment of Abu Dhabi’s Communication Centre. Initiated, implemented, and led HAAD’s Customer Service Centre (including migration from manual drop-in boxes to automated system). Recruited and trained and supervised seven Customer Service Representatives.","CV Employee Work Experience[CV Start Date]":"2008-01-01","CV Employee Work Experience[CV End Date]":"2009-12-31"},{"CV Employee Work Experience[CV Company Name]":"General Secretariat of Abu Dhabi Executive Council","CV Employee Work Experience[CV Job Title]":"Senior Specialist at the Strategy &amp; Policy Division","CV Employee Work Experience[CV Responsibilities Summary]":"Senior researcher, analyst, and project member in the social policy project. Senior analyst in the first CAPEX review and evaluation cycle of 2010/2011. Team lead in operational requests for entities mapped under the social sector. Senior member in the project of restructuring social services sector [2011-2012].","CV Employee Work Experience[CV Start Date]":"2009-01-01","CV Employee Work Experience[CV End Date]":"2011-12-31"},{"CV Employee Work Experience[CV Company Name]":"General Secretariat of Abu Dhabi Executive Council","CV Employee Work Experience[CV Job Title]":"Head of Social Policy &amp; Research Section","CV Employee Work Experience[CV Responsibilities Summary]":"Member of the Abu Dhabi Advising Committee for Social Services. Member of Prisoners Care Working Group in Abu Dhabi. Leading major projects: e.g., poverty study, baseline of social assistance system, baseline of social development sector, prisoners care, inclusion policy, social policy, social service evaluation, child protection system. Team responsibilities: delegating, following up, reviewing, editing, finalizing, evaluating progress and performance, and executing employees’ development plans.","CV Employee Work Experience[CV Start Date]":"2011-01-01","CV Employee Work Experience[CV End Date]":"2013-12-31"},{"CV Employee Work Experience[CV Company Name]":"General Secretariat of Abu Dhabi Executive Council","CV Employee Work Experience[CV Job Title]":"Senior Projects Manager","CV Employee Work Experience[CV Responsibilities Summary]":"Leading a number of special projects: e.g. GSEC IT Strategy, OCSA Initiatives 2014, and Demography Development in Emirate of Abu Dhabi.","CV Employee Work Experience[CV Start Date]":"2013-06-01","CV Employee Work Experience[CV End Date]":"2016-12-31"},{"CV Employee Work Experience[CV Company Name]":"German Federal Ministry of Health – BMG","CV Employee Work Experience[CV Job Title]":"2-months work placement","CV Employee Work Experience[CV Responsibilities Summary]":"","CV Employee Work Experience[CV Start Date]":"2014-08-01","CV Employee Work Experience[CV End Date]":"2014-09-30"},{"CV Employee Work Experience[CV Company Name]":"General Secretariat of Abu Dhabi Executive Council","CV Employee Work Experience[CV Job Title]":"Acting Head of Health Systems Section","CV Employee Work Experience[CV Responsibilities Summary]":"Managing daily operations related to the executive committees’ tasks. Analysis of daily requests received from entities in the healthcare sector. Managing special projects related to healthcare sector.","CV Employee Work Experience[CV Start Date]":"2015-01-01","CV Employee Work Experience[CV End Date]":"2016-03-31"},{"CV Employee Work Experience[CV Company Name]":"Nickl Academy GmbH","CV Employee Work Experience[CV Job Title]":"CEO &amp; Founder","CV Employee Work Experience[CV Responsibilities Summary]":"Founded an Academy in Munich focusing on delivering training programs for young professionals directly involved in designing and managing healthcare facilities.","CV Employee Work Experience[CV Start Date]":"2017-01-01","CV Employee Work Experience[CV End Date]":"2021-12-31"},{"CV Employee Work Experience[CV Company Name]":"Charitable Foundation","CV Employee Work Experience[CV Job Title]":"CEO","CV Employee Work Experience[CV Responsibilities Summary]":"Developed the foundation’s vision, mission, and its goals. Developed the foundation’s corporate design and website. Leading its daily operations and annual reviews and submissions. Represented the foundation in a 40th establishment celebration.","CV Employee Work Experience[CV Start Date]":"2017-11-01","CV Employee Work Experience[CV End Date]":""},{"CV Employee Work Experience[CV Company Name]":"Nickl &amp; Partner Architecture Company","CV Employee Work Experience[CV Job Title]":"consultant in healthcare facility design and management","CV Employee Work Experience[CV Responsibilities Summary]":"Worked closely in several investment opportunities mainly in healthcare facility design and management. Participated in several projects, cooperation, and investment initiatives in several cities across China (those were led by the Germany Company and its Chinese Partners).","CV Employee Work Experience[CV Start Date]":"2019-01-01","CV Employee Work Experience[CV End Date]":"2021-12-31"}]</v>
       </c>
       <c r="BD4" t="str">
         <v>Afra Khalifa Alghfeli is a seasoned healthcare leader with over 21 years of executive experience in strategic planning, health systems management, and healthcare facility design across Abu Dhabi’s public sector and international institutions. She has held senior roles including CEO of a charitable foundation, Acting Head of Health Systems at the Abu Dhabi Executive Council, and leadership positions at HAAD, driving quality assurance, policy development, and customer service excellence. A recognized expert in data analysis and reporting, she holds an MBA in International Hospital &amp; Healthcare Management, a Bachelor’s in Health Information Management, and an Oxford Diploma in Organizational Leadership from Said Business School.</v>
@@ -1211,25 +1211,25 @@
         <v>0</v>
       </c>
       <c r="AN5" t="str">
-        <v>[{"'CV Employee Competencies'[Technical Competency Name]":"Critical thinking"},{"'CV Employee Competencies'[Technical Competency Name]":"Time Management"},{"'CV Employee Competencies'[Technical Competency Name]":"Collaborative"},{"'CV Employee Competencies'[Technical Competency Name]":"Leadership"},{"'CV Employee Competencies'[Technical Competency Name]":"English"},{"'CV Employee Competencies'[Technical Competency Name]":"Arabic"},{"'CV Employee Competencies'[Technical Competency Name]":"International Studies"},{"'CV Employee Competencies'[Technical Competency Name]":"Data Research and Analysis"},{"'CV Employee Competencies'[Technical Competency Name]":"Financial Analysis"},{"'CV Employee Competencies'[Technical Competency Name]":"Professional Networking"},{"'CV Employee Competencies'[Technical Competency Name]":"Effective Workplace Communication"},{"'CV Employee Competencies'[Technical Competency Name]":"Edaad Workshops"}]</v>
+        <v>[{"CV Employee Competencies[Technical Competency Name]":"Critical thinking"},{"CV Employee Competencies[Technical Competency Name]":"Time Management"},{"CV Employee Competencies[Technical Competency Name]":"Collaborative"},{"CV Employee Competencies[Technical Competency Name]":"Leadership"},{"CV Employee Competencies[Technical Competency Name]":"English"},{"CV Employee Competencies[Technical Competency Name]":"Arabic"},{"CV Employee Competencies[Technical Competency Name]":"International Studies"},{"CV Employee Competencies[Technical Competency Name]":"Data Research and Analysis"},{"CV Employee Competencies[Technical Competency Name]":"Financial Analysis"},{"CV Employee Competencies[Technical Competency Name]":"Professional Networking"},{"CV Employee Competencies[Technical Competency Name]":"Effective Workplace Communication"},{"CV Employee Competencies[Technical Competency Name]":"Edaad Workshops"}]</v>
       </c>
       <c r="AO5" t="str">
-        <v>[{"'Employee Competencies Rating'[Competancy Name]":"Facilitates Collaboration and Influence","'Employee Competencies Rating'[Employee Rating]":"5","'Employee Competencies Rating'[Supervisor Rating]":"4","'Employee Competencies Rating'[Employee Rating Description]":"Role Model","'Employee Competencies Rating'[Supervisor Rating Description]":"Champion"},{"'Employee Competencies Rating'[Competancy Name]":"Critical Thinking and Data-Driven Decision Making","'Employee Competencies Rating'[Employee Rating]":"4","'Employee Competencies Rating'[Supervisor Rating]":"4","'Employee Competencies Rating'[Employee Rating Description]":"Champion","'Employee Competencies Rating'[Supervisor Rating Description]":"Champion"},{"'Employee Competencies Rating'[Competancy Name]":"Digital Savviness","'Employee Competencies Rating'[Employee Rating]":"3","'Employee Competencies Rating'[Supervisor Rating]":"3","'Employee Competencies Rating'[Employee Rating Description]":"Solid Performer","'Employee Competencies Rating'[Supervisor Rating Description]":"Solid Performer"},{"'Employee Competencies Rating'[Competancy Name]":"Intrapreneurship","'Employee Competencies Rating'[Employee Rating]":"5","'Employee Competencies Rating'[Supervisor Rating]":"4","'Employee Competencies Rating'[Employee Rating Description]":"Role Model","'Employee Competencies Rating'[Supervisor Rating Description]":"Champion"},{"'Employee Competencies Rating'[Competancy Name]":"Learning Agility","'Employee Competencies Rating'[Employee Rating]":"5","'Employee Competencies Rating'[Supervisor Rating]":"5","'Employee Competencies Rating'[Employee Rating Description]":"Role Model","'Employee Competencies Rating'[Supervisor Rating Description]":"Role Model"},{"'Employee Competencies Rating'[Competancy Name]":"Public Service Excellence","'Employee Competencies Rating'[Employee Rating]":"5","'Employee Competencies Rating'[Supervisor Rating]":"4","'Employee Competencies Rating'[Employee Rating Description]":"Role Model","'Employee Competencies Rating'[Supervisor Rating Description]":"Champion"},{"'Employee Competencies Rating'[Competancy Name]":"Results-Driven Outcomes","'Employee Competencies Rating'[Employee Rating]":"4","'Employee Competencies Rating'[Supervisor Rating]":"4","'Employee Competencies Rating'[Employee Rating Description]":"Champion","'Employee Competencies Rating'[Supervisor Rating Description]":"Champion"},{"'Employee Competencies Rating'[Competancy Name]":"Leading Change","'Employee Competencies Rating'[Employee Rating]":"5","'Employee Competencies Rating'[Supervisor Rating]":"3","'Employee Competencies Rating'[Employee Rating Description]":"Role Model","'Employee Competencies Rating'[Supervisor Rating Description]":"Solid Performer"}]</v>
+        <v>[{"Employee Competencies Rating[Competancy Name]":"Facilitates Collaboration and Influence","Employee Competencies Rating[Employee Rating]":"5","Employee Competencies Rating[Supervisor Rating]":"4","Employee Competencies Rating[Employee Rating Description]":"Role Model","Employee Competencies Rating[Supervisor Rating Description]":"Champion"},{"Employee Competencies Rating[Competancy Name]":"Critical Thinking and Data-Driven Decision Making","Employee Competencies Rating[Employee Rating]":"4","Employee Competencies Rating[Supervisor Rating]":"4","Employee Competencies Rating[Employee Rating Description]":"Champion","Employee Competencies Rating[Supervisor Rating Description]":"Champion"},{"Employee Competencies Rating[Competancy Name]":"Digital Savviness","Employee Competencies Rating[Employee Rating]":"3","Employee Competencies Rating[Supervisor Rating]":"3","Employee Competencies Rating[Employee Rating Description]":"Solid Performer","Employee Competencies Rating[Supervisor Rating Description]":"Solid Performer"},{"Employee Competencies Rating[Competancy Name]":"Intrapreneurship","Employee Competencies Rating[Employee Rating]":"5","Employee Competencies Rating[Supervisor Rating]":"4","Employee Competencies Rating[Employee Rating Description]":"Role Model","Employee Competencies Rating[Supervisor Rating Description]":"Champion"},{"Employee Competencies Rating[Competancy Name]":"Learning Agility","Employee Competencies Rating[Employee Rating]":"5","Employee Competencies Rating[Supervisor Rating]":"5","Employee Competencies Rating[Employee Rating Description]":"Role Model","Employee Competencies Rating[Supervisor Rating Description]":"Role Model"},{"Employee Competencies Rating[Competancy Name]":"Public Service Excellence","Employee Competencies Rating[Employee Rating]":"5","Employee Competencies Rating[Supervisor Rating]":"4","Employee Competencies Rating[Employee Rating Description]":"Role Model","Employee Competencies Rating[Supervisor Rating Description]":"Champion"},{"Employee Competencies Rating[Competancy Name]":"Results-Driven Outcomes","Employee Competencies Rating[Employee Rating]":"4","Employee Competencies Rating[Supervisor Rating]":"4","Employee Competencies Rating[Employee Rating Description]":"Champion","Employee Competencies Rating[Supervisor Rating Description]":"Champion"},{"Employee Competencies Rating[Competancy Name]":"Leading Change","Employee Competencies Rating[Employee Rating]":"5","Employee Competencies Rating[Supervisor Rating]":"3","Employee Competencies Rating[Employee Rating Description]":"Role Model","Employee Competencies Rating[Supervisor Rating Description]":"Solid Performer"}]</v>
       </c>
       <c r="AP5" t="str">
         <v>[]</v>
       </c>
       <c r="AQ5" t="str">
-        <v>[{"'CV Employee Achievements and Awards'[CV Title]":"Professional Networking","'CV Employee Achievements and Awards'[CV Achievement Description]":"","'CV Employee Achievements and Awards'[CV Issue Date]":"2023-01-01"},{"'CV Employee Achievements and Awards'[CV Title]":"Effective Workplace Communication","'CV Employee Achievements and Awards'[CV Achievement Description]":"","'CV Employee Achievements and Awards'[CV Issue Date]":"2023-01-01"},{"'CV Employee Achievements and Awards'[CV Title]":"Edaad Workshops","'CV Employee Achievements and Awards'[CV Achievement Description]":"","'CV Employee Achievements and Awards'[CV Issue Date]":"2022-01-01"}]</v>
+        <v>[{"CV Employee Achievements and Awards[CV Title]":"Professional Networking","CV Employee Achievements and Awards[CV Achievement Description]":"","CV Employee Achievements and Awards[CV Issue Date]":"2023-01-01"},{"CV Employee Achievements and Awards[CV Title]":"Effective Workplace Communication","CV Employee Achievements and Awards[CV Achievement Description]":"","CV Employee Achievements and Awards[CV Issue Date]":"2023-01-01"},{"CV Employee Achievements and Awards[CV Title]":"Edaad Workshops","CV Employee Achievements and Awards[CV Achievement Description]":"","CV Employee Achievements and Awards[CV Issue Date]":"2022-01-01"}]</v>
       </c>
       <c r="AR5" t="str">
         <v>[]</v>
       </c>
       <c r="AS5" t="str">
-        <v>[{"'Employee Performance'[Performance Review Period]":"2024 Review Period","'Employee Performance'[Calculated Rating]":"3.92","'Employee Performance'[Normalized Performance Rating]":"Meets Expectations"}]</v>
+        <v>[{"Employee Performance[Performance Review Period]":"2024 Review Period","Employee Performance[Calculated Rating]":"3.92","Employee Performance[Normalized Performance Rating]":"Meets Expectations"}]</v>
       </c>
       <c r="AT5" t="str">
-        <v>[{"'Employee Achievements'[Customary Name]":"2024 Annual Appraisal","'Employee Achievements'[Manager OA Comments]":"Noura has demonstrated excellent progress since joining in April 2024. She has consistently shown dedication, reliability, and a proactive attitude in supporting the team and contributing to key projects. Her ability to collaborate effectively with internal and external stakeholders, coupled with her eagerness to seek feedback and improve has made her a valuable team member. Noura's growing confidence and willingness to take ownership of tasks, including leading some independently, highlight her strong potential for future growth.","'Employee Achievements'[Employee OA Comments]":"Overall, I'm very proud of everything I achieved and everything my team achieved. For the time I've been here we have been through challenges together, yet we stayed put which is one of the things I really valued. During this time, we had major and high priority requests and projects that we have been through many challenges while working on. My main focus on both was to ensure that the outcome will add to Abu Dhabi as a whole and contribute to the betterment of our country. My secondary focus was to build myself and create bonds with my teammates. I'm happy to see that by now I achieved all of the above. I learned a lot from everyone around me especially my team. I'm looking forward to more positive outcomes under all circumstances and hopefully end next year on the same positive note as this year."}]</v>
+        <v>[{"Employee Achievements[Customary Name]":"2024 Annual Appraisal","Employee Achievements[Manager OA Comments]":"Noura has demonstrated excellent progress since joining in April 2024. She has consistently shown dedication, reliability, and a proactive attitude in supporting the team and contributing to key projects. Her ability to collaborate effectively with internal and external stakeholders, coupled with her eagerness to seek feedback and improve has made her a valuable team member. Noura's growing confidence and willingness to take ownership of tasks, including leading some independently, highlight her strong potential for future growth.","Employee Achievements[Employee OA Comments]":"Overall, I'm very proud of everything I achieved and everything my team achieved. For the time I've been here we have been through challenges together, yet we stayed put which is one of the things I really valued. During this time, we had major and high priority requests and projects that we have been through many challenges while working on. My main focus on both was to ensure that the outcome will add to Abu Dhabi as a whole and contribute to the betterment of our country. My secondary focus was to build myself and create bonds with my teammates. I'm happy to see that by now I achieved all of the above. I learned a lot from everyone around me especially my team. I'm looking forward to more positive outcomes under all circumstances and hopefully end next year on the same positive note as this year."}]</v>
       </c>
       <c r="AU5" t="str">
         <v>[]</v>
@@ -1238,13 +1238,13 @@
         <v/>
       </c>
       <c r="AY5" t="str">
-        <v>[{"'Employee Qualification'[Qualification Title]":"Interntional Studies Concentration in Political Economy and Development","'Employee Qualification'[Educational Institute]":"Zayed University","'Employee Qualification'[GPA (Grade Point Average)]":"3.52","'Employee Qualification'[Study Start Date]":"2019-09-01","'Employee Qualification'[Study End Date]":"2023-10-03"}]</v>
+        <v>[{"Employee Qualification[Qualification Title]":"Interntional Studies Concentration in Political Economy and Development","Employee Qualification[Educational Institute]":"Zayed University","Employee Qualification[GPA (Grade Point Average)]":"3.52","Employee Qualification[Study Start Date]":"2019-09-01","Employee Qualification[Study End Date]":"2023-10-03"}]</v>
       </c>
       <c r="AZ5" t="str">
-        <v>[{"'CV Employee Education'[CV Institution Name]":"Zayed University","'CV Employee Education'[CV Degree Name]":"Bachelor of Arts","'CV Employee Education'[CV Start Date]":"2019-01-01","'CV Employee Education'[CV End Date]":"2023-12-31"}]</v>
+        <v>[{"CV Employee Education[CV Institution Name]":"Zayed University","CV Employee Education[CV Degree Name]":"Bachelor of Arts","CV Employee Education[CV Start Date]":"2019-01-01","CV Employee Education[CV End Date]":"2023-12-31"}]</v>
       </c>
       <c r="BA5" t="str">
-        <v>[{"'Employee Assignment History'[Assignment Name]":"E1318","'Employee Assignment History'[Position Title]":"Junior Specialist, Community Affairs","'Employee Assignment History'[Employee Grade]":"4C","'Employee Assignment History'[Assignment Start Date]":"2024-04-16","'Employee Assignment History'[Assignment End Date]":"2025-07-31","'Employee Assignment History'[Assignment Experience (Years &amp; Months)]":"1 Years, 3 Months"},{"'Employee Assignment History'[Assignment Name]":"Junior Specialist, Community Affairs","'Employee Assignment History'[Position Title]":"Junior Specialist, Community Affairs","'Employee Assignment History'[Employee Grade]":"4C","'Employee Assignment History'[Assignment Start Date]":"2025-08-01","'Employee Assignment History'[Assignment End Date]":"","'Employee Assignment History'[Assignment Experience (Years &amp; Months)]":""}]</v>
+        <v>[{"Employee Assignment History[Assignment Name]":"E1318","Employee Assignment History[Position Title]":"Junior Specialist, Community Affairs","Employee Assignment History[Employee Grade]":"4C","Employee Assignment History[Assignment Start Date]":"2024-04-16","Employee Assignment History[Assignment End Date]":"2025-07-31","Employee Assignment History[Assignment Experience (Years &amp; Months)]":"1 Years, 3 Months"},{"Employee Assignment History[Assignment Name]":"Junior Specialist, Community Affairs","Employee Assignment History[Position Title]":"Junior Specialist, Community Affairs","Employee Assignment History[Employee Grade]":"4C","Employee Assignment History[Assignment Start Date]":"2025-08-01","Employee Assignment History[Assignment End Date]":"","Employee Assignment History[Assignment Experience (Years &amp; Months)]":""}]</v>
       </c>
       <c r="BB5" t="str">
         <v>[]</v>
@@ -1378,25 +1378,25 @@
         <v>0</v>
       </c>
       <c r="AN6" t="str">
-        <v>[{"'CV Employee Competencies'[Technical Competency Name]":"English"},{"'CV Employee Competencies'[Technical Competency Name]":"Arabic"},{"'CV Employee Competencies'[Technical Competency Name]":"Executive MBA"},{"'CV Employee Competencies'[Technical Competency Name]":"Strategic Planning"},{"'CV Employee Competencies'[Technical Competency Name]":"Business Continuity"},{"'CV Employee Competencies'[Technical Competency Name]":"Merger Integration"},{"'CV Employee Competencies'[Technical Competency Name]":"Social Innovation"},{"'CV Employee Competencies'[Technical Competency Name]":"Strategic Management"},{"'CV Employee Competencies'[Technical Competency Name]":"Leadership"},{"'CV Employee Competencies'[Technical Competency Name]":"Performance Management"},{"'CV Employee Competencies'[Technical Competency Name]":"Risk Management"},{"'CV Employee Competencies'[Technical Competency Name]":"Strategic Partnerships"},{"'CV Employee Competencies'[Technical Competency Name]":"Project Management"},{"'CV Employee Competencies'[Technical Competency Name]":"Program Management Office (PMO)"},{"'CV Employee Competencies'[Technical Competency Name]":"Balanced Scorecard"},{"'CV Employee Competencies'[Technical Competency Name]":"Market Research"},{"'CV Employee Competencies'[Technical Competency Name]":"Economic Analysis"},{"'CV Employee Competencies'[Technical Competency Name]":"Financial Analysis"},{"'CV Employee Competencies'[Technical Competency Name]":"Valuation Models"},{"'CV Employee Competencies'[Technical Competency Name]":"Business Development"},{"'CV Employee Competencies'[Technical Competency Name]":"Go-to-Market Strategy"},{"'CV Employee Competencies'[Technical Competency Name]":"Corporate Strategy"},{"'CV Employee Competencies'[Technical Competency Name]":"Stakeholder Management"},{"'CV Employee Competencies'[Technical Competency Name]":"Team Leadership"},{"'CV Employee Competencies'[Technical Competency Name]":"Communication"},{"'CV Employee Competencies'[Technical Competency Name]":"Policy Development"},{"'CV Employee Competencies'[Technical Competency Name]":"Corporate Social Responsibility"},{"'CV Employee Competencies'[Technical Competency Name]":"Community Engagement"}]</v>
+        <v>[{"CV Employee Competencies[Technical Competency Name]":"English"},{"CV Employee Competencies[Technical Competency Name]":"Arabic"},{"CV Employee Competencies[Technical Competency Name]":"Executive MBA"},{"CV Employee Competencies[Technical Competency Name]":"Strategic Planning"},{"CV Employee Competencies[Technical Competency Name]":"Business Continuity"},{"CV Employee Competencies[Technical Competency Name]":"Merger Integration"},{"CV Employee Competencies[Technical Competency Name]":"Social Innovation"},{"CV Employee Competencies[Technical Competency Name]":"Strategic Management"},{"CV Employee Competencies[Technical Competency Name]":"Leadership"},{"CV Employee Competencies[Technical Competency Name]":"Performance Management"},{"CV Employee Competencies[Technical Competency Name]":"Risk Management"},{"CV Employee Competencies[Technical Competency Name]":"Strategic Partnerships"},{"CV Employee Competencies[Technical Competency Name]":"Project Management"},{"CV Employee Competencies[Technical Competency Name]":"Program Management Office (PMO)"},{"CV Employee Competencies[Technical Competency Name]":"Balanced Scorecard"},{"CV Employee Competencies[Technical Competency Name]":"Market Research"},{"CV Employee Competencies[Technical Competency Name]":"Economic Analysis"},{"CV Employee Competencies[Technical Competency Name]":"Financial Analysis"},{"CV Employee Competencies[Technical Competency Name]":"Valuation Models"},{"CV Employee Competencies[Technical Competency Name]":"Business Development"},{"CV Employee Competencies[Technical Competency Name]":"Go-to-Market Strategy"},{"CV Employee Competencies[Technical Competency Name]":"Corporate Strategy"},{"CV Employee Competencies[Technical Competency Name]":"Stakeholder Management"},{"CV Employee Competencies[Technical Competency Name]":"Team Leadership"},{"CV Employee Competencies[Technical Competency Name]":"Communication"},{"CV Employee Competencies[Technical Competency Name]":"Policy Development"},{"CV Employee Competencies[Technical Competency Name]":"Corporate Social Responsibility"},{"CV Employee Competencies[Technical Competency Name]":"Community Engagement"}]</v>
       </c>
       <c r="AO6" t="str">
         <v>[]</v>
       </c>
       <c r="AP6" t="str">
-        <v>[{"'CV Employee Interest and Hobbies'[CV Interest Name]":"Female Volleyball Tournament","'CV Employee Interest and Hobbies'[CV Interest Description]":"Organized as part of community and charity events"},{"'CV Employee Interest and Hobbies'[CV Interest Name]":"Community Service","'CV Employee Interest and Hobbies'[CV Interest Description]":"Administered marketing and communication activities for community and charity events, including schools re-building"}]</v>
+        <v>[{"CV Employee Interest and Hobbies[CV Interest Name]":"Female Volleyball Tournament","CV Employee Interest and Hobbies[CV Interest Description]":"Organized as part of community and charity events"},{"CV Employee Interest and Hobbies[CV Interest Name]":"Community Service","CV Employee Interest and Hobbies[CV Interest Description]":"Administered marketing and communication activities for community and charity events, including schools re-building"}]</v>
       </c>
       <c r="AQ6" t="str">
-        <v>[{"'CV Employee Achievements and Awards'[CV Title]":"Executive Education; Strategic Management of Regulatory and Enforcement Agencies","'CV Employee Achievements and Awards'[CV Achievement Description]":"","'CV Employee Achievements and Awards'[CV Issue Date]":"2021-01-01"},{"'CV Employee Achievements and Awards'[CV Title]":"Executive Education; Inspirational Leadership","'CV Employee Achievements and Awards'[CV Achievement Description]":"","'CV Employee Achievements and Awards'[CV Issue Date]":"2020-01-01"},{"'CV Employee Achievements and Awards'[CV Title]":"International Exchange Programme Participant","'CV Employee Achievements and Awards'[CV Achievement Description]":"","'CV Employee Achievements and Awards'[CV Issue Date]":"2016-09-01"}]</v>
+        <v>[{"CV Employee Achievements and Awards[CV Title]":"Executive Education; Strategic Management of Regulatory and Enforcement Agencies","CV Employee Achievements and Awards[CV Achievement Description]":"","CV Employee Achievements and Awards[CV Issue Date]":"2021-01-01"},{"CV Employee Achievements and Awards[CV Title]":"Executive Education; Inspirational Leadership","CV Employee Achievements and Awards[CV Achievement Description]":"","CV Employee Achievements and Awards[CV Issue Date]":"2020-01-01"},{"CV Employee Achievements and Awards[CV Title]":"International Exchange Programme Participant","CV Employee Achievements and Awards[CV Achievement Description]":"","CV Employee Achievements and Awards[CV Issue Date]":"2016-09-01"}]</v>
       </c>
       <c r="AR6" t="str">
         <v>[]</v>
       </c>
       <c r="AS6" t="str">
-        <v>[{"'Employee Performance'[Performance Review Period]":"2024 Review Period","'Employee Performance'[Calculated Rating]":"","'Employee Performance'[Normalized Performance Rating]":"Exceeds Expectations"}]</v>
+        <v>[{"Employee Performance[Performance Review Period]":"2024 Review Period","Employee Performance[Calculated Rating]":"","Employee Performance[Normalized Performance Rating]":"Exceeds Expectations"}]</v>
       </c>
       <c r="AT6" t="str">
-        <v>[{"'Employee Achievements'[Customary Name]":"2024 Annual Appraisal","'Employee Achievements'[Manager OA Comments]":"","'Employee Achievements'[Employee OA Comments]":"By completing 10 months, I have consistently delivered high-impact results, demonstrating leadership, strategic thinking, and operational excellence across multiple areas. My contributions have enhanced efficiency, strengthened decision-making, and driven key activities that align with Abu Dhabi and the organization’s priorities.1. Case Management &amp; ECAS RequestsLed efforts to enhance team performance, analysis quality, and decision-making speed within 9–10 months.Instilled a case management mindset within the team, ensuring ownership and accountability across the full value chain of requests.Achieved 93% in Wellbeing (exceeding the 90% target) and 90% in Urban Planning, where I served in an acting capacity.Q3 &amp; Q4: 0% of topics returned due to insufficient analysis, ensuring seamless committee decision-making.2. Talent ManagementSuccessfully addressed critical workforce shortages, filling 100% of Health sector roles and 2 out of 3 Social sector roles.Coached &amp; developed high-potential leaders, empowering Saeed in Operations and preparing Reem for the Executive Director succession pool.Facilitated the voluntary transition of 4 disengaged employees, allowing for new high-performing talent and reinforcing workforce alignment and leadership effectiveness.3. Special ProjectsAchieved 100% completion of special projects (exceeding the 80% target) with high-quality, timely studies and policy recommendations.Led strategic projects on Mental Health, Civil Defense &amp; Fire, Higher Education &amp; TVET, Fertility &amp; Family Growth, and Livability 2.0.Proposed and completed key initiatives such as Emiratization in the Health Sector, a Mental Health Deep Dive, and the EC Committee Governance Model, driving data-driven decision-making.4. Stakeholder ManagementExceeded the target for engagement meetings, with Q4 alone capturing 24 meetings (double the target).Proactively engaged committee chairmen and leadership, ensuring informed, aligned, and engaged decision-makers.Provided critical briefings, studies, and analyses on Fires Deep Dive, IPC, Alternative Pregnancy Methods, Fertility &amp; Family Growth, and Al Falah’s outcomes demonstration.Ensured full alignment with the Wellbeing Committee Chairman on agendas, topics, and resolutions, reinforcing strategic readiness and effective decision-making.5. Committee Management &amp; Chairman Account ManagementExceeded resolution success targets, achieving 0% returned requests (vs. the Exceeded stakeholder engagement targets, with 24 meetings in Q4, reinforcing continuous leadership alignmen"}]</v>
+        <v>[{"Employee Achievements[Customary Name]":"2024 Annual Appraisal","Employee Achievements[Manager OA Comments]":"","Employee Achievements[Employee OA Comments]":"By completing 10 months, I have consistently delivered high-impact results, demonstrating leadership, strategic thinking, and operational excellence across multiple areas. My contributions have enhanced efficiency, strengthened decision-making, and driven key activities that align with Abu Dhabi and the organization’s priorities.1. Case Management &amp; ECAS RequestsLed efforts to enhance team performance, analysis quality, and decision-making speed within 9–10 months.Instilled a case management mindset within the team, ensuring ownership and accountability across the full value chain of requests.Achieved 93% in Wellbeing (exceeding the 90% target) and 90% in Urban Planning, where I served in an acting capacity.Q3 &amp; Q4: 0% of topics returned due to insufficient analysis, ensuring seamless committee decision-making.2. Talent ManagementSuccessfully addressed critical workforce shortages, filling 100% of Health sector roles and 2 out of 3 Social sector roles.Coached &amp; developed high-potential leaders, empowering Saeed in Operations and preparing Reem for the Executive Director succession pool.Facilitated the voluntary transition of 4 disengaged employees, allowing for new high-performing talent and reinforcing workforce alignment and leadership effectiveness.3. Special ProjectsAchieved 100% completion of special projects (exceeding the 80% target) with high-quality, timely studies and policy recommendations.Led strategic projects on Mental Health, Civil Defense &amp; Fire, Higher Education &amp; TVET, Fertility &amp; Family Growth, and Livability 2.0.Proposed and completed key initiatives such as Emiratization in the Health Sector, a Mental Health Deep Dive, and the EC Committee Governance Model, driving data-driven decision-making.4. Stakeholder ManagementExceeded the target for engagement meetings, with Q4 alone capturing 24 meetings (double the target).Proactively engaged committee chairmen and leadership, ensuring informed, aligned, and engaged decision-makers.Provided critical briefings, studies, and analyses on Fires Deep Dive, IPC, Alternative Pregnancy Methods, Fertility &amp; Family Growth, and Al Falah’s outcomes demonstration.Ensured full alignment with the Wellbeing Committee Chairman on agendas, topics, and resolutions, reinforcing strategic readiness and effective decision-making.5. Committee Management &amp; Chairman Account ManagementExceeded resolution success targets, achieving 0% returned requests (vs. the Exceeded stakeholder engagement targets, with 24 meetings in Q4, reinforcing continuous leadership alignmen"}]</v>
       </c>
       <c r="AU6" t="str">
         <v>[]</v>
@@ -1411,19 +1411,19 @@
         <v>Financial Increase</v>
       </c>
       <c r="AY6" t="str">
-        <v>[{"'Employee Qualification'[Qualification Title]":"Master of Business Administration","'Employee Qualification'[Educational Institute]":"London Business School","'Employee Qualification'[GPA (Grade Point Average)]":"","'Employee Qualification'[Study Start Date]":"2015-09-01","'Employee Qualification'[Study End Date]":"2017-07-26"}]</v>
+        <v>[{"Employee Qualification[Qualification Title]":"Master of Business Administration","Employee Qualification[Educational Institute]":"London Business School","Employee Qualification[GPA (Grade Point Average)]":"","Employee Qualification[Study Start Date]":"2015-09-01","Employee Qualification[Study End Date]":"2017-07-26"}]</v>
       </c>
       <c r="AZ6" t="str">
-        <v>[{"'CV Employee Education'[CV Institution Name]":"American University of Sharjah","'CV Employee Education'[CV Degree Name]":"","'CV Employee Education'[CV Start Date]":"2003-01-01","'CV Employee Education'[CV End Date]":"2007-12-31"},{"'CV Employee Education'[CV Institution Name]":"London Business School","'CV Employee Education'[CV Degree Name]":"Executive MBA","'CV Employee Education'[CV Start Date]":"2015-01-01","'CV Employee Education'[CV End Date]":"2017-12-31"}]</v>
+        <v>[{"CV Employee Education[CV Institution Name]":"American University of Sharjah","CV Employee Education[CV Degree Name]":"","CV Employee Education[CV Start Date]":"2003-01-01","CV Employee Education[CV End Date]":"2007-12-31"},{"CV Employee Education[CV Institution Name]":"London Business School","CV Employee Education[CV Degree Name]":"Executive MBA","CV Employee Education[CV Start Date]":"2015-01-01","CV Employee Education[CV End Date]":"2017-12-31"}]</v>
       </c>
       <c r="BA6" t="str">
-        <v>[{"'Employee Assignment History'[Assignment Name]":"Executive Director","'Employee Assignment History'[Position Title]":"Executive Director, Wellbeing Sector","'Employee Assignment History'[Employee Grade]":"EDA","'Employee Assignment History'[Assignment Start Date]":"2024-02-19","'Employee Assignment History'[Assignment End Date]":"2025-05-21","'Employee Assignment History'[Assignment Experience (Years &amp; Months)]":"1 Years, 3 Months"},{"'Employee Assignment History'[Assignment Name]":"Executive Director, Wellbeing Sector","'Employee Assignment History'[Position Title]":"Executive Director, Wellbeing Sector","'Employee Assignment History'[Employee Grade]":"EDA","'Employee Assignment History'[Assignment Start Date]":"2025-05-22","'Employee Assignment History'[Assignment End Date]":"","'Employee Assignment History'[Assignment Experience (Years &amp; Months)]":""}]</v>
+        <v>[{"Employee Assignment History[Assignment Name]":"Executive Director","Employee Assignment History[Position Title]":"Executive Director, Wellbeing Sector","Employee Assignment History[Employee Grade]":"EDA","Employee Assignment History[Assignment Start Date]":"2024-02-19","Employee Assignment History[Assignment End Date]":"2025-05-21","Employee Assignment History[Assignment Experience (Years &amp; Months)]":"1 Years, 3 Months"},{"Employee Assignment History[Assignment Name]":"Executive Director, Wellbeing Sector","Employee Assignment History[Position Title]":"Executive Director, Wellbeing Sector","Employee Assignment History[Employee Grade]":"EDA","Employee Assignment History[Assignment Start Date]":"2025-05-22","Employee Assignment History[Assignment End Date]":"","Employee Assignment History[Assignment Experience (Years &amp; Months)]":""}]</v>
       </c>
       <c r="BB6" t="str">
-        <v>[{"'Employee Previous Employer'[Previous Employer Name]":"Yahsat","'Employee Previous Employer'[Previous Job Title]":"Officer - Business Development","'Employee Previous Employer'[Start Date]":"2008-04-13","'Employee Previous Employer'[End Date]":"2011-02-03"},{"'Employee Previous Employer'[Previous Employer Name]":"Department of Community Development","'Employee Previous Employer'[Previous Job Title]":"Strategic Affairs Office Executive Director","'Employee Previous Employer'[Start Date]":"2019-04-14","'Employee Previous Employer'[End Date]":""}]</v>
+        <v>[{"Employee Previous Employer[Previous Employer Name]":"Yahsat","Employee Previous Employer[Previous Job Title]":"Officer - Business Development","Employee Previous Employer[Start Date]":"2008-04-13","Employee Previous Employer[End Date]":"2011-02-03"},{"Employee Previous Employer[Previous Employer Name]":"Department of Community Development","Employee Previous Employer[Previous Job Title]":"Strategic Affairs Office Executive Director","Employee Previous Employer[Start Date]":"2019-04-14","Employee Previous Employer[End Date]":""}]</v>
       </c>
       <c r="BC6" t="str">
-        <v>[{"'CV Employee Work Experience'[CV Company Name]":"YAHSAT","'CV Employee Work Experience'[CV Job Title]":"MENA Region and International Accounts Business Development Officer","'CV Employee Work Experience'[CV Responsibilities Summary]":"Elevated Yahsat regional brand awareness; assisted in appointment of &gt;25 Service Partners across 27 countries. Formed successful relationships with regional business partners, large enterprises and government authorities; resulted in 150% client database growth. Produced MENA region business development strategy and steered marketing research initiatives; ensured 70% of commitment before satellite launch. Contributed in setting up Service Partner Service Agreement to secure company's commercial assets of &gt;$400Mn. Acted as Deputy Chairman of Social Committee with $50,000 budget to enhance corporate citizenship and increased employee engagement.","'CV Employee Work Experience'[CV Start Date]":"2008-04-01","'CV Employee Work Experience'[CV End Date]":"2010-12-31"},{"'CV Employee Work Experience'[CV Company Name]":"YAHSAT","'CV Employee Work Experience'[CV Job Title]":"MENA Region and International Accounts Country Manager","'CV Employee Work Experience'[CV Responsibilities Summary]":"Managed &gt;10 Service Partners in 13 MENA &amp; Asia countries with an average commitment of ~$3.5Mn before satellite launch. Designed solutions for MENA governments and ministries to roll-out national broadband projects (&gt;2Mn) and ICT fund investments to connect schools and hospitals. Created detailed Go-to-Market strategy and executed service launch and operations in 6 MENA countries, along with NGO initiatives with UN &amp; other entities. Conducted economic and financial analysis and customized business cases for enterprise and government accounts on behalf of &gt;10 Service Partners to maximize profitability. Implemented marketing tactics and realized opportunities within regional governmental authorities, Oil &amp; Gas, Banks &amp; NGOs for nationwide projects to evaluate P&amp;L trade-offs. Increased corporate social responsibility and corporate citizenship by chairing Social Committee and a team of 15 seniors with budget of $100,000.","'CV Employee Work Experience'[CV Start Date]":"2011-01-01","'CV Employee Work Experience'[CV End Date]":"2012-12-31"},{"'CV Employee Work Experience'[CV Company Name]":"YAHSAT","'CV Employee Work Experience'[CV Job Title]":"Strategy and Business Development Associate","'CV Employee Work Experience'[CV Responsibilities Summary]":"Supervised strategic management and planning services to establish and align UAE Space Agency with UAE's economy vision, secured $13Mn consultancy project. Collaborated with CEO, Senior Management and Board of Directors to create strategic analysis &amp; actions mandate to enhance operations efficiencies &amp; revenue growth &gt;$1bn. Directed business &amp; development analysis and recommendations to CEO &amp; third parties; resulted in partnerships, procurement &amp; academic program (~$4Mn). Restructured corporate and departmental objectives for 200 employees; directed Performance Management activities (e.g. BSC and CPMS) for corporate strategy execution.","'CV Employee Work Experience'[CV Start Date]":"2013-01-01","'CV Employee Work Experience'[CV End Date]":"2015-12-31"},{"'CV Employee Work Experience'[CV Company Name]":"YAHSAT","'CV Employee Work Experience'[CV Job Title]":"Strategy and Business Development Manager","'CV Employee Work Experience'[CV Responsibilities Summary]":"Conducted market research and social and economic analysis for UAE's governmental space investments and related global projects (&gt; $1bn cumulative). Organized and managed Program Management Office of third satellite manufacturing project (~$300Mn), overseeing &gt;10 work streams and &gt;50 employees. Developed program management policies and processes for a government confidential project (worth ~$1.5Bn). Supported in closing &gt;$150Mn revenue contract for Yahsat. Spearheaded investments and partnership opportunities' feasibility studies, valuation models construction, and new business models propositions to grow profit margins.","'CV Employee Work Experience'[CV Start Date]":"2015-01-01","'CV Employee Work Experience'[CV End Date]":"2017-12-31"},{"'CV Employee Work Experience'[CV Company Name]":"AL YAH SATELLITE COMMUNICATION COMPANY (YAHSAT)","'CV Employee Work Experience'[CV Job Title]":"Strategy and Business Development Associate Vice President (AVP)","'CV Employee Work Experience'[CV Responsibilities Summary]":"Led the pre- and post-merger integration office set up and planning exercise for Thuraya Telecommunication Company, including operational readiness, synergies identification, value capture plan development, day-1 readiness, and governance establishment. Supported valuation and due diligence of Thuraya Telecommunication Company acquisition (multi-million dollar deal). Led Yahsat Government Solutions (YGS) 5-year strategy formation and implementation plan to achieve &gt;$600M in target gross revenue. Managed an overarching corporate PMO on multiple strategic projects, reporting directly to CEO and management, to deliver potentially multi-million dollar projects. Designed and supervised the automation of the performance management function through an in-house system, saving Yahsat $5M.","'CV Employee Work Experience'[CV Start Date]":"2018-01-01","'CV Employee Work Experience'[CV End Date]":"2019-04-30"},{"'CV Employee Work Experience'[CV Company Name]":"DEPARTMENT OF COMMUNITY DEVELOPMENT (DCD)","'CV Employee Work Experience'[CV Job Title]":"Strategic Planning and Performance Management Division Manager (Director)","'CV Employee Work Experience'[CV Responsibilities Summary]":"Acted as strategic partner for DCD leadership to ensure informed decision-making by driving special projects and strategic alignment of DCD and 11 social sector operators. Led the delivery of the 3-year (2019-2021) strategy and supervised the development of DCD and Abu Dhabi Social Sector Strategy 2.0 (2022-2025/2026). Drove strategic alignment of 15 thematic strategies and frameworks in the Social Sector to realize social outcomes. Spearheaded the 20-year Abu Dhabi Government Social Sector Strategy with internal and external stakeholders, resulting in a defined 20-year social agenda and 5-year execution plan. Established the strategy planning office, process, and function by designing and launching the Strategy Planning TOM, processes, and interaction framework. Established the performance management function by designing, creating, and launching procedures, TOM, processes, framework, and tools including Balanced Scorecard, analytics project management tool, and Program Management Office (PMO). Established and implemented risk management and business continuity, supervising the design and implementation of DCD Enterprise Risk policies, governance, and Social Sector assessment. Supervised Business Continuity assurance during COVID-19 pandemic. Identified social priority topics for awareness campaigns based on analysis of social challenges raised by COVID-19, created framework to identify short-term, medium- and long-term challenges and opportunities, and identified required policy interventions. Designed the Social Innovation division activation plan and supervised provisioning of intervention proposals with proof of concepts, speakers’ series, and targeted objectives. From Nov 2021 – Acting Executive Director Office of Strategic Affairs, supervising and advising DCD leadership on strategic planning, performance management, risk management, business continuity, strategic communication, and organizational development and excellence.","'CV Employee Work Experience'[CV Start Date]":"2019-04-01","'CV Employee Work Experience'[CV End Date]":""}]</v>
+        <v>[{"CV Employee Work Experience[CV Company Name]":"YAHSAT","CV Employee Work Experience[CV Job Title]":"MENA Region and International Accounts Business Development Officer","CV Employee Work Experience[CV Responsibilities Summary]":"Elevated Yahsat regional brand awareness; assisted in appointment of &gt;25 Service Partners across 27 countries. Formed successful relationships with regional business partners, large enterprises and government authorities; resulted in 150% client database growth. Produced MENA region business development strategy and steered marketing research initiatives; ensured 70% of commitment before satellite launch. Contributed in setting up Service Partner Service Agreement to secure company's commercial assets of &gt;$400Mn. Acted as Deputy Chairman of Social Committee with $50,000 budget to enhance corporate citizenship and increased employee engagement.","CV Employee Work Experience[CV Start Date]":"2008-04-01","CV Employee Work Experience[CV End Date]":"2010-12-31"},{"CV Employee Work Experience[CV Company Name]":"YAHSAT","CV Employee Work Experience[CV Job Title]":"MENA Region and International Accounts Country Manager","CV Employee Work Experience[CV Responsibilities Summary]":"Managed &gt;10 Service Partners in 13 MENA &amp; Asia countries with an average commitment of ~$3.5Mn before satellite launch. Designed solutions for MENA governments and ministries to roll-out national broadband projects (&gt;2Mn) and ICT fund investments to connect schools and hospitals. Created detailed Go-to-Market strategy and executed service launch and operations in 6 MENA countries, along with NGO initiatives with UN &amp; other entities. Conducted economic and financial analysis and customized business cases for enterprise and government accounts on behalf of &gt;10 Service Partners to maximize profitability. Implemented marketing tactics and realized opportunities within regional governmental authorities, Oil &amp; Gas, Banks &amp; NGOs for nationwide projects to evaluate P&amp;L trade-offs. Increased corporate social responsibility and corporate citizenship by chairing Social Committee and a team of 15 seniors with budget of $100,000.","CV Employee Work Experience[CV Start Date]":"2011-01-01","CV Employee Work Experience[CV End Date]":"2012-12-31"},{"CV Employee Work Experience[CV Company Name]":"YAHSAT","CV Employee Work Experience[CV Job Title]":"Strategy and Business Development Associate","CV Employee Work Experience[CV Responsibilities Summary]":"Supervised strategic management and planning services to establish and align UAE Space Agency with UAE's economy vision, secured $13Mn consultancy project. Collaborated with CEO, Senior Management and Board of Directors to create strategic analysis &amp; actions mandate to enhance operations efficiencies &amp; revenue growth &gt;$1bn. Directed business &amp; development analysis and recommendations to CEO &amp; third parties; resulted in partnerships, procurement &amp; academic program (~$4Mn). Restructured corporate and departmental objectives for 200 employees; directed Performance Management activities (e.g. BSC and CPMS) for corporate strategy execution.","CV Employee Work Experience[CV Start Date]":"2013-01-01","CV Employee Work Experience[CV End Date]":"2015-12-31"},{"CV Employee Work Experience[CV Company Name]":"YAHSAT","CV Employee Work Experience[CV Job Title]":"Strategy and Business Development Manager","CV Employee Work Experience[CV Responsibilities Summary]":"Conducted market research and social and economic analysis for UAE's governmental space investments and related global projects (&gt; $1bn cumulative). Organized and managed Program Management Office of third satellite manufacturing project (~$300Mn), overseeing &gt;10 work streams and &gt;50 employees. Developed program management policies and processes for a government confidential project (worth ~$1.5Bn). Supported in closing &gt;$150Mn revenue contract for Yahsat. Spearheaded investments and partnership opportunities' feasibility studies, valuation models construction, and new business models propositions to grow profit margins.","CV Employee Work Experience[CV Start Date]":"2015-01-01","CV Employee Work Experience[CV End Date]":"2017-12-31"},{"CV Employee Work Experience[CV Company Name]":"AL YAH SATELLITE COMMUNICATION COMPANY (YAHSAT)","CV Employee Work Experience[CV Job Title]":"Strategy and Business Development Associate Vice President (AVP)","CV Employee Work Experience[CV Responsibilities Summary]":"Led the pre- and post-merger integration office set up and planning exercise for Thuraya Telecommunication Company, including operational readiness, synergies identification, value capture plan development, day-1 readiness, and governance establishment. Supported valuation and due diligence of Thuraya Telecommunication Company acquisition (multi-million dollar deal). Led Yahsat Government Solutions (YGS) 5-year strategy formation and implementation plan to achieve &gt;$600M in target gross revenue. Managed an overarching corporate PMO on multiple strategic projects, reporting directly to CEO and management, to deliver potentially multi-million dollar projects. Designed and supervised the automation of the performance management function through an in-house system, saving Yahsat $5M.","CV Employee Work Experience[CV Start Date]":"2018-01-01","CV Employee Work Experience[CV End Date]":"2019-04-30"},{"CV Employee Work Experience[CV Company Name]":"DEPARTMENT OF COMMUNITY DEVELOPMENT (DCD)","CV Employee Work Experience[CV Job Title]":"Strategic Planning and Performance Management Division Manager (Director)","CV Employee Work Experience[CV Responsibilities Summary]":"Acted as strategic partner for DCD leadership to ensure informed decision-making by driving special projects and strategic alignment of DCD and 11 social sector operators. Led the delivery of the 3-year (2019-2021) strategy and supervised the development of DCD and Abu Dhabi Social Sector Strategy 2.0 (2022-2025/2026). Drove strategic alignment of 15 thematic strategies and frameworks in the Social Sector to realize social outcomes. Spearheaded the 20-year Abu Dhabi Government Social Sector Strategy with internal and external stakeholders, resulting in a defined 20-year social agenda and 5-year execution plan. Established the strategy planning office, process, and function by designing and launching the Strategy Planning TOM, processes, and interaction framework. Established the performance management function by designing, creating, and launching procedures, TOM, processes, framework, and tools including Balanced Scorecard, analytics project management tool, and Program Management Office (PMO). Established and implemented risk management and business continuity, supervising the design and implementation of DCD Enterprise Risk policies, governance, and Social Sector assessment. Supervised Business Continuity assurance during COVID-19 pandemic. Identified social priority topics for awareness campaigns based on analysis of social challenges raised by COVID-19, created framework to identify short-term, medium- and long-term challenges and opportunities, and identified required policy interventions. Designed the Social Innovation division activation plan and supervised provisioning of intervention proposals with proof of concepts, speakers’ series, and targeted objectives. From Nov 2021 – Acting Executive Director Office of Strategic Affairs, supervising and advising DCD leadership on strategic planning, performance management, risk management, business continuity, strategic communication, and organizational development and excellence.","CV Employee Work Experience[CV Start Date]":"2019-04-01","CV Employee Work Experience[CV End Date]":""}]</v>
       </c>
       <c r="BD6" t="str">
         <v>Sara A. Alharbi is a seasoned strategic leader with 17.8 years of experience driving performance management and business development across public and private sectors. She has held senior roles at YAHSAT and the Department of Community Development, excelling in strategic planning, risk management, and establishing strategic partnerships. A holder of an Executive MBA from London Business School, she has completed executive education in strategic management and inspirational leadership, and participated in an international exchange program.</v>
@@ -1548,7 +1548,7 @@
         <v>0</v>
       </c>
       <c r="AN7" t="str">
-        <v>[{"'CV Employee Competencies'[Technical Competency Name]":"Artificial Intelligence"},{"'CV Employee Competencies'[Technical Competency Name]":"English"},{"'CV Employee Competencies'[Technical Competency Name]":"Arabic"},{"'CV Employee Competencies'[Technical Competency Name]":"Biotechnology"},{"'CV Employee Competencies'[Technical Competency Name]":"Mural"},{"'CV Employee Competencies'[Technical Competency Name]":"Data Analysis and Reporting"},{"'CV Employee Competencies'[Technical Competency Name]":"Microsoft Excel"},{"'CV Employee Competencies'[Technical Competency Name]":"Project Management"},{"'CV Employee Competencies'[Technical Competency Name]":"Project Management Office (PMO)"},{"'CV Employee Competencies'[Technical Competency Name]":"Stakeholder Management"},{"'CV Employee Competencies'[Technical Competency Name]":"Team Leadership"},{"'CV Employee Competencies'[Technical Competency Name]":"Change Management"},{"'CV Employee Competencies'[Technical Competency Name]":"Process Mapping"},{"'CV Employee Competencies'[Technical Competency Name]":"Workshop Facilitation"},{"'CV Employee Competencies'[Technical Competency Name]":"Coaching and Mentoring"},{"'CV Employee Competencies'[Technical Competency Name]":"RFP Development"},{"'CV Employee Competencies'[Technical Competency Name]":"Operating Model Design"},{"'CV Employee Competencies'[Technical Competency Name]":"Healthcare Strategy"},{"'CV Employee Competencies'[Technical Competency Name]":"Leadership"}]</v>
+        <v>[{"CV Employee Competencies[Technical Competency Name]":"Artificial Intelligence"},{"CV Employee Competencies[Technical Competency Name]":"English"},{"CV Employee Competencies[Technical Competency Name]":"Arabic"},{"CV Employee Competencies[Technical Competency Name]":"Biotechnology"},{"CV Employee Competencies[Technical Competency Name]":"Mural"},{"CV Employee Competencies[Technical Competency Name]":"Data Analysis and Reporting"},{"CV Employee Competencies[Technical Competency Name]":"Microsoft Excel"},{"CV Employee Competencies[Technical Competency Name]":"Project Management"},{"CV Employee Competencies[Technical Competency Name]":"Project Management Office (PMO)"},{"CV Employee Competencies[Technical Competency Name]":"Stakeholder Management"},{"CV Employee Competencies[Technical Competency Name]":"Team Leadership"},{"CV Employee Competencies[Technical Competency Name]":"Change Management"},{"CV Employee Competencies[Technical Competency Name]":"Process Mapping"},{"CV Employee Competencies[Technical Competency Name]":"Workshop Facilitation"},{"CV Employee Competencies[Technical Competency Name]":"Coaching and Mentoring"},{"CV Employee Competencies[Technical Competency Name]":"RFP Development"},{"CV Employee Competencies[Technical Competency Name]":"Operating Model Design"},{"CV Employee Competencies[Technical Competency Name]":"Healthcare Strategy"},{"CV Employee Competencies[Technical Competency Name]":"Leadership"}]</v>
       </c>
       <c r="AO7" t="str">
         <v>[]</v>
@@ -1557,7 +1557,7 @@
         <v>[]</v>
       </c>
       <c r="AQ7" t="str">
-        <v>[{"'CV Employee Achievements and Awards'[CV Title]":"Client Centricity: Best Client Experience 2021","'CV Employee Achievements and Awards'[CV Achievement Description]":"","'CV Employee Achievements and Awards'[CV Issue Date]":"2021-01-01"},{"'CV Employee Achievements and Awards'[CV Title]":"Shukran Stars","'CV Employee Achievements and Awards'[CV Achievement Description]":"Awarded for exceptional contribution in four engagements (2019, 2020, 2021, 2022)","'CV Employee Achievements and Awards'[CV Issue Date]":"2019-01-01"},{"'CV Employee Achievements and Awards'[CV Title]":"Al Maktoum training program in leadership and globalization","'CV Employee Achievements and Awards'[CV Achievement Description]":"Accredited by the Scottish Qualification Authority","'CV Employee Achievements and Awards'[CV Issue Date]":"2018-01-01"}]</v>
+        <v>[{"CV Employee Achievements and Awards[CV Title]":"Client Centricity: Best Client Experience 2021","CV Employee Achievements and Awards[CV Achievement Description]":"","CV Employee Achievements and Awards[CV Issue Date]":"2021-01-01"},{"CV Employee Achievements and Awards[CV Title]":"Shukran Stars","CV Employee Achievements and Awards[CV Achievement Description]":"Awarded for exceptional contribution in four engagements (2019, 2020, 2021, 2022)","CV Employee Achievements and Awards[CV Issue Date]":"2019-01-01"},{"CV Employee Achievements and Awards[CV Title]":"Al Maktoum training program in leadership and globalization","CV Employee Achievements and Awards[CV Achievement Description]":"Accredited by the Scottish Qualification Authority","CV Employee Achievements and Awards[CV Issue Date]":"2018-01-01"}]</v>
       </c>
       <c r="AR7" t="str">
         <v>[]</v>
@@ -1575,19 +1575,19 @@
         <v/>
       </c>
       <c r="AY7" t="str">
-        <v>[{"'Employee Qualification'[Qualification Title]":"Bachelor of Science in Biotechnology","'Employee Qualification'[Educational Institute]":"University of Sharjah, UAE","'Employee Qualification'[GPA (Grade Point Average)]":"3.07","'Employee Qualification'[Study Start Date]":"","'Employee Qualification'[Study End Date]":"2018-01-09"}]</v>
+        <v>[{"Employee Qualification[Qualification Title]":"Bachelor of Science in Biotechnology","Employee Qualification[Educational Institute]":"University of Sharjah, UAE","Employee Qualification[GPA (Grade Point Average)]":"3.07","Employee Qualification[Study Start Date]":"","Employee Qualification[Study End Date]":"2018-01-09"}]</v>
       </c>
       <c r="AZ7" t="str">
-        <v>[{"'CV Employee Education'[CV Institution Name]":"University of Sharjah","'CV Employee Education'[CV Degree Name]":"Bachelor of Science in Biotechnology","'CV Employee Education'[CV Start Date]":"2014-01-01","'CV Employee Education'[CV End Date]":"2018-12-31"}]</v>
+        <v>[{"CV Employee Education[CV Institution Name]":"University of Sharjah","CV Employee Education[CV Degree Name]":"Bachelor of Science in Biotechnology","CV Employee Education[CV Start Date]":"2014-01-01","CV Employee Education[CV End Date]":"2018-12-31"}]</v>
       </c>
       <c r="BA7" t="str">
-        <v>[{"'Employee Assignment History'[Assignment Name]":"Senior Specialist","'Employee Assignment History'[Position Title]":"Senior Specialist, Health","'Employee Assignment History'[Employee Grade]":"3B","'Employee Assignment History'[Assignment Start Date]":"2024-11-26","'Employee Assignment History'[Assignment End Date]":"2025-07-31","'Employee Assignment History'[Assignment Experience (Years &amp; Months)]":"0 Years, 8 Months"},{"'Employee Assignment History'[Assignment Name]":"Senior Specialist, Health","'Employee Assignment History'[Position Title]":"Senior Specialist, Health","'Employee Assignment History'[Employee Grade]":"3B","'Employee Assignment History'[Assignment Start Date]":"2025-08-01","'Employee Assignment History'[Assignment End Date]":"","'Employee Assignment History'[Assignment Experience (Years &amp; Months)]":""}]</v>
+        <v>[{"Employee Assignment History[Assignment Name]":"Senior Specialist","Employee Assignment History[Position Title]":"Senior Specialist, Health","Employee Assignment History[Employee Grade]":"3B","Employee Assignment History[Assignment Start Date]":"2024-11-26","Employee Assignment History[Assignment End Date]":"2025-07-31","Employee Assignment History[Assignment Experience (Years &amp; Months)]":"0 Years, 8 Months"},{"Employee Assignment History[Assignment Name]":"Senior Specialist, Health","Employee Assignment History[Position Title]":"Senior Specialist, Health","Employee Assignment History[Employee Grade]":"3B","Employee Assignment History[Assignment Start Date]":"2025-08-01","Employee Assignment History[Assignment End Date]":"","Employee Assignment History[Assignment Experience (Years &amp; Months)]":""}]</v>
       </c>
       <c r="BB7" t="str">
         <v>[]</v>
       </c>
       <c r="BC7" t="str">
-        <v>[{"'CV Employee Work Experience'[CV Company Name]":"Ernest and Young","'CV Employee Work Experience'[CV Job Title]":"Assistant Manager","'CV Employee Work Experience'[CV Responsibilities Summary]":"Awarded four Shukran Stars for exceptional contribution in four engagements (2019, 2020, 2021, 2022). Awarded EY EMEIA (Europe-Middle East-India and Africa) 'Client Centricity: Best Client Experience 2021' Award. Supported in response development for RFPs (Request for Proposal). Engaged in learning and development activities such as exercise facilitation for a two-day Healthcare Consulting Academy. Set up and ran an Enterprise Project Management Office for a major healthcare sector transformation initiative. Led the current state assessment phase and provided evidence-based recommendations, supported by SMEs input. Led interviews with clients' leadership, senior management, and operational staff. Supported in the Project Management Office (PMO) and rolled out relevant tools and processes. Managed the development of the team members though on-the-job coaching on project management, stakeholder management, and MS office. Led program delivery in 6 medical facilities, and managed stakeholders ranging from c-suite to operational staff and ensured the buy in of the clients and their continuous involvement in the program. Identified areas for improvement and optimization by process mapping and utilizing industry experts and EY global network to implement best practices in healthcare. Supported the client in the initiation and management of over 30 improvement projects over the course of 12 months. Developed support material such as videos, pictorials, and processing forms to support the clients in navigating the improvement projects. Designed and ran workshops and coaching sessions for client teams. Established the workflow approach for smart meter operation and maintenance procedures development. Oversaw the output of four vendors totaling over 100 procedures and consulted with subject matter experts to verify the content. Managed the relationship between the client and the vendors and sustained a clear communication line. Supported junior team members though coaching on data analysis, story boarding, and project management.","'CV Employee Work Experience'[CV Start Date]":"2018-09-01","'CV Employee Work Experience'[CV End Date]":"2022-08-31"},{"'CV Employee Work Experience'[CV Company Name]":"PricewaterhouseCoopers","'CV Employee Work Experience'[CV Job Title]":"Manager","'CV Employee Work Experience'[CV Responsibilities Summary]":"Leading and directing teams to deliver on scope of work, which includes the development of strategies, operating models, benchmarking, etc. Responsible for monitoring project budgets. Developed strong skills in stakeholder management across all levels (c-suit to mid-level to operational) to ensure buy-in and maintain client engagement. Led and supported in response development for RFPs (Request for Proposal) for key health entities within the GCC. Responsible for directing the work of junior colleagues and overseeing the quality of work. Led the team in development of deliverables ranging from current state assessment, benchmarking, workforce analysis, strategy, operating model, and others. Designed the strategy of the localization of healthcare resources in the private sector, which required the close alignment of 20+ entities across the health ecosystem and outside of it as well. Designed the operating model for the entity in alignment with newly developed strategy, and optimized operations. Built strong relationships with client based on trust and reliability and was the main point of contact for the client. Responsible for the day-to-day planning and management of the project, client interaction, identifying and mitigating risks and issues, management of ad-hoc requests, and development of junior team members. Responsible for the successful delivery of the project and being the main point of contact to the client. Managed the team and led key phases of the project including the current state assessment (interviews across the organization, data and document analysis, and process mapping), and target state design. Designed a target operating model fit for the objectives and vision of the department and organization, which included a revised organizational structure, roles and responsibilities, processes, KPIs, governance, tools, templates, and an implementation roadmap. Designed and ran workshops for the client teams across the company to socialize the new operating model, in addition to running training sessions to enable the client team to successfully implement the operating model. Incorporated change management principles in the approach to the client to provide them with the necessary tools for them to lead the change. Managed the development of the team members though on-the-job coaching regarding technical and soft skills.","'CV Employee Work Experience'[CV Start Date]":"2022-08-01","'CV Employee Work Experience'[CV End Date]":""}]</v>
+        <v>[{"CV Employee Work Experience[CV Company Name]":"Ernest and Young","CV Employee Work Experience[CV Job Title]":"Assistant Manager","CV Employee Work Experience[CV Responsibilities Summary]":"Awarded four Shukran Stars for exceptional contribution in four engagements (2019, 2020, 2021, 2022). Awarded EY EMEIA (Europe-Middle East-India and Africa) 'Client Centricity: Best Client Experience 2021' Award. Supported in response development for RFPs (Request for Proposal). Engaged in learning and development activities such as exercise facilitation for a two-day Healthcare Consulting Academy. Set up and ran an Enterprise Project Management Office for a major healthcare sector transformation initiative. Led the current state assessment phase and provided evidence-based recommendations, supported by SMEs input. Led interviews with clients' leadership, senior management, and operational staff. Supported in the Project Management Office (PMO) and rolled out relevant tools and processes. Managed the development of the team members though on-the-job coaching on project management, stakeholder management, and MS office. Led program delivery in 6 medical facilities, and managed stakeholders ranging from c-suite to operational staff and ensured the buy in of the clients and their continuous involvement in the program. Identified areas for improvement and optimization by process mapping and utilizing industry experts and EY global network to implement best practices in healthcare. Supported the client in the initiation and management of over 30 improvement projects over the course of 12 months. Developed support material such as videos, pictorials, and processing forms to support the clients in navigating the improvement projects. Designed and ran workshops and coaching sessions for client teams. Established the workflow approach for smart meter operation and maintenance procedures development. Oversaw the output of four vendors totaling over 100 procedures and consulted with subject matter experts to verify the content. Managed the relationship between the client and the vendors and sustained a clear communication line. Supported junior team members though coaching on data analysis, story boarding, and project management.","CV Employee Work Experience[CV Start Date]":"2018-09-01","CV Employee Work Experience[CV End Date]":"2022-08-31"},{"CV Employee Work Experience[CV Company Name]":"PricewaterhouseCoopers","CV Employee Work Experience[CV Job Title]":"Manager","CV Employee Work Experience[CV Responsibilities Summary]":"Leading and directing teams to deliver on scope of work, which includes the development of strategies, operating models, benchmarking, etc. Responsible for monitoring project budgets. Developed strong skills in stakeholder management across all levels (c-suit to mid-level to operational) to ensure buy-in and maintain client engagement. Led and supported in response development for RFPs (Request for Proposal) for key health entities within the GCC. Responsible for directing the work of junior colleagues and overseeing the quality of work. Led the team in development of deliverables ranging from current state assessment, benchmarking, workforce analysis, strategy, operating model, and others. Designed the strategy of the localization of healthcare resources in the private sector, which required the close alignment of 20+ entities across the health ecosystem and outside of it as well. Designed the operating model for the entity in alignment with newly developed strategy, and optimized operations. Built strong relationships with client based on trust and reliability and was the main point of contact for the client. Responsible for the day-to-day planning and management of the project, client interaction, identifying and mitigating risks and issues, management of ad-hoc requests, and development of junior team members. Responsible for the successful delivery of the project and being the main point of contact to the client. Managed the team and led key phases of the project including the current state assessment (interviews across the organization, data and document analysis, and process mapping), and target state design. Designed a target operating model fit for the objectives and vision of the department and organization, which included a revised organizational structure, roles and responsibilities, processes, KPIs, governance, tools, templates, and an implementation roadmap. Designed and ran workshops for the client teams across the company to socialize the new operating model, in addition to running training sessions to enable the client team to successfully implement the operating model. Incorporated change management principles in the approach to the client to provide them with the necessary tools for them to lead the change. Managed the development of the team members though on-the-job coaching regarding technical and soft skills.","CV Employee Work Experience[CV Start Date]":"2022-08-01","CV Employee Work Experience[CV End Date]":""}]</v>
       </c>
       <c r="BD7" t="str">
         <v>Sara Alafeefi is a seasoned consulting professional with over seven years of experience delivering high-impact solutions at PricewaterhouseCoopers and Ernst &amp; Young. She excels in data analysis and reporting, with advanced proficiency in Microsoft Excel, project management, and PMO operations, alongside a strong track record in stakeholder engagement and change leadership. Recognized with the Client Centricity: Best Client Experience 2021 award and the Shukran Stars honor, she has also completed the prestigious Al Maktoum Leadership and Globalization training program. Holding a Bachelor of Science in Biotechnology from the University of Sharjah, Sara brings a unique analytical rigor to strategic consulting initiatives.</v>
@@ -1715,7 +1715,7 @@
         <v>0</v>
       </c>
       <c r="AN8" t="str">
-        <v>[{"'CV Employee Competencies'[Technical Competency Name]":"Arabic"},{"'CV Employee Competencies'[Technical Competency Name]":"English"},{"'CV Employee Competencies'[Technical Competency Name]":"French"},{"'CV Employee Competencies'[Technical Competency Name]":"HTML"},{"'CV Employee Competencies'[Technical Competency Name]":"CSS"},{"'CV Employee Competencies'[Technical Competency Name]":"JavaScript"},{"'CV Employee Competencies'[Technical Competency Name]":"Python"},{"'CV Employee Competencies'[Technical Competency Name]":"C++"},{"'CV Employee Competencies'[Technical Competency Name]":"Markdown"},{"'CV Employee Competencies'[Technical Competency Name]":"Interactive Media"},{"'CV Employee Competencies'[Technical Competency Name]":"Social Research"},{"'CV Employee Competencies'[Technical Competency Name]":"Public Policy"},{"'CV Employee Competencies'[Technical Competency Name]":"Recipe Development"},{"'CV Employee Competencies'[Technical Competency Name]":"Customer Service"},{"'CV Employee Competencies'[Technical Competency Name]":"Order Management"},{"'CV Employee Competencies'[Technical Competency Name]":"Delivery Coordination"},{"'CV Employee Competencies'[Technical Competency Name]":"Event Logistics"},{"'CV Employee Competencies'[Technical Competency Name]":"Multimedia Documentation"},{"'CV Employee Competencies'[Technical Competency Name]":"Interview Research"},{"'CV Employee Competencies'[Technical Competency Name]":"Field Research"},{"'CV Employee Competencies'[Technical Competency Name]":"Bibliographic Research"},{"'CV Employee Competencies'[Technical Competency Name]":"Translation and Localization"},{"'CV Employee Competencies'[Technical Competency Name]":"Insight Reporting"},{"'CV Employee Competencies'[Technical Competency Name]":"Program and Project Management"},{"'CV Employee Competencies'[Technical Competency Name]":"Reporting"},{"'CV Employee Competencies'[Technical Competency Name]":"Financial Modelling &amp; Forecasting"},{"'CV Employee Competencies'[Technical Competency Name]":"Mentorship"},{"'CV Employee Competencies'[Technical Competency Name]":"Digital Humanities"},{"'CV Employee Competencies'[Technical Competency Name]":"Workplace Communication"}]</v>
+        <v>[{"CV Employee Competencies[Technical Competency Name]":"Arabic"},{"CV Employee Competencies[Technical Competency Name]":"English"},{"CV Employee Competencies[Technical Competency Name]":"French"},{"CV Employee Competencies[Technical Competency Name]":"HTML"},{"CV Employee Competencies[Technical Competency Name]":"CSS"},{"CV Employee Competencies[Technical Competency Name]":"JavaScript"},{"CV Employee Competencies[Technical Competency Name]":"Python"},{"CV Employee Competencies[Technical Competency Name]":"C++"},{"CV Employee Competencies[Technical Competency Name]":"Markdown"},{"CV Employee Competencies[Technical Competency Name]":"Interactive Media"},{"CV Employee Competencies[Technical Competency Name]":"Social Research"},{"CV Employee Competencies[Technical Competency Name]":"Public Policy"},{"CV Employee Competencies[Technical Competency Name]":"Recipe Development"},{"CV Employee Competencies[Technical Competency Name]":"Customer Service"},{"CV Employee Competencies[Technical Competency Name]":"Order Management"},{"CV Employee Competencies[Technical Competency Name]":"Delivery Coordination"},{"CV Employee Competencies[Technical Competency Name]":"Event Logistics"},{"CV Employee Competencies[Technical Competency Name]":"Multimedia Documentation"},{"CV Employee Competencies[Technical Competency Name]":"Interview Research"},{"CV Employee Competencies[Technical Competency Name]":"Field Research"},{"CV Employee Competencies[Technical Competency Name]":"Bibliographic Research"},{"CV Employee Competencies[Technical Competency Name]":"Translation and Localization"},{"CV Employee Competencies[Technical Competency Name]":"Insight Reporting"},{"CV Employee Competencies[Technical Competency Name]":"Program and Project Management"},{"CV Employee Competencies[Technical Competency Name]":"Reporting"},{"CV Employee Competencies[Technical Competency Name]":"Financial Modelling &amp; Forecasting"},{"CV Employee Competencies[Technical Competency Name]":"Mentorship"},{"CV Employee Competencies[Technical Competency Name]":"Digital Humanities"},{"CV Employee Competencies[Technical Competency Name]":"Workplace Communication"}]</v>
       </c>
       <c r="AO8" t="str">
         <v>[]</v>
@@ -1724,7 +1724,7 @@
         <v>[]</v>
       </c>
       <c r="AQ8" t="str">
-        <v>[{"'CV Employee Achievements and Awards'[CV Title]":"Winter Institute in Digital Humanities","'CV Employee Achievements and Awards'[CV Achievement Description]":"Participant and panelist; enrolled in an Arabic Digital Humanities course to enhance expertise and apply the discipline to different languages","'CV Employee Achievements and Awards'[CV Issue Date]":"2024-01-16"},{"'CV Employee Achievements and Awards'[CV Title]":"Jusoor Program","'CV Employee Achievements and Awards'[CV Achievement Description]":"career guidance and training program; gained essential workplace communication skills, enhanced multitasking and project management efficiency, established a network for pursuing new opportunities and experiences","'CV Employee Achievements and Awards'[CV Issue Date]":"2022-04-03"},{"'CV Employee Achievements and Awards'[CV Title]":"Academic Enrichment Program (AEP) Ambassadors","'CV Employee Achievements and Awards'[CV Achievement Description]":"Mentor; assisted four mentors during their university transition, offering continuous support and guidance, resulting in their increased confidence in choosing majors and academic paths","'CV Employee Achievements and Awards'[CV Issue Date]":"2021-09-19"},{"'CV Employee Achievements and Awards'[CV Title]":"Fulbright Foreign Student Nominee","'CV Employee Achievements and Awards'[CV Achievement Description]":"","'CV Employee Achievements and Awards'[CV Issue Date]":""}]</v>
+        <v>[{"CV Employee Achievements and Awards[CV Title]":"Winter Institute in Digital Humanities","CV Employee Achievements and Awards[CV Achievement Description]":"Participant and panelist; enrolled in an Arabic Digital Humanities course to enhance expertise and apply the discipline to different languages","CV Employee Achievements and Awards[CV Issue Date]":"2024-01-16"},{"CV Employee Achievements and Awards[CV Title]":"Jusoor Program","CV Employee Achievements and Awards[CV Achievement Description]":"career guidance and training program; gained essential workplace communication skills, enhanced multitasking and project management efficiency, established a network for pursuing new opportunities and experiences","CV Employee Achievements and Awards[CV Issue Date]":"2022-04-03"},{"CV Employee Achievements and Awards[CV Title]":"Academic Enrichment Program (AEP) Ambassadors","CV Employee Achievements and Awards[CV Achievement Description]":"Mentor; assisted four mentors during their university transition, offering continuous support and guidance, resulting in their increased confidence in choosing majors and academic paths","CV Employee Achievements and Awards[CV Issue Date]":"2021-09-19"},{"CV Employee Achievements and Awards[CV Title]":"Fulbright Foreign Student Nominee","CV Employee Achievements and Awards[CV Achievement Description]":"","CV Employee Achievements and Awards[CV Issue Date]":""}]</v>
       </c>
       <c r="AR8" t="str">
         <v>[]</v>
@@ -1742,19 +1742,19 @@
         <v/>
       </c>
       <c r="AY8" t="str">
-        <v>[{"'Employee Qualification'[Qualification Title]":"Interactive Media","'Employee Qualification'[Educational Institute]":"New York University, Abu Dhabi","'Employee Qualification'[GPA (Grade Point Average)]":"3.86","'Employee Qualification'[Study Start Date]":"","'Employee Qualification'[Study End Date]":"2024-06-01"}]</v>
+        <v>[{"Employee Qualification[Qualification Title]":"Interactive Media","Employee Qualification[Educational Institute]":"New York University, Abu Dhabi","Employee Qualification[GPA (Grade Point Average)]":"3.86","Employee Qualification[Study Start Date]":"","Employee Qualification[Study End Date]":"2024-06-01"}]</v>
       </c>
       <c r="AZ8" t="str">
-        <v>[{"'CV Employee Education'[CV Institution Name]":"New York University","'CV Employee Education'[CV Degree Name]":"Bachelor's Degree","'CV Employee Education'[CV Start Date]":"2020-09-01","'CV Employee Education'[CV End Date]":"2024-05-31"}]</v>
+        <v>[{"CV Employee Education[CV Institution Name]":"New York University","CV Employee Education[CV Degree Name]":"Bachelor's Degree","CV Employee Education[CV Start Date]":"2020-09-01","CV Employee Education[CV End Date]":"2024-05-31"}]</v>
       </c>
       <c r="BA8" t="str">
-        <v>[{"'Employee Assignment History'[Assignment Name]":"Junior Specialist, Tourism","'Employee Assignment History'[Position Title]":"Junior Specialist, Tourism","'Employee Assignment History'[Employee Grade]":"4C","'Employee Assignment History'[Assignment Start Date]":"2025-02-04","'Employee Assignment History'[Assignment End Date]":"","'Employee Assignment History'[Assignment Experience (Years &amp; Months)]":""}]</v>
+        <v>[{"Employee Assignment History[Assignment Name]":"Junior Specialist, Tourism","Employee Assignment History[Position Title]":"Junior Specialist, Tourism","Employee Assignment History[Employee Grade]":"4C","Employee Assignment History[Assignment Start Date]":"2025-02-04","Employee Assignment History[Assignment End Date]":"","Employee Assignment History[Assignment Experience (Years &amp; Months)]":""}]</v>
       </c>
       <c r="BB8" t="str">
-        <v>[{"'Employee Previous Employer'[Previous Employer Name]":"Flaved Bakery","'Employee Previous Employer'[Previous Job Title]":"Founder and owner","'Employee Previous Employer'[Start Date]":"2024-03-30","'Employee Previous Employer'[End Date]":"2025-02-03"}]</v>
+        <v>[{"Employee Previous Employer[Previous Employer Name]":"Flaved Bakery","Employee Previous Employer[Previous Job Title]":"Founder and owner","Employee Previous Employer[Start Date]":"2024-03-30","Employee Previous Employer[End Date]":"2025-02-03"}]</v>
       </c>
       <c r="BC8" t="str">
-        <v>[{"'CV Employee Work Experience'[CV Company Name]":"Academic Enrichment Program (AEP) Ambassadors","'CV Employee Work Experience'[CV Job Title]":"Mentor","'CV Employee Work Experience'[CV Responsibilities Summary]":"Assisted four mentors during their university transition, offering continuous support and guidance, resulting in their increased confidence in choosing majors and academic paths.","'CV Employee Work Experience'[CV Start Date]":"2021-09-19","'CV Employee Work Experience'[CV End Date]":"2022-05-23"},{"'CV Employee Work Experience'[CV Company Name]":"Arts and Humanities Department","'CV Employee Work Experience'[CV Job Title]":"Research Assistant","'CV Employee Work Experience'[CV Responsibilities Summary]":"Verified location accuracy by cross-referencing textual descriptions. Conducted in-depth research on elusive place names not readily available online. Collaboratively maintained and updated extensive datasets, while generating informative blog-style reports and conducting bibliographic research in multiple languages.","'CV Employee Work Experience'[CV Start Date]":"2022-05-24","'CV Employee Work Experience'[CV End Date]":"2022-07-08"},{"'CV Employee Work Experience'[CV Company Name]":"Arts and Humanities Department","'CV Employee Work Experience'[CV Job Title]":"Research Assistant","'CV Employee Work Experience'[CV Responsibilities Summary]":"Conducted insightful interviews with the key subject of interest in collaboration with a visual artist professor. Assisted with translation tasks, facilitating effective communications in a multilingual context. Engaged in valuable field research to enhance the research objectives.","'CV Employee Work Experience'[CV Start Date]":"2023-06-04","'CV Employee Work Experience'[CV End Date]":"2023-08-29"},{"'CV Employee Work Experience'[CV Company Name]":"Office of Community-Based Learning (CBL)","'CV Employee Work Experience'[CV Job Title]":"Local Education Officer","'CV Employee Work Experience'[CV Responsibilities Summary]":"Managed logistical details for the class's off-campus engagements (including reservations) and aided guest lecturers. Provided comprehensive event support, including arranging admission tickets, equipment, and payments, while also carrying emergency contact information and coordinated with the assigned photographers. Captured images and videos of the engagements for CBL's social media.","'CV Employee Work Experience'[CV Start Date]":"2024-01-01","'CV Employee Work Experience'[CV End Date]":"2024-01-19"},{"'CV Employee Work Experience'[CV Company Name]":"Flaved Bakery","'CV Employee Work Experience'[CV Job Title]":"Founder and owner","'CV Employee Work Experience'[CV Responsibilities Summary]":"Developed unique gluten-free recipes, continuously innovate to meet customer preferences and dietary needs. Managed all incoming orders, ensuring accuracy and timely preparation for dispatch. Oversaw communications with customers, maintaining high standards of customer service and satisfaction. Coordinated with delivery personnel to ensure efficient and reliable delivery of orders. Created business models going over the different finances and projected growth potential.","'CV Employee Work Experience'[CV Start Date]":"2024-03-30","'CV Employee Work Experience'[CV End Date]":""}]</v>
+        <v>[{"CV Employee Work Experience[CV Company Name]":"Academic Enrichment Program (AEP) Ambassadors","CV Employee Work Experience[CV Job Title]":"Mentor","CV Employee Work Experience[CV Responsibilities Summary]":"Assisted four mentors during their university transition, offering continuous support and guidance, resulting in their increased confidence in choosing majors and academic paths.","CV Employee Work Experience[CV Start Date]":"2021-09-19","CV Employee Work Experience[CV End Date]":"2022-05-23"},{"CV Employee Work Experience[CV Company Name]":"Arts and Humanities Department","CV Employee Work Experience[CV Job Title]":"Research Assistant","CV Employee Work Experience[CV Responsibilities Summary]":"Verified location accuracy by cross-referencing textual descriptions. Conducted in-depth research on elusive place names not readily available online. Collaboratively maintained and updated extensive datasets, while generating informative blog-style reports and conducting bibliographic research in multiple languages.","CV Employee Work Experience[CV Start Date]":"2022-05-24","CV Employee Work Experience[CV End Date]":"2022-07-08"},{"CV Employee Work Experience[CV Company Name]":"Arts and Humanities Department","CV Employee Work Experience[CV Job Title]":"Research Assistant","CV Employee Work Experience[CV Responsibilities Summary]":"Conducted insightful interviews with the key subject of interest in collaboration with a visual artist professor. Assisted with translation tasks, facilitating effective communications in a multilingual context. Engaged in valuable field research to enhance the research objectives.","CV Employee Work Experience[CV Start Date]":"2023-06-04","CV Employee Work Experience[CV End Date]":"2023-08-29"},{"CV Employee Work Experience[CV Company Name]":"Office of Community-Based Learning (CBL)","CV Employee Work Experience[CV Job Title]":"Local Education Officer","CV Employee Work Experience[CV Responsibilities Summary]":"Managed logistical details for the class's off-campus engagements (including reservations) and aided guest lecturers. Provided comprehensive event support, including arranging admission tickets, equipment, and payments, while also carrying emergency contact information and coordinated with the assigned photographers. Captured images and videos of the engagements for CBL's social media.","CV Employee Work Experience[CV Start Date]":"2024-01-01","CV Employee Work Experience[CV End Date]":"2024-01-19"},{"CV Employee Work Experience[CV Company Name]":"Flaved Bakery","CV Employee Work Experience[CV Job Title]":"Founder and owner","CV Employee Work Experience[CV Responsibilities Summary]":"Developed unique gluten-free recipes, continuously innovate to meet customer preferences and dietary needs. Managed all incoming orders, ensuring accuracy and timely preparation for dispatch. Oversaw communications with customers, maintaining high standards of customer service and satisfaction. Coordinated with delivery personnel to ensure efficient and reliable delivery of orders. Created business models going over the different finances and projected growth potential.","CV Employee Work Experience[CV Start Date]":"2024-03-30","CV Employee Work Experience[CV End Date]":""}]</v>
       </c>
       <c r="BD8" t="str">
         <v>Nouf Ahmed Alnuaimi is a dynamic professional with nearly three years of diverse experience spanning entrepreneurship, education, and research. As founder of Flaved Bakery, she demonstrates advanced program and project management skills through end-to-end operations, while her roles as a Research Assistant and Local Education Officer highlight strong field research, interview techniques, and community engagement capabilities. A Fulbright Foreign Student Nominee and participant in the Winter Institute in Digital Humanities and Jusoor Program, she brings a multidisciplinary perspective shaped by her Bachelor’s in Interactive Media with a minor in Social Research and Public Policy from NYU.</v>
@@ -1879,13 +1879,13 @@
         <v>0</v>
       </c>
       <c r="AN9" t="str">
-        <v>[{"'CV Employee Competencies'[Technical Competency Name]":"Adaptable and reliable in dynamic environments"},{"'CV Employee Competencies'[Technical Competency Name]":"Strong attention to detail"},{"'CV Employee Competencies'[Technical Competency Name]":"Strong communication and delegation skills"},{"'CV Employee Competencies'[Technical Competency Name]":"Microsoft PowerPoint"},{"'CV Employee Competencies'[Technical Competency Name]":"Arabic"},{"'CV Employee Competencies'[Technical Competency Name]":"English"},{"'CV Employee Competencies'[Technical Competency Name]":"Survey Design"},{"'CV Employee Competencies'[Technical Competency Name]":"Qualitative Data Analysis"},{"'CV Employee Competencies'[Technical Competency Name]":"Applied Psychology"},{"'CV Employee Competencies'[Technical Competency Name]":"Contacts Drafting"},{"'CV Employee Competencies'[Technical Competency Name]":"Reporting"},{"'CV Employee Competencies'[Technical Competency Name]":"Data Analysis and Reporting"},{"'CV Employee Competencies'[Technical Competency Name]":"Project Advisory"},{"'CV Employee Competencies'[Technical Competency Name]":"Market Research"}]</v>
+        <v>[{"CV Employee Competencies[Technical Competency Name]":"Adaptable and reliable in dynamic environments"},{"CV Employee Competencies[Technical Competency Name]":"Strong attention to detail"},{"CV Employee Competencies[Technical Competency Name]":"Strong communication and delegation skills"},{"CV Employee Competencies[Technical Competency Name]":"Microsoft PowerPoint"},{"CV Employee Competencies[Technical Competency Name]":"Arabic"},{"CV Employee Competencies[Technical Competency Name]":"English"},{"CV Employee Competencies[Technical Competency Name]":"Survey Design"},{"CV Employee Competencies[Technical Competency Name]":"Qualitative Data Analysis"},{"CV Employee Competencies[Technical Competency Name]":"Applied Psychology"},{"CV Employee Competencies[Technical Competency Name]":"Contacts Drafting"},{"CV Employee Competencies[Technical Competency Name]":"Reporting"},{"CV Employee Competencies[Technical Competency Name]":"Data Analysis and Reporting"},{"CV Employee Competencies[Technical Competency Name]":"Project Advisory"},{"CV Employee Competencies[Technical Competency Name]":"Market Research"}]</v>
       </c>
       <c r="AO9" t="str">
         <v>[]</v>
       </c>
       <c r="AP9" t="str">
-        <v>[{"'CV Employee Interest and Hobbies'[CV Interest Name]":"Participation in Khazaf Fine Arts Studio workshops","'CV Employee Interest and Hobbies'[CV Interest Description]":"Assisted clients with tools and techniques during workshops; participated in the production and launching of project 0.2 (Liwa) merchandise"}]</v>
+        <v>[{"CV Employee Interest and Hobbies[CV Interest Name]":"Participation in Khazaf Fine Arts Studio workshops","CV Employee Interest and Hobbies[CV Interest Description]":"Assisted clients with tools and techniques during workshops; participated in the production and launching of project 0.2 (Liwa) merchandise"}]</v>
       </c>
       <c r="AQ9" t="str">
         <v>[]</v>
@@ -1906,19 +1906,19 @@
         <v/>
       </c>
       <c r="AY9" t="str">
-        <v>[{"'Employee Qualification'[Qualification Title]":"Applied Psychology","'Employee Qualification'[Educational Institute]":"Zayed University – Abu Dhabi","'Employee Qualification'[GPA (Grade Point Average)]":"3.93","'Employee Qualification'[Study Start Date]":"","'Employee Qualification'[Study End Date]":"2023-05-23"}]</v>
+        <v>[{"Employee Qualification[Qualification Title]":"Applied Psychology","Employee Qualification[Educational Institute]":"Zayed University – Abu Dhabi","Employee Qualification[GPA (Grade Point Average)]":"3.93","Employee Qualification[Study Start Date]":"","Employee Qualification[Study End Date]":"2023-05-23"}]</v>
       </c>
       <c r="AZ9" t="str">
-        <v>[{"'CV Employee Education'[CV Institution Name]":"Zayed University","'CV Employee Education'[CV Degree Name]":"BSc Applied Psychology","'CV Employee Education'[CV Start Date]":"","'CV Employee Education'[CV End Date]":"2023-05-31"}]</v>
+        <v>[{"CV Employee Education[CV Institution Name]":"Zayed University","CV Employee Education[CV Degree Name]":"BSc Applied Psychology","CV Employee Education[CV Start Date]":"","CV Employee Education[CV End Date]":"2023-05-31"}]</v>
       </c>
       <c r="BA9" t="str">
-        <v>[{"'Employee Assignment History'[Assignment Name]":"Specialist","'Employee Assignment History'[Position Title]":"Specialist, Special Projects","'Employee Assignment History'[Employee Grade]":"4B","'Employee Assignment History'[Assignment Start Date]":"2025-04-08","'Employee Assignment History'[Assignment End Date]":"2025-05-31","'Employee Assignment History'[Assignment Experience (Years &amp; Months)]":"0 Years, 1 Months"},{"'Employee Assignment History'[Assignment Name]":"Specialist","'Employee Assignment History'[Position Title]":"Specialist, Special Intervention","'Employee Assignment History'[Employee Grade]":"4B","'Employee Assignment History'[Assignment Start Date]":"2025-06-01","'Employee Assignment History'[Assignment End Date]":"2025-05-31","'Employee Assignment History'[Assignment Experience (Years &amp; Months)]":"0 Years, -1 Months"},{"'Employee Assignment History'[Assignment Name]":"Specialist, Special Intervention","'Employee Assignment History'[Position Title]":"Specialist, Special Intervention","'Employee Assignment History'[Employee Grade]":"4B","'Employee Assignment History'[Assignment Start Date]":"2025-06-01","'Employee Assignment History'[Assignment End Date]":"","'Employee Assignment History'[Assignment Experience (Years &amp; Months)]":""}]</v>
+        <v>[{"Employee Assignment History[Assignment Name]":"Specialist","Employee Assignment History[Position Title]":"Specialist, Special Projects","Employee Assignment History[Employee Grade]":"4B","Employee Assignment History[Assignment Start Date]":"2025-04-08","Employee Assignment History[Assignment End Date]":"2025-05-31","Employee Assignment History[Assignment Experience (Years &amp; Months)]":"0 Years, 1 Months"},{"Employee Assignment History[Assignment Name]":"Specialist","Employee Assignment History[Position Title]":"Specialist, Special Intervention","Employee Assignment History[Employee Grade]":"4B","Employee Assignment History[Assignment Start Date]":"2025-06-01","Employee Assignment History[Assignment End Date]":"2025-05-31","Employee Assignment History[Assignment Experience (Years &amp; Months)]":"0 Years, -1 Months"},{"Employee Assignment History[Assignment Name]":"Specialist, Special Intervention","Employee Assignment History[Position Title]":"Specialist, Special Intervention","Employee Assignment History[Employee Grade]":"4B","Employee Assignment History[Assignment Start Date]":"2025-06-01","Employee Assignment History[Assignment End Date]":"","Employee Assignment History[Assignment Experience (Years &amp; Months)]":""}]</v>
       </c>
       <c r="BB9" t="str">
-        <v>[{"'Employee Previous Employer'[Previous Employer Name]":"Strategy&amp; (Part of the PwC network)","'Employee Previous Employer'[Previous Job Title]":"Associate Consultant / Business Analyst","'Employee Previous Employer'[Start Date]":"2023-10-02","'Employee Previous Employer'[End Date]":"2025-04-01"}]</v>
+        <v>[{"Employee Previous Employer[Previous Employer Name]":"Strategy&amp; (Part of the PwC network)","Employee Previous Employer[Previous Job Title]":"Associate Consultant / Business Analyst","Employee Previous Employer[Start Date]":"2023-10-02","Employee Previous Employer[End Date]":"2025-04-01"}]</v>
       </c>
       <c r="BC9" t="str">
-        <v>[{"'CV Employee Work Experience'[CV Company Name]":"Abu Dhabi Executive Office","'CV Employee Work Experience'[CV Job Title]":"Intern","'CV Employee Work Experience'[CV Responsibilities Summary]":"Conducted benchmarking studies and best practice in research design and methodology. Conceptualized psychological theories related to behavior, cognition and identity. Tailored surveys and social experiments to focus groups and minorities. Archived and recoded qualitative data to derive insights. Participated in on-site visits to Abu Dhabi regions (Abu Dhabi city, Al Ain city and al Dhafra region) to gather data.","'CV Employee Work Experience'[CV Start Date]":"2023-01-01","'CV Employee Work Experience'[CV End Date]":"2023-07-01"},{"'CV Employee Work Experience'[CV Company Name]":"Strategy&amp; (Part of the PwC network)","'CV Employee Work Experience'[CV Job Title]":"Business Analyst","'CV Employee Work Experience'[CV Responsibilities Summary]":"Analyzed sector wide data to identify trends, patterns and derive valuable insights. Generated visual representations and process maps to illustrate business processes. Carried out market research studies in various industries (FS, TMT, GPS, EUR etc.). Created baseline reports and preliminary business models to derive recommendations. Provided overall team support on ad hoc tasks and general project management and execution tasks.","'CV Employee Work Experience'[CV Start Date]":"2023-10-01","'CV Employee Work Experience'[CV End Date]":"2024-10-01"},{"'CV Employee Work Experience'[CV Company Name]":"Strategy&amp; (Part of the PwC network)","'CV Employee Work Experience'[CV Job Title]":"Associate Consultant","'CV Employee Work Experience'[CV Responsibilities Summary]":"Contributed to the design and development of solutions tailored to client needs. Analyzed data and trends to support recommendations and decisions. Assisted in developing project plans, timelines, and deliverables.","'CV Employee Work Experience'[CV Start Date]":"2024-10-01","'CV Employee Work Experience'[CV End Date]":""}]</v>
+        <v>[{"CV Employee Work Experience[CV Company Name]":"Abu Dhabi Executive Office","CV Employee Work Experience[CV Job Title]":"Intern","CV Employee Work Experience[CV Responsibilities Summary]":"Conducted benchmarking studies and best practice in research design and methodology. Conceptualized psychological theories related to behavior, cognition and identity. Tailored surveys and social experiments to focus groups and minorities. Archived and recoded qualitative data to derive insights. Participated in on-site visits to Abu Dhabi regions (Abu Dhabi city, Al Ain city and al Dhafra region) to gather data.","CV Employee Work Experience[CV Start Date]":"2023-01-01","CV Employee Work Experience[CV End Date]":"2023-07-01"},{"CV Employee Work Experience[CV Company Name]":"Strategy&amp; (Part of the PwC network)","CV Employee Work Experience[CV Job Title]":"Business Analyst","CV Employee Work Experience[CV Responsibilities Summary]":"Analyzed sector wide data to identify trends, patterns and derive valuable insights. Generated visual representations and process maps to illustrate business processes. Carried out market research studies in various industries (FS, TMT, GPS, EUR etc.). Created baseline reports and preliminary business models to derive recommendations. Provided overall team support on ad hoc tasks and general project management and execution tasks.","CV Employee Work Experience[CV Start Date]":"2023-10-01","CV Employee Work Experience[CV End Date]":"2024-10-01"},{"CV Employee Work Experience[CV Company Name]":"Strategy&amp; (Part of the PwC network)","CV Employee Work Experience[CV Job Title]":"Associate Consultant","CV Employee Work Experience[CV Responsibilities Summary]":"Contributed to the design and development of solutions tailored to client needs. Analyzed data and trends to support recommendations and decisions. Assisted in developing project plans, timelines, and deliverables.","CV Employee Work Experience[CV Start Date]":"2024-10-01","CV Employee Work Experience[CV End Date]":""}]</v>
       </c>
       <c r="BD9" t="str">
         <v>Nouf Mohamed Abdullah Baadheem brings 2.8 years of consulting experience at Strategy&amp;, part of the PwC network, where she progressed from Business Analyst to Associate Consultant. She specializes in market research, survey design, and qualitative data analysis, supporting project advisory initiatives with strong data-driven reporting capabilities. Her foundational expertise in contacts drafting and reporting is complemented by a BSc in Applied Psychology from Zayed University, grounding her work in behavioral insights.</v>
@@ -2046,16 +2046,16 @@
         <v>0</v>
       </c>
       <c r="AN10" t="str">
-        <v>[{"'CV Employee Competencies'[Technical Competency Name]":"Client Relationship Management"},{"'CV Employee Competencies'[Technical Competency Name]":"Delegation"},{"'CV Employee Competencies'[Technical Competency Name]":"Creativity"},{"'CV Employee Competencies'[Technical Competency Name]":"Time Management"},{"'CV Employee Competencies'[Technical Competency Name]":"Interpersonal Skills"},{"'CV Employee Competencies'[Technical Competency Name]":"Effective Communication"},{"'CV Employee Competencies'[Technical Competency Name]":"Cross-Cultural Communication"},{"'CV Employee Competencies'[Technical Competency Name]":"International Affairs"},{"'CV Employee Competencies'[Technical Competency Name]":"Site Evaluation"},{"'CV Employee Competencies'[Technical Competency Name]":"Executive briefs and content development"},{"'CV Employee Competencies'[Technical Competency Name]":"Data Research and Analysis"},{"'CV Employee Competencies'[Technical Competency Name]":"Strategic Advisory"},{"'CV Employee Competencies'[Technical Competency Name]":"Accounts Management"},{"'CV Employee Competencies'[Technical Competency Name]":"Reporting"}]</v>
+        <v>[{"CV Employee Competencies[Technical Competency Name]":"Client Relationship Management"},{"CV Employee Competencies[Technical Competency Name]":"Delegation"},{"CV Employee Competencies[Technical Competency Name]":"Creativity"},{"CV Employee Competencies[Technical Competency Name]":"Time Management"},{"CV Employee Competencies[Technical Competency Name]":"Interpersonal Skills"},{"CV Employee Competencies[Technical Competency Name]":"Effective Communication"},{"CV Employee Competencies[Technical Competency Name]":"Cross-Cultural Communication"},{"CV Employee Competencies[Technical Competency Name]":"International Affairs"},{"CV Employee Competencies[Technical Competency Name]":"Site Evaluation"},{"CV Employee Competencies[Technical Competency Name]":"Executive briefs and content development"},{"CV Employee Competencies[Technical Competency Name]":"Data Research and Analysis"},{"CV Employee Competencies[Technical Competency Name]":"Strategic Advisory"},{"CV Employee Competencies[Technical Competency Name]":"Accounts Management"},{"CV Employee Competencies[Technical Competency Name]":"Reporting"}]</v>
       </c>
       <c r="AO10" t="str">
         <v>[]</v>
       </c>
       <c r="AP10" t="str">
-        <v>[{"'CV Employee Interest and Hobbies'[CV Interest Name]":"Football","'CV Employee Interest and Hobbies'[CV Interest Description]":"Assistant Coach for Zayed University Football Team"}]</v>
+        <v>[{"CV Employee Interest and Hobbies[CV Interest Name]":"Football","CV Employee Interest and Hobbies[CV Interest Description]":"Assistant Coach for Zayed University Football Team"}]</v>
       </c>
       <c r="AQ10" t="str">
-        <v>[{"'CV Employee Achievements and Awards'[CV Title]":"INNOVATION WORKSHOP","'CV Employee Achievements and Awards'[CV Achievement Description]":"","'CV Employee Achievements and Awards'[CV Issue Date]":"2015-01-01"},{"'CV Employee Achievements and Awards'[CV Title]":"ORGANIZER, ZU FESTIVAL &amp; NEPAL EARTHQUAKE FUNDRAISER","'CV Employee Achievements and Awards'[CV Achievement Description]":"","'CV Employee Achievements and Awards'[CV Issue Date]":"2015-01-01"},{"'CV Employee Achievements and Awards'[CV Title]":"INTERNATIONAL AFFAIRS SEMINAR","'CV Employee Achievements and Awards'[CV Achievement Description]":"","'CV Employee Achievements and Awards'[CV Issue Date]":"2014-01-01"},{"'CV Employee Achievements and Awards'[CV Title]":"CIT COMPUTER IT AND SYSTEMS COURSE","'CV Employee Achievements and Awards'[CV Achievement Description]":"","'CV Employee Achievements and Awards'[CV Issue Date]":"2011-01-01"}]</v>
+        <v>[{"CV Employee Achievements and Awards[CV Title]":"INNOVATION WORKSHOP","CV Employee Achievements and Awards[CV Achievement Description]":"","CV Employee Achievements and Awards[CV Issue Date]":"2015-01-01"},{"CV Employee Achievements and Awards[CV Title]":"ORGANIZER, ZU FESTIVAL &amp; NEPAL EARTHQUAKE FUNDRAISER","CV Employee Achievements and Awards[CV Achievement Description]":"","CV Employee Achievements and Awards[CV Issue Date]":"2015-01-01"},{"CV Employee Achievements and Awards[CV Title]":"INTERNATIONAL AFFAIRS SEMINAR","CV Employee Achievements and Awards[CV Achievement Description]":"","CV Employee Achievements and Awards[CV Issue Date]":"2014-01-01"},{"CV Employee Achievements and Awards[CV Title]":"CIT COMPUTER IT AND SYSTEMS COURSE","CV Employee Achievements and Awards[CV Achievement Description]":"","CV Employee Achievements and Awards[CV Issue Date]":"2011-01-01"}]</v>
       </c>
       <c r="AR10" t="str">
         <v>[]</v>
@@ -2073,19 +2073,19 @@
         <v/>
       </c>
       <c r="AY10" t="str">
-        <v>[{"'Employee Qualification'[Qualification Title]":"International Studies","'Employee Qualification'[Educational Institute]":"Zayed University","'Employee Qualification'[GPA (Grade Point Average)]":"2.48","'Employee Qualification'[Study Start Date]":"","'Employee Qualification'[Study End Date]":"2016-12-15"}]</v>
+        <v>[{"Employee Qualification[Qualification Title]":"International Studies","Employee Qualification[Educational Institute]":"Zayed University","Employee Qualification[GPA (Grade Point Average)]":"2.48","Employee Qualification[Study Start Date]":"","Employee Qualification[Study End Date]":"2016-12-15"}]</v>
       </c>
       <c r="AZ10" t="str">
-        <v>[{"'CV Employee Education'[CV Institution Name]":"International Academic School","'CV Employee Education'[CV Degree Name]":"High School Diploma","'CV Employee Education'[CV Start Date]":"2006-01-01","'CV Employee Education'[CV End Date]":"2010-06-30"},{"'CV Employee Education'[CV Institution Name]":"Zayed University","'CV Employee Education'[CV Degree Name]":"BA International Affairs","'CV Employee Education'[CV Start Date]":"2012-01-01","'CV Employee Education'[CV End Date]":"2016-12-31"}]</v>
+        <v>[{"CV Employee Education[CV Institution Name]":"International Academic School","CV Employee Education[CV Degree Name]":"High School Diploma","CV Employee Education[CV Start Date]":"2006-01-01","CV Employee Education[CV End Date]":"2010-06-30"},{"CV Employee Education[CV Institution Name]":"Zayed University","CV Employee Education[CV Degree Name]":"BA International Affairs","CV Employee Education[CV Start Date]":"2012-01-01","CV Employee Education[CV End Date]":"2016-12-31"}]</v>
       </c>
       <c r="BA10" t="str">
-        <v>[{"'Employee Assignment History'[Assignment Name]":"Senior Specialist, Agenda Management","'Employee Assignment History'[Position Title]":"Senior Specialist, Agenda Management","'Employee Assignment History'[Employee Grade]":"3B","'Employee Assignment History'[Assignment Start Date]":"2025-04-08","'Employee Assignment History'[Assignment End Date]":"","'Employee Assignment History'[Assignment Experience (Years &amp; Months)]":""}]</v>
+        <v>[{"Employee Assignment History[Assignment Name]":"Senior Specialist, Agenda Management","Employee Assignment History[Position Title]":"Senior Specialist, Agenda Management","Employee Assignment History[Employee Grade]":"3B","Employee Assignment History[Assignment Start Date]":"2025-04-08","Employee Assignment History[Assignment End Date]":"","Employee Assignment History[Assignment Experience (Years &amp; Months)]":""}]</v>
       </c>
       <c r="BB10" t="str">
-        <v>[{"'Employee Previous Employer'[Previous Employer Name]":"Crif Gulf","'Employee Previous Employer'[Previous Job Title]":"SENIOR EVALUATOR","'Employee Previous Employer'[Start Date]":"2017-12-04","'Employee Previous Employer'[End Date]":"2019-08-29"},{"'Employee Previous Employer'[Previous Employer Name]":"Shamal Military Solutions","'Employee Previous Employer'[Previous Job Title]":"ANALYST","'Employee Previous Employer'[Start Date]":"2021-07-04","'Employee Previous Employer'[End Date]":""}]</v>
+        <v>[{"Employee Previous Employer[Previous Employer Name]":"Crif Gulf","Employee Previous Employer[Previous Job Title]":"SENIOR EVALUATOR","Employee Previous Employer[Start Date]":"2017-12-04","Employee Previous Employer[End Date]":"2019-08-29"},{"Employee Previous Employer[Previous Employer Name]":"Shamal Military Solutions","Employee Previous Employer[Previous Job Title]":"ANALYST","Employee Previous Employer[Start Date]":"2021-07-04","Employee Previous Employer[End Date]":""}]</v>
       </c>
       <c r="BC10" t="str">
-        <v>[{"'CV Employee Work Experience'[CV Company Name]":"Crif Gulf","'CV Employee Work Experience'[CV Job Title]":"SENIOR EVALUATOR","'CV Employee Work Experience'[CV Responsibilities Summary]":"Evaluating and analyzing commercial establishments and companies. Creating and submitting reports.","'CV Employee Work Experience'[CV Start Date]":"2017-01-01","'CV Employee Work Experience'[CV End Date]":"2019-01-01"},{"'CV Employee Work Experience'[CV Company Name]":"Modon Properties","'CV Employee Work Experience'[CV Job Title]":"ACCOUNTS MANAGER","'CV Employee Work Experience'[CV Responsibilities Summary]":"Internship, managing client accounts. Visiting and evaluating the building sites.","'CV Employee Work Experience'[CV Start Date]":"2019-09-01","'CV Employee Work Experience'[CV End Date]":"2019-12-01"},{"'CV Employee Work Experience'[CV Company Name]":"Shamal Military Solutions","'CV Employee Work Experience'[CV Job Title]":"ANALYST","'CV Employee Work Experience'[CV Responsibilities Summary]":"Analyzing and studying confidential information. Providing consultations to decision-makers.","'CV Employee Work Experience'[CV Start Date]":"2021-01-01","'CV Employee Work Experience'[CV End Date]":""}]</v>
+        <v>[{"CV Employee Work Experience[CV Company Name]":"Crif Gulf","CV Employee Work Experience[CV Job Title]":"SENIOR EVALUATOR","CV Employee Work Experience[CV Responsibilities Summary]":"Evaluating and analyzing commercial establishments and companies. Creating and submitting reports.","CV Employee Work Experience[CV Start Date]":"2017-01-01","CV Employee Work Experience[CV End Date]":"2019-01-01"},{"CV Employee Work Experience[CV Company Name]":"Modon Properties","CV Employee Work Experience[CV Job Title]":"ACCOUNTS MANAGER","CV Employee Work Experience[CV Responsibilities Summary]":"Internship, managing client accounts. Visiting and evaluating the building sites.","CV Employee Work Experience[CV Start Date]":"2019-09-01","CV Employee Work Experience[CV End Date]":"2019-12-01"},{"CV Employee Work Experience[CV Company Name]":"Shamal Military Solutions","CV Employee Work Experience[CV Job Title]":"ANALYST","CV Employee Work Experience[CV Responsibilities Summary]":"Analyzing and studying confidential information. Providing consultations to decision-makers.","CV Employee Work Experience[CV Start Date]":"2021-01-01","CV Employee Work Experience[CV End Date]":""}]</v>
       </c>
       <c r="BD10" t="str">
         <v>Ali Alshamsi brings over seven years of cross-sector experience in financial analysis, accounts management, and strategic evaluation, having served at Shamal Military Solutions, Modon Properties, and Crif Gulf. He demonstrates strong proficiency in data research, reporting, and site evaluation, with a solid foundation in executive brief development and strategic advisory. Recognized for leadership in community initiatives, he organized the ZU Festival and Nepal Earthquake fundraiser, and completed the CIT Computer IT and Systems course. A graduate of Zayed University with a BA in International Affairs, he combines analytical rigor with a global perspective.</v>
@@ -2213,10 +2213,10 @@
         <v>0</v>
       </c>
       <c r="AN11" t="str">
-        <v>[{"'CV Employee Competencies'[Technical Competency Name]":"Arabic"},{"'CV Employee Competencies'[Technical Competency Name]":"English"},{"'CV Employee Competencies'[Technical Competency Name]":"Microsoft Windows"},{"'CV Employee Competencies'[Technical Competency Name]":"Microsoft Office"},{"'CV Employee Competencies'[Technical Competency Name]":"Critical thinking"},{"'CV Employee Competencies'[Technical Competency Name]":"Problem Solving"},{"'CV Employee Competencies'[Technical Competency Name]":"C#"},{"'CV Employee Competencies'[Technical Competency Name]":"JavaScript"},{"'CV Employee Competencies'[Technical Competency Name]":"HTML"},{"'CV Employee Competencies'[Technical Competency Name]":"CSS"},{"'CV Employee Competencies'[Technical Competency Name]":"jQuery"},{"'CV Employee Competencies'[Technical Competency Name]":"Economics"},{"'CV Employee Competencies'[Technical Competency Name]":"Social Sciences"},{"'CV Employee Competencies'[Technical Competency Name]":"English Language"},{"'CV Employee Competencies'[Technical Competency Name]":"Reporting"},{"'CV Employee Competencies'[Technical Competency Name]":"Data Research and Analysis"},{"'CV Employee Competencies'[Technical Competency Name]":"Strategic Insight Generation"},{"'CV Employee Competencies'[Technical Competency Name]":"Economic Analysis and Impact"},{"'CV Employee Competencies'[Technical Competency Name]":"Financial Modelling &amp; Forecasting"},{"'CV Employee Competencies'[Technical Competency Name]":"Economic &amp; Financial Analysis"},{"'CV Employee Competencies'[Technical Competency Name]":"Economic Data Analysis"},{"'CV Employee Competencies'[Technical Competency Name]":"Macroeconometric Modelling"},{"'CV Employee Competencies'[Technical Competency Name]":"Computable General Equilibrium Modelling"},{"'CV Employee Competencies'[Technical Competency Name]":"Human Resources Development Modelling"},{"'CV Employee Competencies'[Technical Competency Name]":"Economic Risk Assessment"},{"'CV Employee Competencies'[Technical Competency Name]":"Project Management"},{"'CV Employee Competencies'[Technical Competency Name]":"Stakeholder Engagement"},{"'CV Employee Competencies'[Technical Competency Name]":"Research Methodology"},{"'CV Employee Competencies'[Technical Competency Name]":"National Accounts"},{"'CV Employee Competencies'[Technical Competency Name]":"Econometric Theory"}]</v>
+        <v>[{"CV Employee Competencies[Technical Competency Name]":"Arabic"},{"CV Employee Competencies[Technical Competency Name]":"English"},{"CV Employee Competencies[Technical Competency Name]":"Microsoft Windows"},{"CV Employee Competencies[Technical Competency Name]":"Microsoft Office"},{"CV Employee Competencies[Technical Competency Name]":"Critical thinking"},{"CV Employee Competencies[Technical Competency Name]":"Problem Solving"},{"CV Employee Competencies[Technical Competency Name]":"C#"},{"CV Employee Competencies[Technical Competency Name]":"JavaScript"},{"CV Employee Competencies[Technical Competency Name]":"HTML"},{"CV Employee Competencies[Technical Competency Name]":"CSS"},{"CV Employee Competencies[Technical Competency Name]":"jQuery"},{"CV Employee Competencies[Technical Competency Name]":"Economics"},{"CV Employee Competencies[Technical Competency Name]":"Social Sciences"},{"CV Employee Competencies[Technical Competency Name]":"English Language"},{"CV Employee Competencies[Technical Competency Name]":"Reporting"},{"CV Employee Competencies[Technical Competency Name]":"Data Research and Analysis"},{"CV Employee Competencies[Technical Competency Name]":"Strategic Insight Generation"},{"CV Employee Competencies[Technical Competency Name]":"Economic Analysis and Impact"},{"CV Employee Competencies[Technical Competency Name]":"Financial Modelling &amp; Forecasting"},{"CV Employee Competencies[Technical Competency Name]":"Economic &amp; Financial Analysis"},{"CV Employee Competencies[Technical Competency Name]":"Economic Data Analysis"},{"CV Employee Competencies[Technical Competency Name]":"Macroeconometric Modelling"},{"CV Employee Competencies[Technical Competency Name]":"Computable General Equilibrium Modelling"},{"CV Employee Competencies[Technical Competency Name]":"Human Resources Development Modelling"},{"CV Employee Competencies[Technical Competency Name]":"Economic Risk Assessment"},{"CV Employee Competencies[Technical Competency Name]":"Project Management"},{"CV Employee Competencies[Technical Competency Name]":"Stakeholder Engagement"},{"CV Employee Competencies[Technical Competency Name]":"Research Methodology"},{"CV Employee Competencies[Technical Competency Name]":"National Accounts"},{"CV Employee Competencies[Technical Competency Name]":"Econometric Theory"}]</v>
       </c>
       <c r="AO11" t="str">
-        <v>[{"'Employee Competencies Rating'[Competancy Name]":"Leading Change","'Employee Competencies Rating'[Employee Rating]":"3","'Employee Competencies Rating'[Supervisor Rating]":"2","'Employee Competencies Rating'[Employee Rating Description]":"Solid Performer","'Employee Competencies Rating'[Supervisor Rating Description]":"Developing"},{"'Employee Competencies Rating'[Competancy Name]":"Learning Agility","'Employee Competencies Rating'[Employee Rating]":"2","'Employee Competencies Rating'[Supervisor Rating]":"3","'Employee Competencies Rating'[Employee Rating Description]":"Developing","'Employee Competencies Rating'[Supervisor Rating Description]":"Solid Performer"},{"'Employee Competencies Rating'[Competancy Name]":"Public Service Excellence","'Employee Competencies Rating'[Employee Rating]":"3","'Employee Competencies Rating'[Supervisor Rating]":"4","'Employee Competencies Rating'[Employee Rating Description]":"Solid Performer","'Employee Competencies Rating'[Supervisor Rating Description]":"Champion"},{"'Employee Competencies Rating'[Competancy Name]":"Digital Savviness","'Employee Competencies Rating'[Employee Rating]":"3","'Employee Competencies Rating'[Supervisor Rating]":"4","'Employee Competencies Rating'[Employee Rating Description]":"Solid Performer","'Employee Competencies Rating'[Supervisor Rating Description]":"Champion"},{"'Employee Competencies Rating'[Competancy Name]":"Results-Driven Outcomes","'Employee Competencies Rating'[Employee Rating]":"3","'Employee Competencies Rating'[Supervisor Rating]":"4","'Employee Competencies Rating'[Employee Rating Description]":"Solid Performer","'Employee Competencies Rating'[Supervisor Rating Description]":"Champion"},{"'Employee Competencies Rating'[Competancy Name]":"Critical Thinking and Data-Driven Decision Making","'Employee Competencies Rating'[Employee Rating]":"3","'Employee Competencies Rating'[Supervisor Rating]":"4","'Employee Competencies Rating'[Employee Rating Description]":"Solid Performer","'Employee Competencies Rating'[Supervisor Rating Description]":"Champion"},{"'Employee Competencies Rating'[Competancy Name]":"Intrapreneurship","'Employee Competencies Rating'[Employee Rating]":"3","'Employee Competencies Rating'[Supervisor Rating]":"2","'Employee Competencies Rating'[Employee Rating Description]":"Solid Performer","'Employee Competencies Rating'[Supervisor Rating Description]":"Developing"},{"'Employee Competencies Rating'[Competancy Name]":"Facilitates Collaboration and Influence","'Employee Competencies Rating'[Employee Rating]":"2","'Employee Competencies Rating'[Supervisor Rating]":"3","'Employee Competencies Rating'[Employee Rating Description]":"Developing","'Employee Competencies Rating'[Supervisor Rating Description]":"Solid Performer"}]</v>
+        <v>[{"Employee Competencies Rating[Competancy Name]":"Leading Change","Employee Competencies Rating[Employee Rating]":"3","Employee Competencies Rating[Supervisor Rating]":"2","Employee Competencies Rating[Employee Rating Description]":"Solid Performer","Employee Competencies Rating[Supervisor Rating Description]":"Developing"},{"Employee Competencies Rating[Competancy Name]":"Learning Agility","Employee Competencies Rating[Employee Rating]":"2","Employee Competencies Rating[Supervisor Rating]":"3","Employee Competencies Rating[Employee Rating Description]":"Developing","Employee Competencies Rating[Supervisor Rating Description]":"Solid Performer"},{"Employee Competencies Rating[Competancy Name]":"Public Service Excellence","Employee Competencies Rating[Employee Rating]":"3","Employee Competencies Rating[Supervisor Rating]":"4","Employee Competencies Rating[Employee Rating Description]":"Solid Performer","Employee Competencies Rating[Supervisor Rating Description]":"Champion"},{"Employee Competencies Rating[Competancy Name]":"Digital Savviness","Employee Competencies Rating[Employee Rating]":"3","Employee Competencies Rating[Supervisor Rating]":"4","Employee Competencies Rating[Employee Rating Description]":"Solid Performer","Employee Competencies Rating[Supervisor Rating Description]":"Champion"},{"Employee Competencies Rating[Competancy Name]":"Results-Driven Outcomes","Employee Competencies Rating[Employee Rating]":"3","Employee Competencies Rating[Supervisor Rating]":"4","Employee Competencies Rating[Employee Rating Description]":"Solid Performer","Employee Competencies Rating[Supervisor Rating Description]":"Champion"},{"Employee Competencies Rating[Competancy Name]":"Critical Thinking and Data-Driven Decision Making","Employee Competencies Rating[Employee Rating]":"3","Employee Competencies Rating[Supervisor Rating]":"4","Employee Competencies Rating[Employee Rating Description]":"Solid Performer","Employee Competencies Rating[Supervisor Rating Description]":"Champion"},{"Employee Competencies Rating[Competancy Name]":"Intrapreneurship","Employee Competencies Rating[Employee Rating]":"3","Employee Competencies Rating[Supervisor Rating]":"2","Employee Competencies Rating[Employee Rating Description]":"Solid Performer","Employee Competencies Rating[Supervisor Rating Description]":"Developing"},{"Employee Competencies Rating[Competancy Name]":"Facilitates Collaboration and Influence","Employee Competencies Rating[Employee Rating]":"2","Employee Competencies Rating[Supervisor Rating]":"3","Employee Competencies Rating[Employee Rating Description]":"Developing","Employee Competencies Rating[Supervisor Rating Description]":"Solid Performer"}]</v>
       </c>
       <c r="AP11" t="str">
         <v>[]</v>
@@ -2228,10 +2228,10 @@
         <v>[]</v>
       </c>
       <c r="AS11" t="str">
-        <v>[{"'Employee Performance'[Performance Review Period]":"2024 Review Period","'Employee Performance'[Calculated Rating]":"3.11","'Employee Performance'[Normalized Performance Rating]":"Meets Expectations"}]</v>
+        <v>[{"Employee Performance[Performance Review Period]":"2024 Review Period","Employee Performance[Calculated Rating]":"3.11","Employee Performance[Normalized Performance Rating]":"Meets Expectations"}]</v>
       </c>
       <c r="AT11" t="str">
-        <v>[{"'Employee Achievements'[Customary Name]":"2024 Annual Appraisal","'Employee Achievements'[Manager OA Comments]":"Salem has demonstrated strong performance in 2024, delivering high-quality outcomes in key cases such as the economic strategic review and real estate law. His critical thinking and digital savviness are commendable, enabling him to handle complex tasks effectively. However, there is room for growth in taking a more proactive approach to collaboration, initiating innovative solutions, and fully complying with ADEO policies. To excel in 2025, Salem should focus on enhancing his understanding of ADEO’s systems, independently managing cases, and proposing impactful initiatives. By leveraging his skills and adopting a results-driven mindset, he can significantly contribute to ADEO’s strategic objectives.","'Employee Achievements'[Employee OA Comments]":"I have demonstrated commitment to achieve my goals. I understand that there are areas of development that I can work on for the following year."}]</v>
+        <v>[{"Employee Achievements[Customary Name]":"2024 Annual Appraisal","Employee Achievements[Manager OA Comments]":"Salem has demonstrated strong performance in 2024, delivering high-quality outcomes in key cases such as the economic strategic review and real estate law. His critical thinking and digital savviness are commendable, enabling him to handle complex tasks effectively. However, there is room for growth in taking a more proactive approach to collaboration, initiating innovative solutions, and fully complying with ADEO policies. To excel in 2025, Salem should focus on enhancing his understanding of ADEO’s systems, independently managing cases, and proposing impactful initiatives. By leveraging his skills and adopting a results-driven mindset, he can significantly contribute to ADEO’s strategic objectives.","Employee Achievements[Employee OA Comments]":"I have demonstrated commitment to achieve my goals. I understand that there are areas of development that I can work on for the following year."}]</v>
       </c>
       <c r="AU11" t="str">
         <v>[]</v>
@@ -2240,19 +2240,19 @@
         <v/>
       </c>
       <c r="AY11" t="str">
-        <v>[{"'Employee Qualification'[Qualification Title]":"Bachelor of Science - Economics","'Employee Qualification'[Educational Institute]":"University of London Queen Marry and Westfield College","'Employee Qualification'[GPA (Grade Point Average)]":"","'Employee Qualification'[Study Start Date]":"2005-09-01","'Employee Qualification'[Study End Date]":"2009-07-09"}]</v>
+        <v>[{"Employee Qualification[Qualification Title]":"Bachelor of Science - Economics","Employee Qualification[Educational Institute]":"University of London Queen Marry and Westfield College","Employee Qualification[GPA (Grade Point Average)]":"","Employee Qualification[Study Start Date]":"2005-09-01","Employee Qualification[Study End Date]":"2009-07-09"}]</v>
       </c>
       <c r="AZ11" t="str">
-        <v>[{"'CV Employee Education'[CV Institution Name]":"Ras Al Khaimah High School","'CV Employee Education'[CV Degree Name]":"High School Certificate","'CV Employee Education'[CV Start Date]":"2000-01-01","'CV Employee Education'[CV End Date]":"2003-12-31"},{"'CV Employee Education'[CV Institution Name]":"Queen Mary, University of London","'CV Employee Education'[CV Degree Name]":"Intermediate Certificate in Social Sciences","'CV Employee Education'[CV Start Date]":"2004-01-01","'CV Employee Education'[CV End Date]":"2005-12-31"},{"'CV Employee Education'[CV Institution Name]":"Colchester English Study Centre","'CV Employee Education'[CV Degree Name]":"English Language Course","'CV Employee Education'[CV Start Date]":"2004-02-01","'CV Employee Education'[CV End Date]":"2004-06-30"},{"'CV Employee Education'[CV Institution Name]":"International House London","'CV Employee Education'[CV Degree Name]":"University Foundation Course","'CV Employee Education'[CV Start Date]":"2005-01-01","'CV Employee Education'[CV End Date]":"2006-12-31"},{"'CV Employee Education'[CV Institution Name]":"Queen Mary, University of London","'CV Employee Education'[CV Degree Name]":"Bachelor of Science in Economics","'CV Employee Education'[CV Start Date]":"2006-01-01","'CV Employee Education'[CV End Date]":"2009-12-31"}]</v>
+        <v>[{"CV Employee Education[CV Institution Name]":"Ras Al Khaimah High School","CV Employee Education[CV Degree Name]":"High School Certificate","CV Employee Education[CV Start Date]":"2000-01-01","CV Employee Education[CV End Date]":"2003-12-31"},{"CV Employee Education[CV Institution Name]":"Queen Mary, University of London","CV Employee Education[CV Degree Name]":"Intermediate Certificate in Social Sciences","CV Employee Education[CV Start Date]":"2004-01-01","CV Employee Education[CV End Date]":"2005-12-31"},{"CV Employee Education[CV Institution Name]":"Colchester English Study Centre","CV Employee Education[CV Degree Name]":"English Language Course","CV Employee Education[CV Start Date]":"2004-02-01","CV Employee Education[CV End Date]":"2004-06-30"},{"CV Employee Education[CV Institution Name]":"International House London","CV Employee Education[CV Degree Name]":"University Foundation Course","CV Employee Education[CV Start Date]":"2005-01-01","CV Employee Education[CV End Date]":"2006-12-31"},{"CV Employee Education[CV Institution Name]":"Queen Mary, University of London","CV Employee Education[CV Degree Name]":"Bachelor of Science in Economics","CV Employee Education[CV Start Date]":"2006-01-01","CV Employee Education[CV End Date]":"2009-12-31"}]</v>
       </c>
       <c r="BA11" t="str">
-        <v>[{"'Employee Assignment History'[Assignment Name]":"Assistant Advisor","'Employee Assignment History'[Position Title]":"Assistant Advisor, Economic Analysis","'Employee Assignment History'[Employee Grade]":"2B","'Employee Assignment History'[Assignment Start Date]":"2024-06-25","'Employee Assignment History'[Assignment End Date]":"2025-09-21","'Employee Assignment History'[Assignment Experience (Years &amp; Months)]":"1 Years, 3 Months"},{"'Employee Assignment History'[Assignment Name]":"Assistant Advisor, Economic Analysis","'Employee Assignment History'[Position Title]":"Assistant Advisor, Economic Analysis","'Employee Assignment History'[Employee Grade]":"2B","'Employee Assignment History'[Assignment Start Date]":"2025-09-22","'Employee Assignment History'[Assignment End Date]":"","'Employee Assignment History'[Assignment Experience (Years &amp; Months)]":""}]</v>
+        <v>[{"Employee Assignment History[Assignment Name]":"Assistant Advisor","Employee Assignment History[Position Title]":"Assistant Advisor, Economic Analysis","Employee Assignment History[Employee Grade]":"2B","Employee Assignment History[Assignment Start Date]":"2024-06-25","Employee Assignment History[Assignment End Date]":"2025-09-21","Employee Assignment History[Assignment Experience (Years &amp; Months)]":"1 Years, 3 Months"},{"Employee Assignment History[Assignment Name]":"Assistant Advisor, Economic Analysis","Employee Assignment History[Position Title]":"Assistant Advisor, Economic Analysis","Employee Assignment History[Employee Grade]":"2B","Employee Assignment History[Assignment Start Date]":"2025-09-22","Employee Assignment History[Assignment End Date]":"","Employee Assignment History[Assignment Experience (Years &amp; Months)]":""}]</v>
       </c>
       <c r="BB11" t="str">
-        <v>[{"'Employee Previous Employer'[Previous Employer Name]":"Abu Dhabi Council for Economic Development","'Employee Previous Employer'[Previous Job Title]":"Project Manager - economic policy planning","'Employee Previous Employer'[Start Date]":"2013-11-04","'Employee Previous Employer'[End Date]":"2020-12-31"}]</v>
+        <v>[{"Employee Previous Employer[Previous Employer Name]":"Abu Dhabi Council for Economic Development","Employee Previous Employer[Previous Job Title]":"Project Manager - economic policy planning","Employee Previous Employer[Start Date]":"2013-11-04","Employee Previous Employer[End Date]":"2020-12-31"}]</v>
       </c>
       <c r="BC11" t="str">
-        <v>[{"'CV Employee Work Experience'[CV Company Name]":"Department of Economic Development Abu Dhabi","'CV Employee Work Experience'[CV Job Title]":"Economic Researcher","'CV Employee Work Experience'[CV Responsibilities Summary]":"Member of the modelling team at the Department of Economic Development. Updating and maintaining the integrity of Abu Dhabi Macroeconometric model, Computable General Equilibrium model and Human Resources Development modelling system. Economic forecasting, policy analysis for short/mid/long term using variety of economic models and conducting case studies and analyzing the impact of different scenarios on Abu Dhabi economic variables. Preparing research overview and plan, to help recognize goals, methodologies, necessary tools and information sources most suitable for the topic at hand. Preparing progress reports throughout the research timeline and with accordance to the plan. Organizing data bank for the team and update it regularly to centralize and ease the access to necessary information when needed. Analyzing the forecasted growth of economic sectors and variables in Abu Dhabi and identifying reasons behind the forecast. Planning and organizing meetings and events related to ongoing or done research. Identifying the status of current and forecasted Abu Dhabi economy in accordance to Abu Dhabi Economic Vision 2030. Provide recommendations based on research and quantitative impact analysis outcome. Provide suggestions to help improve quality of the research and accuracy of outcome.","'CV Employee Work Experience'[CV Start Date]":"2010-12-01","'CV Employee Work Experience'[CV End Date]":"2013-10-31"},{"'CV Employee Work Experience'[CV Company Name]":"Abu Dhabi Department of Economic Development","'CV Employee Work Experience'[CV Job Title]":"Secondment at Abu Dhabi Department of Economic Development","'CV Employee Work Experience'[CV Responsibilities Summary]":"Handling modelling tasks including economic forecast for Abu Dhabi’s economy, scenario building and analysis. Conducting economic research based on tasks requested by Abu Dhabi Executive Council. Taking a lead role in developing Abu Dhabi Economic Risk Profile. Additionally, taking a significant role in initiating Economic Policy department within the research sector at ADDED through methodology development, stakeholders engagement and submitting white and policy papers.","'CV Employee Work Experience'[CV Start Date]":"2016-10-01","'CV Employee Work Experience'[CV End Date]":"2018-11-30"},{"'CV Employee Work Experience'[CV Company Name]":"Abu Dhabi Council for Economic Development","'CV Employee Work Experience'[CV Job Title]":"Project Manager","'CV Employee Work Experience'[CV Responsibilities Summary]":"Conducting economic research and analysis according to the plan set by Economic Policy Planning Division at the council or by request from higher management. Using the most suitable qualitative and quantitative research methodologies and reliable sources of information. Managing research projects and supporting Project Managers by getting the necessary approvals, setting project plan, setting deadlines, assigning responsibilities to the project team, setting internal and external meetings and delivering the final outcome with all supporting documents. Contributing to the development and implementation of procedures and processes which cater to all aspects of project management and review. Reviewing policies, legislations, papers and reports and provide recommendations. Proactive involvement in outreach workshops through engaging the private sector and liaising with stakeholders in the public sector. Preparing briefs and presentations for management and stakeholders and representing ADCED in international conferences and seminars.","'CV Employee Work Experience'[CV Start Date]":"2018-02-01","'CV Employee Work Experience'[CV End Date]":"2020-12-31"},{"'CV Employee Work Experience'[CV Company Name]":"Abu Dhabi Council for Economic Development","'CV Employee Work Experience'[CV Job Title]":"Acting Director – Economic Policy Planning Division","'CV Employee Work Experience'[CV Responsibilities Summary]":"Reviewing and setting up divisional strategic and operational plan and budget requirement for 2020 and aligning with entity mandate and the emirate’s three years plan. Setting individual development plans and training requirements for division staff and appraisal criteria. Preparing monthly division performance and presenting it to the Director General. Setting up tasks, success criteria and handing projects to work groups within the division, following up work progress and reviewing content and quality. Communicating project results and expectations between work groups and decision maker. Presenting ADCED in meetings and handling cooperation with other government entities. Collaborating with Abu Dhabi Department of Economic Development in setting up Abu Dhabi’s economic strategy 2021-2024.","'CV Employee Work Experience'[CV Start Date]":"2019-07-01","'CV Employee Work Experience'[CV End Date]":"2020-12-31"},{"'CV Employee Work Experience'[CV Company Name]":"Department of Economic Development Abu Dhabi","'CV Employee Work Experience'[CV Job Title]":"Team Leader / Acting Director of Economic Intelligence","'CV Employee Work Experience'[CV Responsibilities Summary]":"Setting up the structure and vision of an economic intelligence department to centralize and improve economic information within the newly formed strategy office at AD DED. Initiating the development of economic models to simulate different aspects of the economy to support economic strategies and policy initiatives. Building a decision support smart platform that includes all available economic information and utilizing both existing and new quantitative analysis tools.","'CV Employee Work Experience'[CV Start Date]":"2020-07-01","'CV Employee Work Experience'[CV End Date]":"2021-12-31"},{"'CV Employee Work Experience'[CV Company Name]":"Department of Economic Development Abu Dhabi","'CV Employee Work Experience'[CV Job Title]":"Acting Director of Economic Planning &amp; Performance","'CV Employee Work Experience'[CV Responsibilities Summary]":"Setting up 2022 EPP department plan and employees’ roles. Engaging stakeholder in initiatives’ proposal and implementations as part of AD Economic Strategy. Reviewing and approving economic performance and initiatives documents. Overseeing strategic initiatives prioritization as part of budget allocation endorsement. Proposing economic strategies governance structure involving AD stakeholders.","'CV Employee Work Experience'[CV Start Date]":"2022-01-01","'CV Employee Work Experience'[CV End Date]":"2022-04-30"},{"'CV Employee Work Experience'[CV Company Name]":"Department of Economic Development Abu Dhabi","'CV Employee Work Experience'[CV Job Title]":"Head of Economic Modelling Section","'CV Employee Work Experience'[CV Responsibilities Summary]":"Leading economic modelling development projects, consisting of; AD Macroeconomic Quarterly Model, AD Planning Model, Industrial Policy and Planning Model, AD Economic Clustering Model, Economic Risk Assessment Tools and framework.","'CV Employee Work Experience'[CV Start Date]":"2022-03-01","'CV Employee Work Experience'[CV End Date]":""}]</v>
+        <v>[{"CV Employee Work Experience[CV Company Name]":"Department of Economic Development Abu Dhabi","CV Employee Work Experience[CV Job Title]":"Economic Researcher","CV Employee Work Experience[CV Responsibilities Summary]":"Member of the modelling team at the Department of Economic Development. Updating and maintaining the integrity of Abu Dhabi Macroeconometric model, Computable General Equilibrium model and Human Resources Development modelling system. Economic forecasting, policy analysis for short/mid/long term using variety of economic models and conducting case studies and analyzing the impact of different scenarios on Abu Dhabi economic variables. Preparing research overview and plan, to help recognize goals, methodologies, necessary tools and information sources most suitable for the topic at hand. Preparing progress reports throughout the research timeline and with accordance to the plan. Organizing data bank for the team and update it regularly to centralize and ease the access to necessary information when needed. Analyzing the forecasted growth of economic sectors and variables in Abu Dhabi and identifying reasons behind the forecast. Planning and organizing meetings and events related to ongoing or done research. Identifying the status of current and forecasted Abu Dhabi economy in accordance to Abu Dhabi Economic Vision 2030. Provide recommendations based on research and quantitative impact analysis outcome. Provide suggestions to help improve quality of the research and accuracy of outcome.","CV Employee Work Experience[CV Start Date]":"2010-12-01","CV Employee Work Experience[CV End Date]":"2013-10-31"},{"CV Employee Work Experience[CV Company Name]":"Abu Dhabi Department of Economic Development","CV Employee Work Experience[CV Job Title]":"Secondment at Abu Dhabi Department of Economic Development","CV Employee Work Experience[CV Responsibilities Summary]":"Handling modelling tasks including economic forecast for Abu Dhabi’s economy, scenario building and analysis. Conducting economic research based on tasks requested by Abu Dhabi Executive Council. Taking a lead role in developing Abu Dhabi Economic Risk Profile. Additionally, taking a significant role in initiating Economic Policy department within the research sector at ADDED through methodology development, stakeholders engagement and submitting white and policy papers.","CV Employee Work Experience[CV Start Date]":"2016-10-01","CV Employee Work Experience[CV End Date]":"2018-11-30"},{"CV Employee Work Experience[CV Company Name]":"Abu Dhabi Council for Economic Development","CV Employee Work Experience[CV Job Title]":"Project Manager","CV Employee Work Experience[CV Responsibilities Summary]":"Conducting economic research and analysis according to the plan set by Economic Policy Planning Division at the council or by request from higher management. Using the most suitable qualitative and quantitative research methodologies and reliable sources of information. Managing research projects and supporting Project Managers by getting the necessary approvals, setting project plan, setting deadlines, assigning responsibilities to the project team, setting internal and external meetings and delivering the final outcome with all supporting documents. Contributing to the development and implementation of procedures and processes which cater to all aspects of project management and review. Reviewing policies, legislations, papers and reports and provide recommendations. Proactive involvement in outreach workshops through engaging the private sector and liaising with stakeholders in the public sector. Preparing briefs and presentations for management and stakeholders and representing ADCED in international conferences and seminars.","CV Employee Work Experience[CV Start Date]":"2018-02-01","CV Employee Work Experience[CV End Date]":"2020-12-31"},{"CV Employee Work Experience[CV Company Name]":"Abu Dhabi Council for Economic Development","CV Employee Work Experience[CV Job Title]":"Acting Director – Economic Policy Planning Division","CV Employee Work Experience[CV Responsibilities Summary]":"Reviewing and setting up divisional strategic and operational plan and budget requirement for 2020 and aligning with entity mandate and the emirate’s three years plan. Setting individual development plans and training requirements for division staff and appraisal criteria. Preparing monthly division performance and presenting it to the Director General. Setting up tasks, success criteria and handing projects to work groups within the division, following up work progress and reviewing content and quality. Communicating project results and expectations between work groups and decision maker. Presenting ADCED in meetings and handling cooperation with other government entities. Collaborating with Abu Dhabi Department of Economic Development in setting up Abu Dhabi’s economic strategy 2021-2024.","CV Employee Work Experience[CV Start Date]":"2019-07-01","CV Employee Work Experience[CV End Date]":"2020-12-31"},{"CV Employee Work Experience[CV Company Name]":"Department of Economic Development Abu Dhabi","CV Employee Work Experience[CV Job Title]":"Team Leader / Acting Director of Economic Intelligence","CV Employee Work Experience[CV Responsibilities Summary]":"Setting up the structure and vision of an economic intelligence department to centralize and improve economic information within the newly formed strategy office at AD DED. Initiating the development of economic models to simulate different aspects of the economy to support economic strategies and policy initiatives. Building a decision support smart platform that includes all available economic information and utilizing both existing and new quantitative analysis tools.","CV Employee Work Experience[CV Start Date]":"2020-07-01","CV Employee Work Experience[CV End Date]":"2021-12-31"},{"CV Employee Work Experience[CV Company Name]":"Department of Economic Development Abu Dhabi","CV Employee Work Experience[CV Job Title]":"Acting Director of Economic Planning &amp; Performance","CV Employee Work Experience[CV Responsibilities Summary]":"Setting up 2022 EPP department plan and employees’ roles. Engaging stakeholder in initiatives’ proposal and implementations as part of AD Economic Strategy. Reviewing and approving economic performance and initiatives documents. Overseeing strategic initiatives prioritization as part of budget allocation endorsement. Proposing economic strategies governance structure involving AD stakeholders.","CV Employee Work Experience[CV Start Date]":"2022-01-01","CV Employee Work Experience[CV End Date]":"2022-04-30"},{"CV Employee Work Experience[CV Company Name]":"Department of Economic Development Abu Dhabi","CV Employee Work Experience[CV Job Title]":"Head of Economic Modelling Section","CV Employee Work Experience[CV Responsibilities Summary]":"Leading economic modelling development projects, consisting of; AD Macroeconomic Quarterly Model, AD Planning Model, Industrial Policy and Planning Model, AD Economic Clustering Model, Economic Risk Assessment Tools and framework.","CV Employee Work Experience[CV Start Date]":"2022-03-01","CV Employee Work Experience[CV End Date]":""}]</v>
       </c>
       <c r="BD11" t="str">
         <v>Salem Ali A. M. Al Nuaimi is a seasoned economic strategist with over 12 years of experience leading economic modelling and planning initiatives at Abu Dhabi’s key economic institutions. He brings expert proficiency in macroeconometric and CGE modelling, financial forecasting, and economic impact analysis, with a strong foundation in national accounts and data-driven policy development. His leadership roles across the Department of Economic Development and Abu Dhabi Council for Economic Development reflect deep expertise in strategic insight generation, stakeholder engagement, and economic risk assessment. He holds a BSc in Economics from Queen Mary, University of London, complemented by rigorous training in social sciences and research methodology.</v>
@@ -2377,7 +2377,7 @@
         <v>0</v>
       </c>
       <c r="AN12" t="str">
-        <v>[{"'CV Employee Competencies'[Technical Competency Name]":"Microsoft Project"},{"'CV Employee Competencies'[Technical Competency Name]":"English"},{"'CV Employee Competencies'[Technical Competency Name]":"Change Management"},{"'CV Employee Competencies'[Technical Competency Name]":"Program and Project Governance"},{"'CV Employee Competencies'[Technical Competency Name]":"Project Advisory"},{"'CV Employee Competencies'[Technical Competency Name]":"Contract Management and Negotiation"},{"'CV Employee Competencies'[Technical Competency Name]":"Reporting"},{"'CV Employee Competencies'[Technical Competency Name]":"Documentation and Archiving"},{"'CV Employee Competencies'[Technical Competency Name]":"Project Management"},{"'CV Employee Competencies'[Technical Competency Name]":"Program Management"},{"'CV Employee Competencies'[Technical Competency Name]":"Risk Management"},{"'CV Employee Competencies'[Technical Competency Name]":"KPI Setting"},{"'CV Employee Competencies'[Technical Competency Name]":"CATIA V5"},{"'CV Employee Competencies'[Technical Competency Name]":"SOLIDWORKS"},{"'CV Employee Competencies'[Technical Competency Name]":"SAP"},{"'CV Employee Competencies'[Technical Competency Name]":"Q-Pulse"},{"'CV Employee Competencies'[Technical Competency Name]":"Artificial Intelligence"},{"'CV Employee Competencies'[Technical Competency Name]":"Root-Cause Analysis"},{"'CV Employee Competencies'[Technical Competency Name]":"Lean Six Sigma"},{"'CV Employee Competencies'[Technical Competency Name]":"Scrum"},{"'CV Employee Competencies'[Technical Competency Name]":"OKR"},{"'CV Employee Competencies'[Technical Competency Name]":"Blockchain"},{"'CV Employee Competencies'[Technical Competency Name]":"ASME Y14.5"},{"'CV Employee Competencies'[Technical Competency Name]":"ASME"},{"'CV Employee Competencies'[Technical Competency Name]":"OSHA"},{"'CV Employee Competencies'[Technical Competency Name]":"Preventative Maintenance"},{"'CV Employee Competencies'[Technical Competency Name]":"Technical Documentation"},{"'CV Employee Competencies'[Technical Competency Name]":"CAD Modeling"},{"'CV Employee Competencies'[Technical Competency Name]":"Technical Drawings"},{"'CV Employee Competencies'[Technical Competency Name]":"Laser Inspection"},{"'CV Employee Competencies'[Technical Competency Name]":"CNC Automation"},{"'CV Employee Competencies'[Technical Competency Name]":"Stakeholder Management"},{"'CV Employee Competencies'[Technical Competency Name]":"Team Leadership"},{"'CV Employee Competencies'[Technical Competency Name]":"Mentoring"},{"'CV Employee Competencies'[Technical Competency Name]":"Communication"},{"'CV Employee Competencies'[Technical Competency Name]":"Problem Solving"}]</v>
+        <v>[{"CV Employee Competencies[Technical Competency Name]":"Microsoft Project"},{"CV Employee Competencies[Technical Competency Name]":"English"},{"CV Employee Competencies[Technical Competency Name]":"Change Management"},{"CV Employee Competencies[Technical Competency Name]":"Program and Project Governance"},{"CV Employee Competencies[Technical Competency Name]":"Project Advisory"},{"CV Employee Competencies[Technical Competency Name]":"Contract Management and Negotiation"},{"CV Employee Competencies[Technical Competency Name]":"Reporting"},{"CV Employee Competencies[Technical Competency Name]":"Documentation and Archiving"},{"CV Employee Competencies[Technical Competency Name]":"Project Management"},{"CV Employee Competencies[Technical Competency Name]":"Program Management"},{"CV Employee Competencies[Technical Competency Name]":"Risk Management"},{"CV Employee Competencies[Technical Competency Name]":"KPI Setting"},{"CV Employee Competencies[Technical Competency Name]":"CATIA V5"},{"CV Employee Competencies[Technical Competency Name]":"SOLIDWORKS"},{"CV Employee Competencies[Technical Competency Name]":"SAP"},{"CV Employee Competencies[Technical Competency Name]":"Q-Pulse"},{"CV Employee Competencies[Technical Competency Name]":"Artificial Intelligence"},{"CV Employee Competencies[Technical Competency Name]":"Root-Cause Analysis"},{"CV Employee Competencies[Technical Competency Name]":"Lean Six Sigma"},{"CV Employee Competencies[Technical Competency Name]":"Scrum"},{"CV Employee Competencies[Technical Competency Name]":"OKR"},{"CV Employee Competencies[Technical Competency Name]":"Blockchain"},{"CV Employee Competencies[Technical Competency Name]":"ASME Y14.5"},{"CV Employee Competencies[Technical Competency Name]":"ASME"},{"CV Employee Competencies[Technical Competency Name]":"OSHA"},{"CV Employee Competencies[Technical Competency Name]":"Preventative Maintenance"},{"CV Employee Competencies[Technical Competency Name]":"Technical Documentation"},{"CV Employee Competencies[Technical Competency Name]":"CAD Modeling"},{"CV Employee Competencies[Technical Competency Name]":"Technical Drawings"},{"CV Employee Competencies[Technical Competency Name]":"Laser Inspection"},{"CV Employee Competencies[Technical Competency Name]":"CNC Automation"},{"CV Employee Competencies[Technical Competency Name]":"Stakeholder Management"},{"CV Employee Competencies[Technical Competency Name]":"Team Leadership"},{"CV Employee Competencies[Technical Competency Name]":"Mentoring"},{"CV Employee Competencies[Technical Competency Name]":"Communication"},{"CV Employee Competencies[Technical Competency Name]":"Problem Solving"}]</v>
       </c>
       <c r="AO12" t="str">
         <v>[]</v>
@@ -2386,16 +2386,16 @@
         <v>[]</v>
       </c>
       <c r="AQ12" t="str">
-        <v>[{"'CV Employee Achievements and Awards'[CV Title]":"Strata High Performer Award","'CV Employee Achievements and Awards'[CV Achievement Description]":"","'CV Employee Achievements and Awards'[CV Issue Date]":"2023-01-01"},{"'CV Employee Achievements and Awards'[CV Title]":"Best Research Reviewer","'CV Employee Achievements and Awards'[CV Achievement Description]":"","'CV Employee Achievements and Awards'[CV Issue Date]":"2021-01-01"},{"'CV Employee Achievements and Awards'[CV Title]":"UAE Young Aerospace Leaders","'CV Employee Achievements and Awards'[CV Achievement Description]":"","'CV Employee Achievements and Awards'[CV Issue Date]":"2018-01-01"},{"'CV Employee Achievements and Awards'[CV Title]":"Professional Scrum Master","'CV Employee Achievements and Awards'[CV Achievement Description]":"Certificate No. 544188","'CV Employee Achievements and Awards'[CV Issue Date]":""},{"'CV Employee Achievements and Awards'[CV Title]":"Certified OKR Professional","'CV Employee Achievements and Awards'[CV Achievement Description]":"Certificate No. 3107230022-OCOKR1","'CV Employee Achievements and Awards'[CV Issue Date]":""},{"'CV Employee Achievements and Awards'[CV Title]":"Certified Blockchain Expert","'CV Employee Achievements and Awards'[CV Achievement Description]":"Certificate No. 14815479","'CV Employee Achievements and Awards'[CV Issue Date]":""},{"'CV Employee Achievements and Awards'[CV Title]":"IELTS","'CV Employee Achievements and Awards'[CV Achievement Description]":"Score 8.0/9, Certificate No. 19AE003082ALDK110A","'CV Employee Achievements and Awards'[CV Issue Date]":""},{"'CV Employee Achievements and Awards'[CV Title]":"Unmanned Aircraft Systems Regulations","'CV Employee Achievements and Awards'[CV Achievement Description]":"Certificate No. 24650c0f-235b-4d63-86bd-0929025cd9aa","'CV Employee Achievements and Awards'[CV Issue Date]":""},{"'CV Employee Achievements and Awards'[CV Title]":"Unmanned Aircraft Systems Operations","'CV Employee Achievements and Awards'[CV Achievement Description]":"Certificate No. c8994b18-3bc6-4d43-81a6-7d819addff9d","'CV Employee Achievements and Awards'[CV Issue Date]":""},{"'CV Employee Achievements and Awards'[CV Title]":"Government Accelerators Program","'CV Employee Achievements and Awards'[CV Achievement Description]":"Completion Letter","'CV Employee Achievements and Awards'[CV Issue Date]":""},{"'CV Employee Achievements and Awards'[CV Title]":"Innovation in the Government Program","'CV Employee Achievements and Awards'[CV Achievement Description]":"Completion Letter","'CV Employee Achievements and Awards'[CV Issue Date]":""},{"'CV Employee Achievements and Awards'[CV Title]":"Project Management Professional (PMP)","'CV Employee Achievements and Awards'[CV Achievement Description]":"Certificate No. 2802540","'CV Employee Achievements and Awards'[CV Issue Date]":""},{"'CV Employee Achievements and Awards'[CV Title]":"Risk Management Professional (RMP)","'CV Employee Achievements and Awards'[CV Achievement Description]":"Certificate No. 2985906","'CV Employee Achievements and Awards'[CV Issue Date]":""},{"'CV Employee Achievements and Awards'[CV Title]":"Certified Lean Six Sigma Black Belt","'CV Employee Achievements and Awards'[CV Achievement Description]":"Certificate No. B-8642","'CV Employee Achievements and Awards'[CV Issue Date]":""}]</v>
+        <v>[{"CV Employee Achievements and Awards[CV Title]":"Strata High Performer Award","CV Employee Achievements and Awards[CV Achievement Description]":"","CV Employee Achievements and Awards[CV Issue Date]":"2023-01-01"},{"CV Employee Achievements and Awards[CV Title]":"Best Research Reviewer","CV Employee Achievements and Awards[CV Achievement Description]":"","CV Employee Achievements and Awards[CV Issue Date]":"2021-01-01"},{"CV Employee Achievements and Awards[CV Title]":"UAE Young Aerospace Leaders","CV Employee Achievements and Awards[CV Achievement Description]":"","CV Employee Achievements and Awards[CV Issue Date]":"2018-01-01"},{"CV Employee Achievements and Awards[CV Title]":"Professional Scrum Master","CV Employee Achievements and Awards[CV Achievement Description]":"Certificate No. 544188","CV Employee Achievements and Awards[CV Issue Date]":""},{"CV Employee Achievements and Awards[CV Title]":"Certified OKR Professional","CV Employee Achievements and Awards[CV Achievement Description]":"Certificate No. 3107230022-OCOKR1","CV Employee Achievements and Awards[CV Issue Date]":""},{"CV Employee Achievements and Awards[CV Title]":"Certified Blockchain Expert","CV Employee Achievements and Awards[CV Achievement Description]":"Certificate No. 14815479","CV Employee Achievements and Awards[CV Issue Date]":""},{"CV Employee Achievements and Awards[CV Title]":"IELTS","CV Employee Achievements and Awards[CV Achievement Description]":"Score 8.0/9, Certificate No. 19AE003082ALDK110A","CV Employee Achievements and Awards[CV Issue Date]":""},{"CV Employee Achievements and Awards[CV Title]":"Unmanned Aircraft Systems Regulations","CV Employee Achievements and Awards[CV Achievement Description]":"Certificate No. 24650c0f-235b-4d63-86bd-0929025cd9aa","CV Employee Achievements and Awards[CV Issue Date]":""},{"CV Employee Achievements and Awards[CV Title]":"Unmanned Aircraft Systems Operations","CV Employee Achievements and Awards[CV Achievement Description]":"Certificate No. c8994b18-3bc6-4d43-81a6-7d819addff9d","CV Employee Achievements and Awards[CV Issue Date]":""},{"CV Employee Achievements and Awards[CV Title]":"Government Accelerators Program","CV Employee Achievements and Awards[CV Achievement Description]":"Completion Letter","CV Employee Achievements and Awards[CV Issue Date]":""},{"CV Employee Achievements and Awards[CV Title]":"Innovation in the Government Program","CV Employee Achievements and Awards[CV Achievement Description]":"Completion Letter","CV Employee Achievements and Awards[CV Issue Date]":""},{"CV Employee Achievements and Awards[CV Title]":"Project Management Professional (PMP)","CV Employee Achievements and Awards[CV Achievement Description]":"Certificate No. 2802540","CV Employee Achievements and Awards[CV Issue Date]":""},{"CV Employee Achievements and Awards[CV Title]":"Risk Management Professional (RMP)","CV Employee Achievements and Awards[CV Achievement Description]":"Certificate No. 2985906","CV Employee Achievements and Awards[CV Issue Date]":""},{"CV Employee Achievements and Awards[CV Title]":"Certified Lean Six Sigma Black Belt","CV Employee Achievements and Awards[CV Achievement Description]":"Certificate No. B-8642","CV Employee Achievements and Awards[CV Issue Date]":""}]</v>
       </c>
       <c r="AR12" t="str">
         <v>[]</v>
       </c>
       <c r="AS12" t="str">
-        <v>[{"'Employee Performance'[Performance Review Period]":"2024 Review Period","'Employee Performance'[Calculated Rating]":"","'Employee Performance'[Normalized Performance Rating]":""}]</v>
+        <v>[{"Employee Performance[Performance Review Period]":"2024 Review Period","Employee Performance[Calculated Rating]":"","Employee Performance[Normalized Performance Rating]":""}]</v>
       </c>
       <c r="AT12" t="str">
-        <v>[{"'Employee Achievements'[Customary Name]":"2024 Annual Appraisal","'Employee Achievements'[Manager OA Comments]":"As Khalifa has been with ADEO for less than six months, he will not receive a formal rating for 2024. However, it’s important to acknowledge his positive contributions. Khalifa has demonstrated enthusiasm for his role and a strong eagerness to contribute to the team’s success. His effective communication within the team and across the organization has been noticeable and appreciated, fostering positive collaboration. Additionally, Khalifa’s willingness to take on topics outside his area of expertise as a learning opportunity reflects his commendable growth mindset and adaptability. Moving forward, it will be essential for Khalifa to deepen his understanding of the energy sector and enhance his technical skills, particularly in governance, policy, and related areas. As he continues to settle into his role, I look forward to seeing his continued growth and contributions","'Employee Achievements'[Employee OA Comments]":""}]</v>
+        <v>[{"Employee Achievements[Customary Name]":"2024 Annual Appraisal","Employee Achievements[Manager OA Comments]":"As Khalifa has been with ADEO for less than six months, he will not receive a formal rating for 2024. However, it’s important to acknowledge his positive contributions. Khalifa has demonstrated enthusiasm for his role and a strong eagerness to contribute to the team’s success. His effective communication within the team and across the organization has been noticeable and appreciated, fostering positive collaboration. Additionally, Khalifa’s willingness to take on topics outside his area of expertise as a learning opportunity reflects his commendable growth mindset and adaptability. Moving forward, it will be essential for Khalifa to deepen his understanding of the energy sector and enhance his technical skills, particularly in governance, policy, and related areas. As he continues to settle into his role, I look forward to seeing his continued growth and contributions","Employee Achievements[Employee OA Comments]":""}]</v>
       </c>
       <c r="AU12" t="str">
         <v>[]</v>
@@ -2404,19 +2404,19 @@
         <v/>
       </c>
       <c r="AY12" t="str">
-        <v>[{"'Employee Qualification'[Qualification Title]":"Mechanical Engineering","'Employee Qualification'[Educational Institute]":"University of San Diego","'Employee Qualification'[GPA (Grade Point Average)]":"3.34","'Employee Qualification'[Study Start Date]":"2013-09-01","'Employee Qualification'[Study End Date]":"2017-01-03"},{"'Employee Qualification'[Qualification Title]":"Project and Enterprise Managment","'Employee Qualification'[Educational Institute]":"University College London","'Employee Qualification'[GPA (Grade Point Average)]":"3.92","'Employee Qualification'[Study Start Date]":"2019-09-01","'Employee Qualification'[Study End Date]":"2021-12-01"}]</v>
+        <v>[{"Employee Qualification[Qualification Title]":"Mechanical Engineering","Employee Qualification[Educational Institute]":"University of San Diego","Employee Qualification[GPA (Grade Point Average)]":"3.34","Employee Qualification[Study Start Date]":"2013-09-01","Employee Qualification[Study End Date]":"2017-01-03"},{"Employee Qualification[Qualification Title]":"Project and Enterprise Managment","Employee Qualification[Educational Institute]":"University College London","Employee Qualification[GPA (Grade Point Average)]":"3.92","Employee Qualification[Study Start Date]":"2019-09-01","Employee Qualification[Study End Date]":"2021-12-01"}]</v>
       </c>
       <c r="AZ12" t="str">
-        <v>[{"'CV Employee Education'[CV Institution Name]":"University of San Diego","'CV Employee Education'[CV Degree Name]":"BS in Mechanical Engineering","'CV Employee Education'[CV Start Date]":"2017-01-01","'CV Employee Education'[CV End Date]":"2017-12-31"},{"'CV Employee Education'[CV Institution Name]":"Oxford University","'CV Employee Education'[CV Degree Name]":"Diploma","'CV Employee Education'[CV Start Date]":"2019-01-01","'CV Employee Education'[CV End Date]":"2019-12-31"},{"'CV Employee Education'[CV Institution Name]":"Prime Minister Office","'CV Employee Education'[CV Degree Name]":"Diploma","'CV Employee Education'[CV Start Date]":"2020-01-01","'CV Employee Education'[CV End Date]":"2020-12-31"},{"'CV Employee Education'[CV Institution Name]":"University College London","'CV Employee Education'[CV Degree Name]":"MS in Project and Enterprise Management","'CV Employee Education'[CV Start Date]":"2021-01-01","'CV Employee Education'[CV End Date]":"2021-12-31"}]</v>
+        <v>[{"CV Employee Education[CV Institution Name]":"University of San Diego","CV Employee Education[CV Degree Name]":"BS in Mechanical Engineering","CV Employee Education[CV Start Date]":"2017-01-01","CV Employee Education[CV End Date]":"2017-12-31"},{"CV Employee Education[CV Institution Name]":"Oxford University","CV Employee Education[CV Degree Name]":"Diploma","CV Employee Education[CV Start Date]":"2019-01-01","CV Employee Education[CV End Date]":"2019-12-31"},{"CV Employee Education[CV Institution Name]":"Prime Minister Office","CV Employee Education[CV Degree Name]":"Diploma","CV Employee Education[CV Start Date]":"2020-01-01","CV Employee Education[CV End Date]":"2020-12-31"},{"CV Employee Education[CV Institution Name]":"University College London","CV Employee Education[CV Degree Name]":"MS in Project and Enterprise Management","CV Employee Education[CV Start Date]":"2021-01-01","CV Employee Education[CV End Date]":"2021-12-31"}]</v>
       </c>
       <c r="BA12" t="str">
-        <v>[{"'Employee Assignment History'[Assignment Name]":"Senior Specialist","'Employee Assignment History'[Position Title]":"Senior Specialist, Energy","'Employee Assignment History'[Employee Grade]":"3B","'Employee Assignment History'[Assignment Start Date]":"2024-07-09","'Employee Assignment History'[Assignment End Date]":"2025-07-31","'Employee Assignment History'[Assignment Experience (Years &amp; Months)]":"1 Years, 0 Months"},{"'Employee Assignment History'[Assignment Name]":"Senior Specialist, Energy","'Employee Assignment History'[Position Title]":"Senior Specialist, Energy","'Employee Assignment History'[Employee Grade]":"3B","'Employee Assignment History'[Assignment Start Date]":"2025-08-01","'Employee Assignment History'[Assignment End Date]":"","'Employee Assignment History'[Assignment Experience (Years &amp; Months)]":""}]</v>
+        <v>[{"Employee Assignment History[Assignment Name]":"Senior Specialist","Employee Assignment History[Position Title]":"Senior Specialist, Energy","Employee Assignment History[Employee Grade]":"3B","Employee Assignment History[Assignment Start Date]":"2024-07-09","Employee Assignment History[Assignment End Date]":"2025-07-31","Employee Assignment History[Assignment Experience (Years &amp; Months)]":"1 Years, 0 Months"},{"Employee Assignment History[Assignment Name]":"Senior Specialist, Energy","Employee Assignment History[Position Title]":"Senior Specialist, Energy","Employee Assignment History[Employee Grade]":"3B","Employee Assignment History[Assignment Start Date]":"2025-08-01","Employee Assignment History[Assignment End Date]":"","Employee Assignment History[Assignment Experience (Years &amp; Months)]":""}]</v>
       </c>
       <c r="BB12" t="str">
-        <v>[{"'Employee Previous Employer'[Previous Employer Name]":"Strata Manufacturing PJSC","'Employee Previous Employer'[Previous Job Title]":"Project Manager","'Employee Previous Employer'[Start Date]":"2017-06-01","'Employee Previous Employer'[End Date]":"2023-06-29"},{"'Employee Previous Employer'[Previous Employer Name]":"Khalifa Sameh Khalaf aldhaen","'Employee Previous Employer'[Previous Job Title]":"Senior Specialist  PMO","'Employee Previous Employer'[Start Date]":"2023-07-24","'Employee Previous Employer'[End Date]":"2024-07-03"}]</v>
+        <v>[{"Employee Previous Employer[Previous Employer Name]":"Strata Manufacturing PJSC","Employee Previous Employer[Previous Job Title]":"Project Manager","Employee Previous Employer[Start Date]":"2017-06-01","Employee Previous Employer[End Date]":"2023-06-29"},{"Employee Previous Employer[Previous Employer Name]":"Khalifa Sameh Khalaf aldhaen","Employee Previous Employer[Previous Job Title]":"Senior Specialist  PMO","Employee Previous Employer[Start Date]":"2023-07-24","Employee Previous Employer[End Date]":"2024-07-03"}]</v>
       </c>
       <c r="BC12" t="str">
-        <v>[{"'CV Employee Work Experience'[CV Company Name]":"Strata Manufacturing PJSC (A Mubadala Company)","'CV Employee Work Experience'[CV Job Title]":"Junior Tooling Engineer","'CV Employee Work Experience'[CV Responsibilities Summary]":"Lead the implementation of the Preventative Maintenance Plan. Wrote technical documentation on the operation and maintenance of +100 tools and machineries. Controlled tooling engineering activities to maintain ASME, OSHA, and internal standards. Drafted technical drawings and CAD models in CATIA V5 and SOLIDWORKS. Adhered to ASME Y14.5 Dimensioning and Tolerances standards in produced engineering drawings. Deployment and management of all department documents and procedures on ENOVIA. Conducted the inspection activities of Boeing 777X tools and machines readiness. Maintained tooling records in SAP using several types of transactions. Had 2 Direct Reports consisting of 2 tooling technicians.","'CV Employee Work Experience'[CV Start Date]":"2017-01-01","'CV Employee Work Experience'[CV End Date]":"2018-12-31"},{"'CV Employee Work Experience'[CV Company Name]":"Strata Manufacturing PJSC (A Mubadala Company)","'CV Employee Work Experience'[CV Job Title]":"Tooling Engineer","'CV Employee Work Experience'[CV Responsibilities Summary]":"Lead tooling engineer for a classified Unmanned Aerial Vehicle (UAV) manufacturing project. Lead tooling engineer for a classified Fighter Aircraft outer shell manufacturing project. Lead tooling engineer for the Pilatus PC-24 Business Jet. Achieved cost savings of +$13,000 by automating repetitive tasks. Improved tooling engineering ticket closure speed by 19% which decreased machine downtime. Analysed laser inspection technical reports of assembly and lay-up tools. Presented implementation plans for the use of Artificial Intelligence in 2 departments. Commissioned the CNC Tools Automation System on-time and within budget. Performed several root-cause analyses using Quality Management System software (Q-Pulse). Had 3 Direct Reports consisting of 2 tooling technicians and 1 tool designer.","'CV Employee Work Experience'[CV Start Date]":"2019-01-01","'CV Employee Work Experience'[CV End Date]":"2020-12-31"},{"'CV Employee Work Experience'[CV Company Name]":"Strata Manufacturing PJSC (A Mubadala Company)","'CV Employee Work Experience'[CV Job Title]":"Project Manager","'CV Employee Work Experience'[CV Responsibilities Summary]":"Spearheaded the first joint venture of the company having a budget of 100 MM AED. Lead a 15-member project team consisting of 5 engineers, 8 operators, and 2 function managers. Compressed the initial JV schedule in MS Project by more than 25%. Designed the governance structure of the JV project to satisfy internal and external stakeholders. Presented weekly and monthly project updates to the Board Members. Lead weekly risk management sessions to identify, qualify, quantify, and update risk response plans. Acquired government approvals and licenses for the JV company. Consulted on the set up of the procurement department at the JV. Provided oversight on original equipment manufacturers (OEMs) during machines installations. Advised on the launch of Strata’s long-term strategy through the Advanced Manufacturing Office.","'CV Employee Work Experience'[CV Start Date]":"2021-01-01","'CV Employee Work Experience'[CV End Date]":"2023-01-01"},{"'CV Employee Work Experience'[CV Company Name]":"Strata Manufacturing PJSC (A Mubadala Company)","'CV Employee Work Experience'[CV Job Title]":"Lead Tooling Engineer (Acting)","'CV Employee Work Experience'[CV Responsibilities Summary]":"Main point of contact for the Tooling Department on all Strata projects. Coached 3 engineers and transferred knowledge through workshops, presentations, and tutorials. Provide dispositions and advise production department on all tooling disputes. Performed Data Analytics and Visualization with Microsoft Power BI. Had 5 Direct Reports consisting of 3 tooling technicians, 1 tool designer and 1 junior tooling engineer.","'CV Employee Work Experience'[CV Start Date]":"2021-01-01","'CV Employee Work Experience'[CV End Date]":"2021-12-31"},{"'CV Employee Work Experience'[CV Company Name]":"Abu Dhabi Waste Management Company – Tadweer","'CV Employee Work Experience'[CV Job Title]":"Senior Specialist PMO","'CV Employee Work Experience'[CV Responsibilities Summary]":"Establish and maintain a robust program and project governance framework to oversee all functional and cross-functional projects and programs (incl. roles and responsibilities, decision-making processes, escalation procedures, tracking tools, etc.). Develop and manage the enterprise program monitoring and reporting systems and manage ad-hoc reporting to the MD &amp; CEO. Ensure periodic management reporting on project status (i.e., schedule, costs, activities, opportunities, and risks) to ensure visibility of project status to Management. Manage Tadweer’s strategic projects and initiatives portfolio, ensuring effective initiatives and projects prioritization and synchronization (such as Waste-to-Safe Aviation Fuel and Waste-to-Energy). Facilitate large-scale change management programs, ensuring their effective delivery across all functions, in support of transformational initiatives. Oversee the management of contracts and other transformational project related commitments. Contribute setting joint KPIs as applicable with relevant functions and work together to achieve desired outcomes.","'CV Employee Work Experience'[CV Start Date]":"2023-01-01","'CV Employee Work Experience'[CV End Date]":""}]</v>
+        <v>[{"CV Employee Work Experience[CV Company Name]":"Strata Manufacturing PJSC (A Mubadala Company)","CV Employee Work Experience[CV Job Title]":"Junior Tooling Engineer","CV Employee Work Experience[CV Responsibilities Summary]":"Lead the implementation of the Preventative Maintenance Plan. Wrote technical documentation on the operation and maintenance of +100 tools and machineries. Controlled tooling engineering activities to maintain ASME, OSHA, and internal standards. Drafted technical drawings and CAD models in CATIA V5 and SOLIDWORKS. Adhered to ASME Y14.5 Dimensioning and Tolerances standards in produced engineering drawings. Deployment and management of all department documents and procedures on ENOVIA. Conducted the inspection activities of Boeing 777X tools and machines readiness. Maintained tooling records in SAP using several types of transactions. Had 2 Direct Reports consisting of 2 tooling technicians.","CV Employee Work Experience[CV Start Date]":"2017-01-01","CV Employee Work Experience[CV End Date]":"2018-12-31"},{"CV Employee Work Experience[CV Company Name]":"Strata Manufacturing PJSC (A Mubadala Company)","CV Employee Work Experience[CV Job Title]":"Tooling Engineer","CV Employee Work Experience[CV Responsibilities Summary]":"Lead tooling engineer for a classified Unmanned Aerial Vehicle (UAV) manufacturing project. Lead tooling engineer for a classified Fighter Aircraft outer shell manufacturing project. Lead tooling engineer for the Pilatus PC-24 Business Jet. Achieved cost savings of +$13,000 by automating repetitive tasks. Improved tooling engineering ticket closure speed by 19% which decreased machine downtime. Analysed laser inspection technical reports of assembly and lay-up tools. Presented implementation plans for the use of Artificial Intelligence in 2 departments. Commissioned the CNC Tools Automation System on-time and within budget. Performed several root-cause analyses using Quality Management System software (Q-Pulse). Had 3 Direct Reports consisting of 2 tooling technicians and 1 tool designer.","CV Employee Work Experience[CV Start Date]":"2019-01-01","CV Employee Work Experience[CV End Date]":"2020-12-31"},{"CV Employee Work Experience[CV Company Name]":"Strata Manufacturing PJSC (A Mubadala Company)","CV Employee Work Experience[CV Job Title]":"Project Manager","CV Employee Work Experience[CV Responsibilities Summary]":"Spearheaded the first joint venture of the company having a budget of 100 MM AED. Lead a 15-member project team consisting of 5 engineers, 8 operators, and 2 function managers. Compressed the initial JV schedule in MS Project by more than 25%. Designed the governance structure of the JV project to satisfy internal and external stakeholders. Presented weekly and monthly project updates to the Board Members. Lead weekly risk management sessions to identify, qualify, quantify, and update risk response plans. Acquired government approvals and licenses for the JV company. Consulted on the set up of the procurement department at the JV. Provided oversight on original equipment manufacturers (OEMs) during machines installations. Advised on the launch of Strata’s long-term strategy through the Advanced Manufacturing Office.","CV Employee Work Experience[CV Start Date]":"2021-01-01","CV Employee Work Experience[CV End Date]":"2023-01-01"},{"CV Employee Work Experience[CV Company Name]":"Strata Manufacturing PJSC (A Mubadala Company)","CV Employee Work Experience[CV Job Title]":"Lead Tooling Engineer (Acting)","CV Employee Work Experience[CV Responsibilities Summary]":"Main point of contact for the Tooling Department on all Strata projects. Coached 3 engineers and transferred knowledge through workshops, presentations, and tutorials. Provide dispositions and advise production department on all tooling disputes. Performed Data Analytics and Visualization with Microsoft Power BI. Had 5 Direct Reports consisting of 3 tooling technicians, 1 tool designer and 1 junior tooling engineer.","CV Employee Work Experience[CV Start Date]":"2021-01-01","CV Employee Work Experience[CV End Date]":"2021-12-31"},{"CV Employee Work Experience[CV Company Name]":"Abu Dhabi Waste Management Company – Tadweer","CV Employee Work Experience[CV Job Title]":"Senior Specialist PMO","CV Employee Work Experience[CV Responsibilities Summary]":"Establish and maintain a robust program and project governance framework to oversee all functional and cross-functional projects and programs (incl. roles and responsibilities, decision-making processes, escalation procedures, tracking tools, etc.). Develop and manage the enterprise program monitoring and reporting systems and manage ad-hoc reporting to the MD &amp; CEO. Ensure periodic management reporting on project status (i.e., schedule, costs, activities, opportunities, and risks) to ensure visibility of project status to Management. Manage Tadweer’s strategic projects and initiatives portfolio, ensuring effective initiatives and projects prioritization and synchronization (such as Waste-to-Safe Aviation Fuel and Waste-to-Energy). Facilitate large-scale change management programs, ensuring their effective delivery across all functions, in support of transformational initiatives. Oversee the management of contracts and other transformational project related commitments. Contribute setting joint KPIs as applicable with relevant functions and work together to achieve desired outcomes.","CV Employee Work Experience[CV Start Date]":"2023-01-01","CV Employee Work Experience[CV End Date]":""}]</v>
       </c>
       <c r="BD12" t="str">
         <v>Khalifa Aldhaen is a seasoned project and program leader with over 9 years of progressive experience in aerospace and public sector waste management, holding senior roles at Strata Manufacturing and Tadweer. He brings advanced expertise in project governance, change management, and contract negotiation, complemented by a robust toolkit including CATIA V5, SAP, and Q-Pulse. A certified PMP, RMP, Lean Six Sigma Black Belt, and Professional Scrum Master, he also holds an MS in Project and Enterprise Management from UCL and has been recognized with the Strata High Performer Award and as a UAE Young Aerospace Leader. His leadership is further distinguished by executive diplomas from the UAE Prime Minister’s Office and Oxford University in AI and government innovation.</v>
@@ -2544,7 +2544,7 @@
         <v>0</v>
       </c>
       <c r="AN13" t="str">
-        <v>[{"'CV Employee Competencies'[Technical Competency Name]":"Analytical Thinking and Innovation"},{"'CV Employee Competencies'[Technical Competency Name]":"Strong Communication Skills"},{"'CV Employee Competencies'[Technical Competency Name]":"Critical Thinking and Analysis"},{"'CV Employee Competencies'[Technical Competency Name]":"Active Learning"},{"'CV Employee Competencies'[Technical Competency Name]":"Complex Problem Solving"},{"'CV Employee Competencies'[Technical Competency Name]":"Self-motivation"},{"'CV Employee Competencies'[Technical Competency Name]":"Adaptability"},{"'CV Employee Competencies'[Technical Competency Name]":"Creativity and Collaboration"},{"'CV Employee Competencies'[Technical Competency Name]":"Resilience"},{"'CV Employee Competencies'[Technical Competency Name]":"Emotional Intelligence"},{"'CV Employee Competencies'[Technical Competency Name]":"International Relations"},{"'CV Employee Competencies'[Technical Competency Name]":"Resource Allocation"},{"'CV Employee Competencies'[Technical Competency Name]":"Event Planning and Organization"},{"'CV Employee Competencies'[Technical Competency Name]":"Reporting"},{"'CV Employee Competencies'[Technical Competency Name]":"Project Advisory"},{"'CV Employee Competencies'[Technical Competency Name]":"Business Model Development and Innovation"},{"'CV Employee Competencies'[Technical Competency Name]":"Project Planning &amp; Execution"},{"'CV Employee Competencies'[Technical Competency Name]":"Strategic Advisory"},{"'CV Employee Competencies'[Technical Competency Name]":"Communication and Coordination"},{"'CV Employee Competencies'[Technical Competency Name]":"Digital Transformation"},{"'CV Employee Competencies'[Technical Competency Name]":"Provider Relationship Management"},{"'CV Employee Competencies'[Technical Competency Name]":"Leadership Skills"},{"'CV Employee Competencies'[Technical Competency Name]":"Creative Problem Solving and Decision Making"},{"'CV Employee Competencies'[Technical Competency Name]":"Business Communication"}]</v>
+        <v>[{"CV Employee Competencies[Technical Competency Name]":"Analytical Thinking and Innovation"},{"CV Employee Competencies[Technical Competency Name]":"Strong Communication Skills"},{"CV Employee Competencies[Technical Competency Name]":"Critical Thinking and Analysis"},{"CV Employee Competencies[Technical Competency Name]":"Active Learning"},{"CV Employee Competencies[Technical Competency Name]":"Complex Problem Solving"},{"CV Employee Competencies[Technical Competency Name]":"Self-motivation"},{"CV Employee Competencies[Technical Competency Name]":"Adaptability"},{"CV Employee Competencies[Technical Competency Name]":"Creativity and Collaboration"},{"CV Employee Competencies[Technical Competency Name]":"Resilience"},{"CV Employee Competencies[Technical Competency Name]":"Emotional Intelligence"},{"CV Employee Competencies[Technical Competency Name]":"International Relations"},{"CV Employee Competencies[Technical Competency Name]":"Resource Allocation"},{"CV Employee Competencies[Technical Competency Name]":"Event Planning and Organization"},{"CV Employee Competencies[Technical Competency Name]":"Reporting"},{"CV Employee Competencies[Technical Competency Name]":"Project Advisory"},{"CV Employee Competencies[Technical Competency Name]":"Business Model Development and Innovation"},{"CV Employee Competencies[Technical Competency Name]":"Project Planning &amp; Execution"},{"CV Employee Competencies[Technical Competency Name]":"Strategic Advisory"},{"CV Employee Competencies[Technical Competency Name]":"Communication and Coordination"},{"CV Employee Competencies[Technical Competency Name]":"Digital Transformation"},{"CV Employee Competencies[Technical Competency Name]":"Provider Relationship Management"},{"CV Employee Competencies[Technical Competency Name]":"Leadership Skills"},{"CV Employee Competencies[Technical Competency Name]":"Creative Problem Solving and Decision Making"},{"CV Employee Competencies[Technical Competency Name]":"Business Communication"}]</v>
       </c>
       <c r="AO13" t="str">
         <v>[]</v>
@@ -2553,16 +2553,16 @@
         <v>[]</v>
       </c>
       <c r="AQ13" t="str">
-        <v>[{"'CV Employee Achievements and Awards'[CV Title]":"LEADING DIGITAL TRANSFORMATION &amp; INNOVATION","'CV Employee Achievements and Awards'[CV Achievement Description]":"","'CV Employee Achievements and Awards'[CV Issue Date]":"2023-01-01"},{"'CV Employee Achievements and Awards'[CV Title]":"LEADERSHIP SKILLS","'CV Employee Achievements and Awards'[CV Achievement Description]":"","'CV Employee Achievements and Awards'[CV Issue Date]":"2022-01-01"},{"'CV Employee Achievements and Awards'[CV Title]":"CREATIVE PROBLEM SOLVING &amp; DECISION MAKING","'CV Employee Achievements and Awards'[CV Achievement Description]":"","'CV Employee Achievements and Awards'[CV Issue Date]":"2022-01-01"},{"'CV Employee Achievements and Awards'[CV Title]":"COMMUNICATING FOR BUSINESS SUCCESS","'CV Employee Achievements and Awards'[CV Achievement Description]":"","'CV Employee Achievements and Awards'[CV Issue Date]":"2022-01-01"},{"'CV Employee Achievements and Awards'[CV Title]":"DEVELOPING AND INNOVATING BUSINESS MODELS FOR SUCCESS","'CV Employee Achievements and Awards'[CV Achievement Description]":"","'CV Employee Achievements and Awards'[CV Issue Date]":"2021-01-01"}]</v>
+        <v>[{"CV Employee Achievements and Awards[CV Title]":"LEADING DIGITAL TRANSFORMATION &amp; INNOVATION","CV Employee Achievements and Awards[CV Achievement Description]":"","CV Employee Achievements and Awards[CV Issue Date]":"2023-01-01"},{"CV Employee Achievements and Awards[CV Title]":"LEADERSHIP SKILLS","CV Employee Achievements and Awards[CV Achievement Description]":"","CV Employee Achievements and Awards[CV Issue Date]":"2022-01-01"},{"CV Employee Achievements and Awards[CV Title]":"CREATIVE PROBLEM SOLVING &amp; DECISION MAKING","CV Employee Achievements and Awards[CV Achievement Description]":"","CV Employee Achievements and Awards[CV Issue Date]":"2022-01-01"},{"CV Employee Achievements and Awards[CV Title]":"COMMUNICATING FOR BUSINESS SUCCESS","CV Employee Achievements and Awards[CV Achievement Description]":"","CV Employee Achievements and Awards[CV Issue Date]":"2022-01-01"},{"CV Employee Achievements and Awards[CV Title]":"DEVELOPING AND INNOVATING BUSINESS MODELS FOR SUCCESS","CV Employee Achievements and Awards[CV Achievement Description]":"","CV Employee Achievements and Awards[CV Issue Date]":"2021-01-01"}]</v>
       </c>
       <c r="AR13" t="str">
         <v>[]</v>
       </c>
       <c r="AS13" t="str">
-        <v>[{"'Employee Performance'[Performance Review Period]":"2024 Review Period","'Employee Performance'[Calculated Rating]":"","'Employee Performance'[Normalized Performance Rating]":""}]</v>
+        <v>[{"Employee Performance[Performance Review Period]":"2024 Review Period","Employee Performance[Calculated Rating]":"","Employee Performance[Normalized Performance Rating]":""}]</v>
       </c>
       <c r="AT13" t="str">
-        <v>[{"'Employee Achievements'[Customary Name]":"2024 Annual Appraisal","'Employee Achievements'[Manager OA Comments]":"","'Employee Achievements'[Employee OA Comments]":""}]</v>
+        <v>[{"Employee Achievements[Customary Name]":"2024 Annual Appraisal","Employee Achievements[Manager OA Comments]":"","Employee Achievements[Employee OA Comments]":""}]</v>
       </c>
       <c r="AU13" t="str">
         <v>[]</v>
@@ -2571,19 +2571,19 @@
         <v/>
       </c>
       <c r="AY13" t="str">
-        <v>[{"'Employee Qualification'[Qualification Title]":"International Studies - International Relations","'Employee Qualification'[Educational Institute]":"Zayed University","'Employee Qualification'[GPA (Grade Point Average)]":"3.62","'Employee Qualification'[Study Start Date]":"2017-09-01","'Employee Qualification'[Study End Date]":"2021-05-24"}]</v>
+        <v>[{"Employee Qualification[Qualification Title]":"International Studies - International Relations","Employee Qualification[Educational Institute]":"Zayed University","Employee Qualification[GPA (Grade Point Average)]":"3.62","Employee Qualification[Study Start Date]":"2017-09-01","Employee Qualification[Study End Date]":"2021-05-24"}]</v>
       </c>
       <c r="AZ13" t="str">
-        <v>[{"'CV Employee Education'[CV Institution Name]":"Sheikh Zayed Private Academy for Girls","'CV Employee Education'[CV Degree Name]":"High School Diploma","'CV Employee Education'[CV Start Date]":"2013-01-01","'CV Employee Education'[CV End Date]":"2017-12-31"},{"'CV Employee Education'[CV Institution Name]":"Zayed University","'CV Employee Education'[CV Degree Name]":"Bachelor of Arts","'CV Employee Education'[CV Start Date]":"2017-01-01","'CV Employee Education'[CV End Date]":"2021-12-31"}]</v>
+        <v>[{"CV Employee Education[CV Institution Name]":"Sheikh Zayed Private Academy for Girls","CV Employee Education[CV Degree Name]":"High School Diploma","CV Employee Education[CV Start Date]":"2013-01-01","CV Employee Education[CV End Date]":"2017-12-31"},{"CV Employee Education[CV Institution Name]":"Zayed University","CV Employee Education[CV Degree Name]":"Bachelor of Arts","CV Employee Education[CV Start Date]":"2017-01-01","CV Employee Education[CV End Date]":"2021-12-31"}]</v>
       </c>
       <c r="BA13" t="str">
-        <v>[{"'Employee Assignment History'[Assignment Name]":"Specialist","'Employee Assignment History'[Position Title]":"Specialist, Special Projects","'Employee Assignment History'[Employee Grade]":"4B","'Employee Assignment History'[Assignment Start Date]":"2024-09-03","'Employee Assignment History'[Assignment End Date]":"2025-07-31","'Employee Assignment History'[Assignment Experience (Years &amp; Months)]":"0 Years, 10 Months"},{"'Employee Assignment History'[Assignment Name]":"Specialist, Special Projects","'Employee Assignment History'[Position Title]":"Specialist, Special Projects","'Employee Assignment History'[Employee Grade]":"4B","'Employee Assignment History'[Assignment Start Date]":"2025-08-01","'Employee Assignment History'[Assignment End Date]":"2025-08-31","'Employee Assignment History'[Assignment Experience (Years &amp; Months)]":"0 Years, 0 Months"},{"'Employee Assignment History'[Assignment Name]":"Specialist, Special Intervention","'Employee Assignment History'[Position Title]":"Specialist, Special Intervention","'Employee Assignment History'[Employee Grade]":"4B","'Employee Assignment History'[Assignment Start Date]":"2025-09-01","'Employee Assignment History'[Assignment End Date]":"","'Employee Assignment History'[Assignment Experience (Years &amp; Months)]":""}]</v>
+        <v>[{"Employee Assignment History[Assignment Name]":"Specialist","Employee Assignment History[Position Title]":"Specialist, Special Projects","Employee Assignment History[Employee Grade]":"4B","Employee Assignment History[Assignment Start Date]":"2024-09-03","Employee Assignment History[Assignment End Date]":"2025-07-31","Employee Assignment History[Assignment Experience (Years &amp; Months)]":"0 Years, 10 Months"},{"Employee Assignment History[Assignment Name]":"Specialist, Special Projects","Employee Assignment History[Position Title]":"Specialist, Special Projects","Employee Assignment History[Employee Grade]":"4B","Employee Assignment History[Assignment Start Date]":"2025-08-01","Employee Assignment History[Assignment End Date]":"2025-08-31","Employee Assignment History[Assignment Experience (Years &amp; Months)]":"0 Years, 0 Months"},{"Employee Assignment History[Assignment Name]":"Specialist, Special Intervention","Employee Assignment History[Position Title]":"Specialist, Special Intervention","Employee Assignment History[Employee Grade]":"4B","Employee Assignment History[Assignment Start Date]":"2025-09-01","Employee Assignment History[Assignment End Date]":"","Employee Assignment History[Assignment Experience (Years &amp; Months)]":""}]</v>
       </c>
       <c r="BB13" t="str">
-        <v>[{"'Employee Previous Employer'[Previous Employer Name]":"Daman","'Employee Previous Employer'[Previous Job Title]":"Officer - Operations","'Employee Previous Employer'[Start Date]":"2021-11-24","'Employee Previous Employer'[End Date]":""}]</v>
+        <v>[{"Employee Previous Employer[Previous Employer Name]":"Daman","Employee Previous Employer[Previous Job Title]":"Officer - Operations","Employee Previous Employer[Start Date]":"2021-11-24","Employee Previous Employer[End Date]":""}]</v>
       </c>
       <c r="BC13" t="str">
-        <v>[{"'CV Employee Work Experience'[CV Company Name]":"Abu Dhabi Center for Sheltering and Humanitarian Care","'CV Employee Work Experience'[CV Job Title]":"PROJECTS AND EVENTS SPECIALIST - INTERNSHIP","'CV Employee Work Experience'[CV Responsibilities Summary]":"Planning and organizing events for victims of human trafficking and violence.","'CV Employee Work Experience'[CV Start Date]":"2021-03-01","'CV Employee Work Experience'[CV End Date]":"2021-05-01"},{"'CV Employee Work Experience'[CV Company Name]":"National Health Insurance Company - Daman","'CV Employee Work Experience'[CV Job Title]":"PROVIDER RELATIONS NETWORK OPERATIONS OFFICER","'CV Employee Work Experience'[CV Responsibilities Summary]":"Managing and strengthening the relationship between Daman and its providers. Cooperate with different departments in Daman to ensure client satisfaction.","'CV Employee Work Experience'[CV Start Date]":"2021-10-01","'CV Employee Work Experience'[CV End Date]":"2023-09-01"},{"'CV Employee Work Experience'[CV Company Name]":"National Health Insurance Company - Daman","'CV Employee Work Experience'[CV Job Title]":"HEALTH INSURANCE SOLUTIONS OFFICER","'CV Employee Work Experience'[CV Responsibilities Summary]":"Collaborate with project managers and team leads to allocate resources based on project requirements and individual capabilities. Contribute to analyzing utilization data and identifying potential areas for improvement. Collaborate with senior team members to provide insights and recommendations to optimize team efficiency and productivity. Facilitate effective communication between management, project managers, team leaders, team members and other stakeholders.","'CV Employee Work Experience'[CV Start Date]":"2023-08-01","'CV Employee Work Experience'[CV End Date]":"2023-12-01"},{"'CV Employee Work Experience'[CV Company Name]":"PureHealth","'CV Employee Work Experience'[CV Job Title]":"PROJECT SPECIALIST, EXECUTIVE OFFICE","'CV Employee Work Experience'[CV Responsibilities Summary]":"Project planning and execution. Developing and proposing campaign ideas. Building strategic partnerships through collaborative initiatives. Member of the Emirati Womens Chapter launched by PureHealth and General Women's Union under the patronage of H.H. Sheikha Fatima bint Mubarak.","'CV Employee Work Experience'[CV Start Date]":"2024-01-01","'CV Employee Work Experience'[CV End Date]":""}]</v>
+        <v>[{"CV Employee Work Experience[CV Company Name]":"Abu Dhabi Center for Sheltering and Humanitarian Care","CV Employee Work Experience[CV Job Title]":"PROJECTS AND EVENTS SPECIALIST - INTERNSHIP","CV Employee Work Experience[CV Responsibilities Summary]":"Planning and organizing events for victims of human trafficking and violence.","CV Employee Work Experience[CV Start Date]":"2021-03-01","CV Employee Work Experience[CV End Date]":"2021-05-01"},{"CV Employee Work Experience[CV Company Name]":"National Health Insurance Company - Daman","CV Employee Work Experience[CV Job Title]":"PROVIDER RELATIONS NETWORK OPERATIONS OFFICER","CV Employee Work Experience[CV Responsibilities Summary]":"Managing and strengthening the relationship between Daman and its providers. Cooperate with different departments in Daman to ensure client satisfaction.","CV Employee Work Experience[CV Start Date]":"2021-10-01","CV Employee Work Experience[CV End Date]":"2023-09-01"},{"CV Employee Work Experience[CV Company Name]":"National Health Insurance Company - Daman","CV Employee Work Experience[CV Job Title]":"HEALTH INSURANCE SOLUTIONS OFFICER","CV Employee Work Experience[CV Responsibilities Summary]":"Collaborate with project managers and team leads to allocate resources based on project requirements and individual capabilities. Contribute to analyzing utilization data and identifying potential areas for improvement. Collaborate with senior team members to provide insights and recommendations to optimize team efficiency and productivity. Facilitate effective communication between management, project managers, team leaders, team members and other stakeholders.","CV Employee Work Experience[CV Start Date]":"2023-08-01","CV Employee Work Experience[CV End Date]":"2023-12-01"},{"CV Employee Work Experience[CV Company Name]":"PureHealth","CV Employee Work Experience[CV Job Title]":"PROJECT SPECIALIST, EXECUTIVE OFFICE","CV Employee Work Experience[CV Responsibilities Summary]":"Project planning and execution. Developing and proposing campaign ideas. Building strategic partnerships through collaborative initiatives. Member of the Emirati Womens Chapter launched by PureHealth and General Women's Union under the patronage of H.H. Sheikha Fatima bint Mubarak.","CV Employee Work Experience[CV Start Date]":"2024-01-01","CV Employee Work Experience[CV End Date]":""}]</v>
       </c>
       <c r="BD13" t="str">
         <v>Rodah Almazrouei brings 4.4 years of progressive experience in healthcare project management and provider relations, with a strong track record in digital transformation and innovative business model development. She has successfully led project planning and execution across key roles at PureHealth and Daman, excelling in resource allocation, provider relationship management, and event coordination. Her foundational reporting and strategic advisory skills, combined with exceptional communication and creative problem-solving abilities, have driven operational efficiency and business success. A graduate of Zayed University with a Bachelor of Arts in International Relations, she bridges policy insight with practical healthcare innovation.</v>
@@ -2705,7 +2705,7 @@
         <v>0</v>
       </c>
       <c r="AN14" t="str">
-        <v>[{"'CV Employee Competencies'[Technical Competency Name]":"Genetic counseling"},{"'CV Employee Competencies'[Technical Competency Name]":"Family planning"},{"'CV Employee Competencies'[Technical Competency Name]":"Smoking cessation"},{"'CV Employee Competencies'[Technical Competency Name]":"Operations coordination"},{"'CV Employee Competencies'[Technical Competency Name]":"Departmental staff supervision"},{"'CV Employee Competencies'[Technical Competency Name]":"Patient care"},{"'CV Employee Competencies'[Technical Competency Name]":"Medical assessment"},{"'CV Employee Competencies'[Technical Competency Name]":"Medical diagnosis"},{"'CV Employee Competencies'[Technical Competency Name]":"Medication administration"},{"'CV Employee Competencies'[Technical Competency Name]":"Clinical standard review"},{"'CV Employee Competencies'[Technical Competency Name]":"English"},{"'CV Employee Competencies'[Technical Competency Name]":"Arabic"},{"'CV Employee Competencies'[Technical Competency Name]":"Healthcare management"},{"'CV Employee Competencies'[Technical Competency Name]":"Payroll Management"},{"'CV Employee Competencies'[Technical Competency Name]":"Performance Monitoring"},{"'CV Employee Competencies'[Technical Competency Name]":"Performance Monitoring &amp; Reporting"},{"'CV Employee Competencies'[Technical Competency Name]":"Project Planning &amp; Execution"},{"'CV Employee Competencies'[Technical Competency Name]":"Budget and Resource Management"},{"'CV Employee Competencies'[Technical Competency Name]":"Policy Advisory"},{"'CV Employee Competencies'[Technical Competency Name]":"Strategic Planning and Implementation"},{"'CV Employee Competencies'[Technical Competency Name]":"Family medicine"}]</v>
+        <v>[{"CV Employee Competencies[Technical Competency Name]":"Genetic counseling"},{"CV Employee Competencies[Technical Competency Name]":"Family planning"},{"CV Employee Competencies[Technical Competency Name]":"Smoking cessation"},{"CV Employee Competencies[Technical Competency Name]":"Operations coordination"},{"CV Employee Competencies[Technical Competency Name]":"Departmental staff supervision"},{"CV Employee Competencies[Technical Competency Name]":"Patient care"},{"CV Employee Competencies[Technical Competency Name]":"Medical assessment"},{"CV Employee Competencies[Technical Competency Name]":"Medical diagnosis"},{"CV Employee Competencies[Technical Competency Name]":"Medication administration"},{"CV Employee Competencies[Technical Competency Name]":"Clinical standard review"},{"CV Employee Competencies[Technical Competency Name]":"English"},{"CV Employee Competencies[Technical Competency Name]":"Arabic"},{"CV Employee Competencies[Technical Competency Name]":"Healthcare management"},{"CV Employee Competencies[Technical Competency Name]":"Payroll Management"},{"CV Employee Competencies[Technical Competency Name]":"Performance Monitoring"},{"CV Employee Competencies[Technical Competency Name]":"Performance Monitoring &amp; Reporting"},{"CV Employee Competencies[Technical Competency Name]":"Project Planning &amp; Execution"},{"CV Employee Competencies[Technical Competency Name]":"Budget and Resource Management"},{"CV Employee Competencies[Technical Competency Name]":"Policy Advisory"},{"CV Employee Competencies[Technical Competency Name]":"Strategic Planning and Implementation"},{"CV Employee Competencies[Technical Competency Name]":"Family medicine"}]</v>
       </c>
       <c r="AO14" t="str">
         <v>[]</v>
@@ -2714,7 +2714,7 @@
         <v>[]</v>
       </c>
       <c r="AQ14" t="str">
-        <v>[{"'CV Employee Achievements and Awards'[CV Title]":"Family medicine Board","'CV Employee Achievements and Awards'[CV Achievement Description]":"","'CV Employee Achievements and Awards'[CV Issue Date]":"2021-04-01"}]</v>
+        <v>[{"CV Employee Achievements and Awards[CV Title]":"Family medicine Board","CV Employee Achievements and Awards[CV Achievement Description]":"","CV Employee Achievements and Awards[CV Issue Date]":"2021-04-01"}]</v>
       </c>
       <c r="AR14" t="str">
         <v>[]</v>
@@ -2732,19 +2732,19 @@
         <v/>
       </c>
       <c r="AY14" t="str">
-        <v>[{"'Employee Qualification'[Qualification Title]":"Healthcare management","'Employee Qualification'[Educational Institute]":"The Royal collage of Surgeons in Ireland (RCSI)","'Employee Qualification'[GPA (Grade Point Average)]":"100","'Employee Qualification'[Study Start Date]":"","'Employee Qualification'[Study End Date]":""},{"'Employee Qualification'[Qualification Title]":"Medicine and Surgery","'Employee Qualification'[Educational Institute]":"United Arab Emirates University","'Employee Qualification'[GPA (Grade Point Average)]":"3.05","'Employee Qualification'[Study Start Date]":"","'Employee Qualification'[Study End Date]":""}]</v>
+        <v>[{"Employee Qualification[Qualification Title]":"Healthcare management","Employee Qualification[Educational Institute]":"The Royal collage of Surgeons in Ireland (RCSI)","Employee Qualification[GPA (Grade Point Average)]":"100","Employee Qualification[Study Start Date]":"","Employee Qualification[Study End Date]":""},{"Employee Qualification[Qualification Title]":"Medicine and Surgery","Employee Qualification[Educational Institute]":"United Arab Emirates University","Employee Qualification[GPA (Grade Point Average)]":"3.05","Employee Qualification[Study Start Date]":"","Employee Qualification[Study End Date]":""}]</v>
       </c>
       <c r="AZ14" t="str">
-        <v>[{"'CV Employee Education'[CV Institution Name]":"The Royal College of Surgeons in Ireland (RCSI)","'CV Employee Education'[CV Degree Name]":"Master's degree: Healthcare management","'CV Employee Education'[CV Start Date]":"","'CV Employee Education'[CV End Date]":"2020-11-30"},{"'CV Employee Education'[CV Institution Name]":"United Arab Emirates University","'CV Employee Education'[CV Degree Name]":"Bachelor of Medicine, Bachelor of Surgery","'CV Employee Education'[CV Start Date]":"","'CV Employee Education'[CV End Date]":"2015-06-30"},{"'CV Employee Education'[CV Institution Name]":"The Arab Board of Health Specializations","'CV Employee Education'[CV Degree Name]":"Family medicine Board","'CV Employee Education'[CV Start Date]":"","'CV Employee Education'[CV End Date]":"2021-04-30"}]</v>
+        <v>[{"CV Employee Education[CV Institution Name]":"The Royal College of Surgeons in Ireland (RCSI)","CV Employee Education[CV Degree Name]":"Master's degree: Healthcare management","CV Employee Education[CV Start Date]":"","CV Employee Education[CV End Date]":"2020-11-30"},{"CV Employee Education[CV Institution Name]":"United Arab Emirates University","CV Employee Education[CV Degree Name]":"Bachelor of Medicine, Bachelor of Surgery","CV Employee Education[CV Start Date]":"","CV Employee Education[CV End Date]":"2015-06-30"},{"CV Employee Education[CV Institution Name]":"The Arab Board of Health Specializations","CV Employee Education[CV Degree Name]":"Family medicine Board","CV Employee Education[CV Start Date]":"","CV Employee Education[CV End Date]":"2021-04-30"}]</v>
       </c>
       <c r="BA14" t="str">
-        <v>[{"'Employee Assignment History'[Assignment Name]":"Assistant Advisor","'Employee Assignment History'[Position Title]":"Assistant Advisor, Health","'Employee Assignment History'[Employee Grade]":"2C","'Employee Assignment History'[Assignment Start Date]":"2025-01-07","'Employee Assignment History'[Assignment End Date]":"2025-07-31","'Employee Assignment History'[Assignment Experience (Years &amp; Months)]":"0 Years, 6 Months"},{"'Employee Assignment History'[Assignment Name]":"Assistant Advisor, Health","'Employee Assignment History'[Position Title]":"Assistant Advisor, Health","'Employee Assignment History'[Employee Grade]":"2C","'Employee Assignment History'[Assignment Start Date]":"2025-08-01","'Employee Assignment History'[Assignment End Date]":"","'Employee Assignment History'[Assignment Experience (Years &amp; Months)]":""}]</v>
+        <v>[{"Employee Assignment History[Assignment Name]":"Assistant Advisor","Employee Assignment History[Position Title]":"Assistant Advisor, Health","Employee Assignment History[Employee Grade]":"2C","Employee Assignment History[Assignment Start Date]":"2025-01-07","Employee Assignment History[Assignment End Date]":"2025-07-31","Employee Assignment History[Assignment Experience (Years &amp; Months)]":"0 Years, 6 Months"},{"Employee Assignment History[Assignment Name]":"Assistant Advisor, Health","Employee Assignment History[Position Title]":"Assistant Advisor, Health","Employee Assignment History[Employee Grade]":"2C","Employee Assignment History[Assignment Start Date]":"2025-08-01","Employee Assignment History[Assignment End Date]":"","Employee Assignment History[Assignment Experience (Years &amp; Months)]":""}]</v>
       </c>
       <c r="BB14" t="str">
-        <v>[{"'Employee Previous Employer'[Previous Employer Name]":"Abu Dhabi Health Services Co.","'Employee Previous Employer'[Previous Job Title]":"Medical Practitioner","'Employee Previous Employer'[Start Date]":"2016-10-19","'Employee Previous Employer'[End Date]":"2023-02-02"},{"'Employee Previous Employer'[Previous Employer Name]":"Department of health - Abu Dhabi","'Employee Previous Employer'[Previous Job Title]":"Genetic Personal protection Specialist","'Employee Previous Employer'[Start Date]":"2023-02-09","'Employee Previous Employer'[End Date]":"2024-01-06"}]</v>
+        <v>[{"Employee Previous Employer[Previous Employer Name]":"Abu Dhabi Health Services Co.","Employee Previous Employer[Previous Job Title]":"Medical Practitioner","Employee Previous Employer[Start Date]":"2016-10-19","Employee Previous Employer[End Date]":"2023-02-02"},{"Employee Previous Employer[Previous Employer Name]":"Department of health - Abu Dhabi","Employee Previous Employer[Previous Job Title]":"Genetic Personal protection Specialist","Employee Previous Employer[Start Date]":"2023-02-09","Employee Previous Employer[End Date]":"2024-01-06"}]</v>
       </c>
       <c r="BC14" t="str">
-        <v>[{"'CV Employee Work Experience'[CV Company Name]":"SEHA - Tawam Hospital","'CV Employee Work Experience'[CV Job Title]":"Medical Intern","'CV Employee Work Experience'[CV Responsibilities Summary]":"","'CV Employee Work Experience'[CV Start Date]":"2015-09-01","'CV Employee Work Experience'[CV End Date]":"2016-08-01"},{"'CV Employee Work Experience'[CV Company Name]":"SEHA - AHS","'CV Employee Work Experience'[CV Job Title]":"Medical Resident - GP","'CV Employee Work Experience'[CV Responsibilities Summary]":"","'CV Employee Work Experience'[CV Start Date]":"2016-09-01","'CV Employee Work Experience'[CV End Date]":"2021-08-01"},{"'CV Employee Work Experience'[CV Company Name]":"SEHA - AHS","'CV Employee Work Experience'[CV Job Title]":"Family medicine specialist","'CV Employee Work Experience'[CV Responsibilities Summary]":"","'CV Employee Work Experience'[CV Start Date]":"2021-08-01","'CV Employee Work Experience'[CV End Date]":"2023-02-01"},{"'CV Employee Work Experience'[CV Company Name]":"AHS- Zayed higher organization center for PODs","'CV Employee Work Experience'[CV Job Title]":"Family medicine specialist","'CV Employee Work Experience'[CV Responsibilities Summary]":"","'CV Employee Work Experience'[CV Start Date]":"2022-06-01","'CV Employee Work Experience'[CV End Date]":"2023-02-01"},{"'CV Employee Work Experience'[CV Company Name]":"Abu Dhabi public health center","'CV Employee Work Experience'[CV Job Title]":"Personal genetic protection Specialist","'CV Employee Work Experience'[CV Responsibilities Summary]":"","'CV Employee Work Experience'[CV Start Date]":"2023-02-01","'CV Employee Work Experience'[CV End Date]":""},{"'CV Employee Work Experience'[CV Company Name]":"Abu Dhabi public health center","'CV Employee Work Experience'[CV Job Title]":"Acting Section head, Screening section","'CV Employee Work Experience'[CV Responsibilities Summary]":"","'CV Employee Work Experience'[CV Start Date]":"2023-07-01","'CV Employee Work Experience'[CV End Date]":""}]</v>
+        <v>[{"CV Employee Work Experience[CV Company Name]":"SEHA - Tawam Hospital","CV Employee Work Experience[CV Job Title]":"Medical Intern","CV Employee Work Experience[CV Responsibilities Summary]":"","CV Employee Work Experience[CV Start Date]":"2015-09-01","CV Employee Work Experience[CV End Date]":"2016-08-01"},{"CV Employee Work Experience[CV Company Name]":"SEHA - AHS","CV Employee Work Experience[CV Job Title]":"Medical Resident - GP","CV Employee Work Experience[CV Responsibilities Summary]":"","CV Employee Work Experience[CV Start Date]":"2016-09-01","CV Employee Work Experience[CV End Date]":"2021-08-01"},{"CV Employee Work Experience[CV Company Name]":"SEHA - AHS","CV Employee Work Experience[CV Job Title]":"Family medicine specialist","CV Employee Work Experience[CV Responsibilities Summary]":"","CV Employee Work Experience[CV Start Date]":"2021-08-01","CV Employee Work Experience[CV End Date]":"2023-02-01"},{"CV Employee Work Experience[CV Company Name]":"AHS- Zayed higher organization center for PODs","CV Employee Work Experience[CV Job Title]":"Family medicine specialist","CV Employee Work Experience[CV Responsibilities Summary]":"","CV Employee Work Experience[CV Start Date]":"2022-06-01","CV Employee Work Experience[CV End Date]":"2023-02-01"},{"CV Employee Work Experience[CV Company Name]":"Abu Dhabi public health center","CV Employee Work Experience[CV Job Title]":"Personal genetic protection Specialist","CV Employee Work Experience[CV Responsibilities Summary]":"","CV Employee Work Experience[CV Start Date]":"2023-02-01","CV Employee Work Experience[CV End Date]":""},{"CV Employee Work Experience[CV Company Name]":"Abu Dhabi public health center","CV Employee Work Experience[CV Job Title]":"Acting Section head, Screening section","CV Employee Work Experience[CV Responsibilities Summary]":"","CV Employee Work Experience[CV Start Date]":"2023-07-01","CV Employee Work Experience[CV End Date]":""}]</v>
       </c>
       <c r="BD14" t="str">
         <v>Hamda Musabah Alremeithi is a seasoned healthcare professional with over a decade of experience in family medicine and public health leadership, including roles as Acting Section Head and Genetic Protection Specialist at Abu Dhabi Public Health Center. She holds a Master’s in Healthcare Management from RCSI and is board-certified in Family Medicine by the Arab Board of Health Specializations. Her expertise spans advanced performance monitoring, strategic planning, and budget/resource management, with a proven track record in clinical operations and project execution across SEHA and AHS facilities.</v>
@@ -2869,7 +2869,7 @@
         <v>0</v>
       </c>
       <c r="AN15" t="str">
-        <v>[{"'CV Employee Competencies'[Technical Competency Name]":"Market Research"},{"'CV Employee Competencies'[Technical Competency Name]":"Public relations"},{"'CV Employee Competencies'[Technical Competency Name]":"Teamwork"},{"'CV Employee Competencies'[Technical Competency Name]":"Time Management"},{"'CV Employee Competencies'[Technical Competency Name]":"Effective Communication"},{"'CV Employee Competencies'[Technical Competency Name]":"Critical thinking"},{"'CV Employee Competencies'[Technical Competency Name]":"Arabic"},{"'CV Employee Competencies'[Technical Competency Name]":"English"},{"'CV Employee Competencies'[Technical Competency Name]":"Petroleum Engineering"},{"'CV Employee Competencies'[Technical Competency Name]":"Business Administration"},{"'CV Employee Competencies'[Technical Competency Name]":"Strategic Insight Generation"},{"'CV Employee Competencies'[Technical Competency Name]":"Supplier Relationship Management"},{"'CV Employee Competencies'[Technical Competency Name]":"Project Management"},{"'CV Employee Competencies'[Technical Competency Name]":"Cost Reduction"},{"'CV Employee Competencies'[Technical Competency Name]":"Team Leadership"},{"'CV Employee Competencies'[Technical Competency Name]":"Process Improvement"},{"'CV Employee Competencies'[Technical Competency Name]":"Stakeholder Engagement"},{"'CV Employee Competencies'[Technical Competency Name]":"Safety Compliance"}]</v>
+        <v>[{"CV Employee Competencies[Technical Competency Name]":"Market Research"},{"CV Employee Competencies[Technical Competency Name]":"Public relations"},{"CV Employee Competencies[Technical Competency Name]":"Teamwork"},{"CV Employee Competencies[Technical Competency Name]":"Time Management"},{"CV Employee Competencies[Technical Competency Name]":"Effective Communication"},{"CV Employee Competencies[Technical Competency Name]":"Critical thinking"},{"CV Employee Competencies[Technical Competency Name]":"Arabic"},{"CV Employee Competencies[Technical Competency Name]":"English"},{"CV Employee Competencies[Technical Competency Name]":"Petroleum Engineering"},{"CV Employee Competencies[Technical Competency Name]":"Business Administration"},{"CV Employee Competencies[Technical Competency Name]":"Strategic Insight Generation"},{"CV Employee Competencies[Technical Competency Name]":"Supplier Relationship Management"},{"CV Employee Competencies[Technical Competency Name]":"Project Management"},{"CV Employee Competencies[Technical Competency Name]":"Cost Reduction"},{"CV Employee Competencies[Technical Competency Name]":"Team Leadership"},{"CV Employee Competencies[Technical Competency Name]":"Process Improvement"},{"CV Employee Competencies[Technical Competency Name]":"Stakeholder Engagement"},{"CV Employee Competencies[Technical Competency Name]":"Safety Compliance"}]</v>
       </c>
       <c r="AO15" t="str">
         <v>[]</v>
@@ -2878,7 +2878,7 @@
         <v>[]</v>
       </c>
       <c r="AQ15" t="str">
-        <v>[{"'CV Employee Achievements and Awards'[CV Title]":"Milestone: Drilling the World's Longest Well","'CV Employee Achievements and Awards'[CV Achievement Description]":"Extended 52,000 feet (15,545 meters) in the UZ oil field","'CV Employee Achievements and Awards'[CV Issue Date]":"2023-01-01"},{"'CV Employee Achievements and Awards'[CV Title]":"Dean's List","'CV Employee Achievements and Awards'[CV Achievement Description]":"Spring 2016, Fall 2016 and Fall 2019","'CV Employee Achievements and Awards'[CV Issue Date]":"2016-05-01"},{"'CV Employee Achievements and Awards'[CV Title]":"Student of The Year","'CV Employee Achievements and Awards'[CV Achievement Description]":"","'CV Employee Achievements and Awards'[CV Issue Date]":"2015-05-01"}]</v>
+        <v>[{"CV Employee Achievements and Awards[CV Title]":"Milestone: Drilling the World's Longest Well","CV Employee Achievements and Awards[CV Achievement Description]":"Extended 52,000 feet (15,545 meters) in the UZ oil field","CV Employee Achievements and Awards[CV Issue Date]":"2023-01-01"},{"CV Employee Achievements and Awards[CV Title]":"Dean's List","CV Employee Achievements and Awards[CV Achievement Description]":"Spring 2016, Fall 2016 and Fall 2019","CV Employee Achievements and Awards[CV Issue Date]":"2016-05-01"},{"CV Employee Achievements and Awards[CV Title]":"Student of The Year","CV Employee Achievements and Awards[CV Achievement Description]":"","CV Employee Achievements and Awards[CV Issue Date]":"2015-05-01"}]</v>
       </c>
       <c r="AR15" t="str">
         <v>[]</v>
@@ -2896,19 +2896,19 @@
         <v/>
       </c>
       <c r="AY15" t="str">
-        <v>[{"'Employee Qualification'[Qualification Title]":"PETROLEUM ENGINEERING","'Employee Qualification'[Educational Institute]":"UNIVERSITY OF KANSAS LAWRENCE, KS","'Employee Qualification'[GPA (Grade Point Average)]":"3.24","'Employee Qualification'[Study Start Date]":"","'Employee Qualification'[Study End Date]":"2021-08-19"}]</v>
+        <v>[{"Employee Qualification[Qualification Title]":"PETROLEUM ENGINEERING","Employee Qualification[Educational Institute]":"UNIVERSITY OF KANSAS LAWRENCE, KS","Employee Qualification[GPA (Grade Point Average)]":"3.24","Employee Qualification[Study Start Date]":"","Employee Qualification[Study End Date]":"2021-08-19"}]</v>
       </c>
       <c r="AZ15" t="str">
-        <v>[{"'CV Employee Education'[CV Institution Name]":"Dubai Modern Education School","'CV Employee Education'[CV Degree Name]":"High School Diploma","'CV Employee Education'[CV Start Date]":"2015-01-01","'CV Employee Education'[CV End Date]":"2015-05-31"},{"'CV Employee Education'[CV Institution Name]":"University of Kansas","'CV Employee Education'[CV Degree Name]":"Bachelor of Science (B.S.)","'CV Employee Education'[CV Start Date]":"2016-01-01","'CV Employee Education'[CV End Date]":"2021-12-31"}]</v>
+        <v>[{"CV Employee Education[CV Institution Name]":"Dubai Modern Education School","CV Employee Education[CV Degree Name]":"High School Diploma","CV Employee Education[CV Start Date]":"2015-01-01","CV Employee Education[CV End Date]":"2015-05-31"},{"CV Employee Education[CV Institution Name]":"University of Kansas","CV Employee Education[CV Degree Name]":"Bachelor of Science (B.S.)","CV Employee Education[CV Start Date]":"2016-01-01","CV Employee Education[CV End Date]":"2021-12-31"}]</v>
       </c>
       <c r="BA15" t="str">
-        <v>[{"'Employee Assignment History'[Assignment Name]":"Specialist, Community Affairs","'Employee Assignment History'[Position Title]":"Specialist, Community Affairs","'Employee Assignment History'[Employee Grade]":"4B","'Employee Assignment History'[Assignment Start Date]":"2025-08-26","'Employee Assignment History'[Assignment End Date]":"","'Employee Assignment History'[Assignment Experience (Years &amp; Months)]":""}]</v>
+        <v>[{"Employee Assignment History[Assignment Name]":"Specialist, Community Affairs","Employee Assignment History[Position Title]":"Specialist, Community Affairs","Employee Assignment History[Employee Grade]":"4B","Employee Assignment History[Assignment Start Date]":"2025-08-26","Employee Assignment History[Assignment End Date]":"","Employee Assignment History[Assignment Experience (Years &amp; Months)]":""}]</v>
       </c>
       <c r="BB15" t="str">
-        <v>[{"'Employee Previous Employer'[Previous Employer Name]":"ADNOC Offshore","'Employee Previous Employer'[Previous Job Title]":"Drilling Site Leader","'Employee Previous Employer'[Start Date]":"2022-04-01","'Employee Previous Employer'[End Date]":"2024-08-01"},{"'Employee Previous Employer'[Previous Employer Name]":"Efficio MENA","'Employee Previous Employer'[Previous Job Title]":"Business Analyst","'Employee Previous Employer'[Start Date]":"2024-08-01","'Employee Previous Employer'[End Date]":"2025-01-30"}]</v>
+        <v>[{"Employee Previous Employer[Previous Employer Name]":"ADNOC Offshore","Employee Previous Employer[Previous Job Title]":"Drilling Site Leader","Employee Previous Employer[Start Date]":"2022-04-01","Employee Previous Employer[End Date]":"2024-08-01"},{"Employee Previous Employer[Previous Employer Name]":"Efficio MENA","Employee Previous Employer[Previous Job Title]":"Business Analyst","Employee Previous Employer[Start Date]":"2024-08-01","Employee Previous Employer[End Date]":"2025-01-30"}]</v>
       </c>
       <c r="BC15" t="str">
-        <v>[{"'CV Employee Work Experience'[CV Company Name]":"ADNOC Offshore","'CV Employee Work Experience'[CV Job Title]":"Drilling Site Leader","'CV Employee Work Experience'[CV Responsibilities Summary]":"Played an active role in managing cross-discipline teams to achieve the milestone of drilling the world's longest well (52,000 feet / 15,545 meters) in the UZ oil field. Identified cost reduction opportunities by analyzing practices and contractual agreements, leading to 17% reduction in drilling OPPEX KPI. Experienced in sourcing and contract management in the O&amp;M space. Managed operations in the offshore pipeline and drilling sector in the GCC. Ensured compliance with safety regulations and industry standards during drilling activities. Assigned tasks based on job requirements and addressed complications through troubleshooting to maintain operational efficiency.","'CV Employee Work Experience'[CV Start Date]":"2022-04-01","'CV Employee Work Experience'[CV End Date]":"2024-08-01"},{"'CV Employee Work Experience'[CV Company Name]":"Efficio MENA","'CV Employee Work Experience'[CV Job Title]":"Business Analyst","'CV Employee Work Experience'[CV Responsibilities Summary]":"Sourced through industry and market research using primary and secondary methods to identify trends, stakeholder feedback, and business opportunities; analyzed data to provide strategic recommendations and forecast business impacts. Worked with cross-functional teams to identify inefficiencies in maintenance processes, facilitated workshops, and developed recommendations to streamline workflows and reduce downtime. Supported KPI development and communication for data-driven decision-making. Conducted market research and benchmarking for high-value sourcing, evaluated supplier capabilities, financial stability, and compliance, and created supplier scorecards. Led procurement transformation initiatives to streamline processes, reduce costs, and improve supplier performance; analyzed company maturity to recommend FTE sizing; implemented digital tools and best practices; enhanced supplier relationships through performance frameworks; managed change via training and stakeholder engagement.","'CV Employee Work Experience'[CV Start Date]":"2024-08-01","'CV Employee Work Experience'[CV End Date]":""}]</v>
+        <v>[{"CV Employee Work Experience[CV Company Name]":"ADNOC Offshore","CV Employee Work Experience[CV Job Title]":"Drilling Site Leader","CV Employee Work Experience[CV Responsibilities Summary]":"Played an active role in managing cross-discipline teams to achieve the milestone of drilling the world's longest well (52,000 feet / 15,545 meters) in the UZ oil field. Identified cost reduction opportunities by analyzing practices and contractual agreements, leading to 17% reduction in drilling OPPEX KPI. Experienced in sourcing and contract management in the O&amp;M space. Managed operations in the offshore pipeline and drilling sector in the GCC. Ensured compliance with safety regulations and industry standards during drilling activities. Assigned tasks based on job requirements and addressed complications through troubleshooting to maintain operational efficiency.","CV Employee Work Experience[CV Start Date]":"2022-04-01","CV Employee Work Experience[CV End Date]":"2024-08-01"},{"CV Employee Work Experience[CV Company Name]":"Efficio MENA","CV Employee Work Experience[CV Job Title]":"Business Analyst","CV Employee Work Experience[CV Responsibilities Summary]":"Sourced through industry and market research using primary and secondary methods to identify trends, stakeholder feedback, and business opportunities; analyzed data to provide strategic recommendations and forecast business impacts. Worked with cross-functional teams to identify inefficiencies in maintenance processes, facilitated workshops, and developed recommendations to streamline workflows and reduce downtime. Supported KPI development and communication for data-driven decision-making. Conducted market research and benchmarking for high-value sourcing, evaluated supplier capabilities, financial stability, and compliance, and created supplier scorecards. Led procurement transformation initiatives to streamline processes, reduce costs, and improve supplier performance; analyzed company maturity to recommend FTE sizing; implemented digital tools and best practices; enhanced supplier relationships through performance frameworks; managed change via training and stakeholder engagement.","CV Employee Work Experience[CV Start Date]":"2024-08-01","CV Employee Work Experience[CV End Date]":""}]</v>
       </c>
       <c r="BD15" t="str">
         <v>Rakan Almazrouei brings 3.8 years of diverse experience as a Business Analyst at Efficio MENA and Drilling Site Leader at ADNOC Offshore, combining technical expertise in petroleum engineering with strong business acumen. He has led high-impact projects focused on cost reduction, process improvement, and safety compliance, while successfully managing cross-functional teams and stakeholder engagements. Recognized for excellence academically with Dean’s List and Student of the Year honors, he played a pivotal role in the milestone achievement of drilling the world’s longest well. His background includes a B.S. in Petroleum Engineering with a minor in Business Administration from the University of Kansas.</v>
@@ -3140,7 +3140,7 @@
         <v>[]</v>
       </c>
       <c r="AR17" t="str">
-        <v>[{"'Employee Leave Details'[Leave Type]":"Remote Work","'Employee Leave Details'[Leave Duration (Days)]":"1","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2025-05-16","'Employee Leave Details'[Leave End Date]":"2025-05-16"},{"'Employee Leave Details'[Leave Type]":"Training Leave","'Employee Leave Details'[Leave Duration (Days)]":"5","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2025-05-05","'Employee Leave Details'[Leave End Date]":"2025-05-09"},{"'Employee Leave Details'[Leave Type]":"Wellbeing","'Employee Leave Details'[Leave Duration (Days)]":"5","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2025-04-28","'Employee Leave Details'[Leave End Date]":"2025-05-02"},{"'Employee Leave Details'[Leave Type]":"Non-Mandatory Leave","'Employee Leave Details'[Leave Duration (Days)]":"2","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2025-04-22","'Employee Leave Details'[Leave End Date]":"2025-04-23"},{"'Employee Leave Details'[Leave Type]":"Remote Work","'Employee Leave Details'[Leave Duration (Days)]":"4","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2025-03-17","'Employee Leave Details'[Leave End Date]":"2025-03-20"},{"'Employee Leave Details'[Leave Type]":"Remote Work","'Employee Leave Details'[Leave Duration (Days)]":"10","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2025-03-03","'Employee Leave Details'[Leave End Date]":"2025-03-14"},{"'Employee Leave Details'[Leave Type]":"Wellbeing","'Employee Leave Details'[Leave Duration (Days)]":"1","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2025-02-20","'Employee Leave Details'[Leave End Date]":"2025-02-20"},{"'Employee Leave Details'[Leave Type]":"Non-Mandatory Leave","'Employee Leave Details'[Leave Duration (Days)]":"3","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2025-02-17","'Employee Leave Details'[Leave End Date]":"2025-02-19"},{"'Employee Leave Details'[Leave Type]":"Non-Mandatory Leave","'Employee Leave Details'[Leave Duration (Days)]":"1","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2025-02-03","'Employee Leave Details'[Leave End Date]":"2025-02-03"},{"'Employee Leave Details'[Leave Type]":"Wellbeing","'Employee Leave Details'[Leave Duration (Days)]":"6","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2025-01-20","'Employee Leave Details'[Leave End Date]":"2025-01-27"},{"'Employee Leave Details'[Leave Type]":"Non-Mandatory Leave","'Employee Leave Details'[Leave Duration (Days)]":"5","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2025-01-13","'Employee Leave Details'[Leave End Date]":"2025-01-17"},{"'Employee Leave Details'[Leave Type]":"Wellbeing","'Employee Leave Details'[Leave Duration (Days)]":"7","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2025-01-02","'Employee Leave Details'[Leave End Date]":"2025-01-10"},{"'Employee Leave Details'[Leave Type]":"Wellbeing","'Employee Leave Details'[Leave Duration (Days)]":"2","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-12-30","'Employee Leave Details'[Leave End Date]":"2024-12-31"},{"'Employee Leave Details'[Leave Type]":"Wellbeing","'Employee Leave Details'[Leave Duration (Days)]":"2","'Employee Leave Details'[Approval Status]":"Denied","'Employee Leave Details'[Leave Start Date]":"2024-12-30","'Employee Leave Details'[Leave End Date]":"2024-12-31"},{"'Employee Leave Details'[Leave Type]":"Non-Mandatory Leave","'Employee Leave Details'[Leave Duration (Days)]":"2","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-12-12","'Employee Leave Details'[Leave End Date]":"2024-12-13"},{"'Employee Leave Details'[Leave Type]":"Non-Mandatory Leave","'Employee Leave Details'[Leave Duration (Days)]":"2","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-12-09","'Employee Leave Details'[Leave End Date]":"2024-12-10"},{"'Employee Leave Details'[Leave Type]":"Non-Mandatory Leave","'Employee Leave Details'[Leave Duration (Days)]":"1","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-11-14","'Employee Leave Details'[Leave End Date]":"2024-11-14"},{"'Employee Leave Details'[Leave Type]":"Non-Mandatory Leave","'Employee Leave Details'[Leave Duration (Days)]":"1","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-11-08","'Employee Leave Details'[Leave End Date]":"2024-11-08"},{"'Employee Leave Details'[Leave Type]":"Non-Mandatory Leave","'Employee Leave Details'[Leave Duration (Days)]":"1","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-10-29","'Employee Leave Details'[Leave End Date]":"2024-10-29"},{"'Employee Leave Details'[Leave Type]":"Remote Work","'Employee Leave Details'[Leave Duration (Days)]":"1","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-10-11","'Employee Leave Details'[Leave End Date]":"2024-10-11"},{"'Employee Leave Details'[Leave Type]":"Wellbeing","'Employee Leave Details'[Leave Duration (Days)]":"4","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-10-07","'Employee Leave Details'[Leave End Date]":"2024-10-10"},{"'Employee Leave Details'[Leave Type]":"Non-Mandatory Leave","'Employee Leave Details'[Leave Duration (Days)]":"4","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-10-01","'Employee Leave Details'[Leave End Date]":"2024-10-04"},{"'Employee Leave Details'[Leave Type]":"Remote Work","'Employee Leave Details'[Leave Duration (Days)]":"1","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-09-30","'Employee Leave Details'[Leave End Date]":"2024-09-30"},{"'Employee Leave Details'[Leave Type]":"Training Leave","'Employee Leave Details'[Leave Duration (Days)]":"5","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-09-23","'Employee Leave Details'[Leave End Date]":"2024-09-27"},{"'Employee Leave Details'[Leave Type]":"Remote Work","'Employee Leave Details'[Leave Duration (Days)]":"1","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-09-20","'Employee Leave Details'[Leave End Date]":"2024-09-20"},{"'Employee Leave Details'[Leave Type]":"Remote Work","'Employee Leave Details'[Leave Duration (Days)]":"1","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-09-06","'Employee Leave Details'[Leave End Date]":"2024-09-06"},{"'Employee Leave Details'[Leave Type]":"Non-Mandatory Leave","'Employee Leave Details'[Leave Duration (Days)]":"2","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-09-02","'Employee Leave Details'[Leave End Date]":"2024-09-03"},{"'Employee Leave Details'[Leave Type]":"Remote Work","'Employee Leave Details'[Leave Duration (Days)]":"1","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-08-30","'Employee Leave Details'[Leave End Date]":"2024-08-30"},{"'Employee Leave Details'[Leave Type]":"Wellbeing","'Employee Leave Details'[Leave Duration (Days)]":"4","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-08-26","'Employee Leave Details'[Leave End Date]":"2024-08-29"},{"'Employee Leave Details'[Leave Type]":"Remote Work","'Employee Leave Details'[Leave Duration (Days)]":"1","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-08-23","'Employee Leave Details'[Leave End Date]":"2024-08-23"},{"'Employee Leave Details'[Leave Type]":"Non-Mandatory Leave","'Employee Leave Details'[Leave Duration (Days)]":"2","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-08-21","'Employee Leave Details'[Leave End Date]":"2024-08-22"},{"'Employee Leave Details'[Leave Type]":"Non-Mandatory Leave","'Employee Leave Details'[Leave Duration (Days)]":"1","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-08-14","'Employee Leave Details'[Leave End Date]":"2024-08-14"},{"'Employee Leave Details'[Leave Type]":"Remote Work","'Employee Leave Details'[Leave Duration (Days)]":"1","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-08-09","'Employee Leave Details'[Leave End Date]":"2024-08-09"},{"'Employee Leave Details'[Leave Type]":"Non-Mandatory Leave","'Employee Leave Details'[Leave Duration (Days)]":"1","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-07-29","'Employee Leave Details'[Leave End Date]":"2024-07-29"},{"'Employee Leave Details'[Leave Type]":"Remote Work","'Employee Leave Details'[Leave Duration (Days)]":"1","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-07-26","'Employee Leave Details'[Leave End Date]":"2024-07-26"},{"'Employee Leave Details'[Leave Type]":"Remote Work","'Employee Leave Details'[Leave Duration (Days)]":"1","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-07-12","'Employee Leave Details'[Leave End Date]":"2024-07-12"},{"'Employee Leave Details'[Leave Type]":"Non-Mandatory Leave","'Employee Leave Details'[Leave Duration (Days)]":"1","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-07-11","'Employee Leave Details'[Leave End Date]":"2024-07-11"},{"'Employee Leave Details'[Leave Type]":"Remote Work","'Employee Leave Details'[Leave Duration (Days)]":"1","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-06-28","'Employee Leave Details'[Leave End Date]":"2024-06-28"},{"'Employee Leave Details'[Leave Type]":"Non-Mandatory Leave","'Employee Leave Details'[Leave Duration (Days)]":"1","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-06-27","'Employee Leave Details'[Leave End Date]":"2024-06-27"},{"'Employee Leave Details'[Leave Type]":"Non-Mandatory Leave","'Employee Leave Details'[Leave Duration (Days)]":"2","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-06-13","'Employee Leave Details'[Leave End Date]":"2024-06-14"},{"'Employee Leave Details'[Leave Type]":"Training Leave","'Employee Leave Details'[Leave Duration (Days)]":"5","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-05-27","'Employee Leave Details'[Leave End Date]":"2024-05-31"},{"'Employee Leave Details'[Leave Type]":"Non-Mandatory Leave","'Employee Leave Details'[Leave Duration (Days)]":"1","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-05-22","'Employee Leave Details'[Leave End Date]":"2024-05-22"},{"'Employee Leave Details'[Leave Type]":"Remote Work","'Employee Leave Details'[Leave Duration (Days)]":"1","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-05-21","'Employee Leave Details'[Leave End Date]":"2024-05-21"},{"'Employee Leave Details'[Leave Type]":"Wellbeing","'Employee Leave Details'[Leave Duration (Days)]":"5","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-05-13","'Employee Leave Details'[Leave End Date]":"2024-05-17"},{"'Employee Leave Details'[Leave Type]":"Non-Mandatory Leave","'Employee Leave Details'[Leave Duration (Days)]":"1","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-05-09","'Employee Leave Details'[Leave End Date]":"2024-05-09"},{"'Employee Leave Details'[Leave Type]":"Non-Mandatory Leave","'Employee Leave Details'[Leave Duration (Days)]":"1","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-05-07","'Employee Leave Details'[Leave End Date]":"2024-05-07"},{"'Employee Leave Details'[Leave Type]":"Remote Work","'Employee Leave Details'[Leave Duration (Days)]":"2","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-05-02","'Employee Leave Details'[Leave End Date]":"2024-05-03"},{"'Employee Leave Details'[Leave Type]":"Remote Work","'Employee Leave Details'[Leave Duration (Days)]":"4","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-04-16","'Employee Leave Details'[Leave End Date]":"2024-04-19"},{"'Employee Leave Details'[Leave Type]":"Remote Work","'Employee Leave Details'[Leave Duration (Days)]":"5","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-04-01","'Employee Leave Details'[Leave End Date]":"2024-04-05"},{"'Employee Leave Details'[Leave Type]":"Remote Work","'Employee Leave Details'[Leave Duration (Days)]":"5","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-03-25","'Employee Leave Details'[Leave End Date]":"2024-03-29"},{"'Employee Leave Details'[Leave Type]":"Remote Work","'Employee Leave Details'[Leave Duration (Days)]":"5","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-03-18","'Employee Leave Details'[Leave End Date]":"2024-03-22"},{"'Employee Leave Details'[Leave Type]":"Remote Work","'Employee Leave Details'[Leave Duration (Days)]":"1","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-03-08","'Employee Leave Details'[Leave End Date]":"2024-03-08"},{"'Employee Leave Details'[Leave Type]":"Wellbeing","'Employee Leave Details'[Leave Duration (Days)]":"4","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-03-04","'Employee Leave Details'[Leave End Date]":"2024-03-07"},{"'Employee Leave Details'[Leave Type]":"Wellbeing","'Employee Leave Details'[Leave Duration (Days)]":"1","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-03-01","'Employee Leave Details'[Leave End Date]":"2024-03-01"},{"'Employee Leave Details'[Leave Type]":"Wellbeing","'Employee Leave Details'[Leave Duration (Days)]":"4","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-02-26","'Employee Leave Details'[Leave End Date]":"2024-02-29"},{"'Employee Leave Details'[Leave Type]":"Remote Work","'Employee Leave Details'[Leave Duration (Days)]":"2","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-02-22","'Employee Leave Details'[Leave End Date]":"2024-02-23"},{"'Employee Leave Details'[Leave Type]":"Remote Work","'Employee Leave Details'[Leave Duration (Days)]":"1","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-02-12","'Employee Leave Details'[Leave End Date]":"2024-02-12"},{"'Employee Leave Details'[Leave Type]":"Remote Work","'Employee Leave Details'[Leave Duration (Days)]":"1","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-02-09","'Employee Leave Details'[Leave End Date]":"2024-02-09"},{"'Employee Leave Details'[Leave Type]":"Remote Work","'Employee Leave Details'[Leave Duration (Days)]":"1","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-02-08","'Employee Leave Details'[Leave End Date]":"2024-02-08"},{"'Employee Leave Details'[Leave Type]":"Remote Work","'Employee Leave Details'[Leave Duration (Days)]":"1","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-02-02","'Employee Leave Details'[Leave End Date]":"2024-02-02"},{"'Employee Leave Details'[Leave Type]":"Wellbeing","'Employee Leave Details'[Leave Duration (Days)]":"1","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-01-29","'Employee Leave Details'[Leave End Date]":"2024-01-29"},{"'Employee Leave Details'[Leave Type]":"Remote Work","'Employee Leave Details'[Leave Duration (Days)]":"1","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-01-26","'Employee Leave Details'[Leave End Date]":"2024-01-26"},{"'Employee Leave Details'[Leave Type]":"Non-Mandatory Leave","'Employee Leave Details'[Leave Duration (Days)]":"1","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-01-18","'Employee Leave Details'[Leave End Date]":"2024-01-18"},{"'Employee Leave Details'[Leave Type]":"Remote Work","'Employee Leave Details'[Leave Duration (Days)]":"1","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-01-12","'Employee Leave Details'[Leave End Date]":"2024-01-12"},{"'Employee Leave Details'[Leave Type]":"Remote Work","'Employee Leave Details'[Leave Duration (Days)]":"1","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-01-09","'Employee Leave Details'[Leave End Date]":"2024-01-09"},{"'Employee Leave Details'[Leave Type]":"Wellbeing","'Employee Leave Details'[Leave Duration (Days)]":"5","'Employee Leave Details'[Approval Status]":"Approved","'Employee Leave Details'[Leave Start Date]":"2024-01-02","'Employee Leave Details'[Leave End Date]":"2024-01-08"}]</v>
+        <v>[{"Employee Leave Details[Leave Type]":"Remote Work","Employee Leave Details[Leave Duration (Days)]":"1","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2025-05-16","Employee Leave Details[Leave End Date]":"2025-05-16"},{"Employee Leave Details[Leave Type]":"Training Leave","Employee Leave Details[Leave Duration (Days)]":"5","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2025-05-05","Employee Leave Details[Leave End Date]":"2025-05-09"},{"Employee Leave Details[Leave Type]":"Wellbeing","Employee Leave Details[Leave Duration (Days)]":"5","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2025-04-28","Employee Leave Details[Leave End Date]":"2025-05-02"},{"Employee Leave Details[Leave Type]":"Non-Mandatory Leave","Employee Leave Details[Leave Duration (Days)]":"2","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2025-04-22","Employee Leave Details[Leave End Date]":"2025-04-23"},{"Employee Leave Details[Leave Type]":"Remote Work","Employee Leave Details[Leave Duration (Days)]":"4","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2025-03-17","Employee Leave Details[Leave End Date]":"2025-03-20"},{"Employee Leave Details[Leave Type]":"Remote Work","Employee Leave Details[Leave Duration (Days)]":"10","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2025-03-03","Employee Leave Details[Leave End Date]":"2025-03-14"},{"Employee Leave Details[Leave Type]":"Wellbeing","Employee Leave Details[Leave Duration (Days)]":"1","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2025-02-20","Employee Leave Details[Leave End Date]":"2025-02-20"},{"Employee Leave Details[Leave Type]":"Non-Mandatory Leave","Employee Leave Details[Leave Duration (Days)]":"3","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2025-02-17","Employee Leave Details[Leave End Date]":"2025-02-19"},{"Employee Leave Details[Leave Type]":"Non-Mandatory Leave","Employee Leave Details[Leave Duration (Days)]":"1","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2025-02-03","Employee Leave Details[Leave End Date]":"2025-02-03"},{"Employee Leave Details[Leave Type]":"Wellbeing","Employee Leave Details[Leave Duration (Days)]":"6","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2025-01-20","Employee Leave Details[Leave End Date]":"2025-01-27"},{"Employee Leave Details[Leave Type]":"Non-Mandatory Leave","Employee Leave Details[Leave Duration (Days)]":"5","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2025-01-13","Employee Leave Details[Leave End Date]":"2025-01-17"},{"Employee Leave Details[Leave Type]":"Wellbeing","Employee Leave Details[Leave Duration (Days)]":"7","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2025-01-02","Employee Leave Details[Leave End Date]":"2025-01-10"},{"Employee Leave Details[Leave Type]":"Wellbeing","Employee Leave Details[Leave Duration (Days)]":"2","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-12-30","Employee Leave Details[Leave End Date]":"2024-12-31"},{"Employee Leave Details[Leave Type]":"Wellbeing","Employee Leave Details[Leave Duration (Days)]":"2","Employee Leave Details[Approval Status]":"Denied","Employee Leave Details[Leave Start Date]":"2024-12-30","Employee Leave Details[Leave End Date]":"2024-12-31"},{"Employee Leave Details[Leave Type]":"Non-Mandatory Leave","Employee Leave Details[Leave Duration (Days)]":"2","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-12-12","Employee Leave Details[Leave End Date]":"2024-12-13"},{"Employee Leave Details[Leave Type]":"Non-Mandatory Leave","Employee Leave Details[Leave Duration (Days)]":"2","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-12-09","Employee Leave Details[Leave End Date]":"2024-12-10"},{"Employee Leave Details[Leave Type]":"Non-Mandatory Leave","Employee Leave Details[Leave Duration (Days)]":"1","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-11-14","Employee Leave Details[Leave End Date]":"2024-11-14"},{"Employee Leave Details[Leave Type]":"Non-Mandatory Leave","Employee Leave Details[Leave Duration (Days)]":"1","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-11-08","Employee Leave Details[Leave End Date]":"2024-11-08"},{"Employee Leave Details[Leave Type]":"Non-Mandatory Leave","Employee Leave Details[Leave Duration (Days)]":"1","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-10-29","Employee Leave Details[Leave End Date]":"2024-10-29"},{"Employee Leave Details[Leave Type]":"Remote Work","Employee Leave Details[Leave Duration (Days)]":"1","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-10-11","Employee Leave Details[Leave End Date]":"2024-10-11"},{"Employee Leave Details[Leave Type]":"Wellbeing","Employee Leave Details[Leave Duration (Days)]":"4","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-10-07","Employee Leave Details[Leave End Date]":"2024-10-10"},{"Employee Leave Details[Leave Type]":"Non-Mandatory Leave","Employee Leave Details[Leave Duration (Days)]":"4","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-10-01","Employee Leave Details[Leave End Date]":"2024-10-04"},{"Employee Leave Details[Leave Type]":"Remote Work","Employee Leave Details[Leave Duration (Days)]":"1","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-09-30","Employee Leave Details[Leave End Date]":"2024-09-30"},{"Employee Leave Details[Leave Type]":"Training Leave","Employee Leave Details[Leave Duration (Days)]":"5","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-09-23","Employee Leave Details[Leave End Date]":"2024-09-27"},{"Employee Leave Details[Leave Type]":"Remote Work","Employee Leave Details[Leave Duration (Days)]":"1","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-09-20","Employee Leave Details[Leave End Date]":"2024-09-20"},{"Employee Leave Details[Leave Type]":"Remote Work","Employee Leave Details[Leave Duration (Days)]":"1","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-09-06","Employee Leave Details[Leave End Date]":"2024-09-06"},{"Employee Leave Details[Leave Type]":"Non-Mandatory Leave","Employee Leave Details[Leave Duration (Days)]":"2","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-09-02","Employee Leave Details[Leave End Date]":"2024-09-03"},{"Employee Leave Details[Leave Type]":"Remote Work","Employee Leave Details[Leave Duration (Days)]":"1","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-08-30","Employee Leave Details[Leave End Date]":"2024-08-30"},{"Employee Leave Details[Leave Type]":"Wellbeing","Employee Leave Details[Leave Duration (Days)]":"4","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-08-26","Employee Leave Details[Leave End Date]":"2024-08-29"},{"Employee Leave Details[Leave Type]":"Remote Work","Employee Leave Details[Leave Duration (Days)]":"1","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-08-23","Employee Leave Details[Leave End Date]":"2024-08-23"},{"Employee Leave Details[Leave Type]":"Non-Mandatory Leave","Employee Leave Details[Leave Duration (Days)]":"2","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-08-21","Employee Leave Details[Leave End Date]":"2024-08-22"},{"Employee Leave Details[Leave Type]":"Non-Mandatory Leave","Employee Leave Details[Leave Duration (Days)]":"1","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-08-14","Employee Leave Details[Leave End Date]":"2024-08-14"},{"Employee Leave Details[Leave Type]":"Remote Work","Employee Leave Details[Leave Duration (Days)]":"1","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-08-09","Employee Leave Details[Leave End Date]":"2024-08-09"},{"Employee Leave Details[Leave Type]":"Non-Mandatory Leave","Employee Leave Details[Leave Duration (Days)]":"1","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-07-29","Employee Leave Details[Leave End Date]":"2024-07-29"},{"Employee Leave Details[Leave Type]":"Remote Work","Employee Leave Details[Leave Duration (Days)]":"1","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-07-26","Employee Leave Details[Leave End Date]":"2024-07-26"},{"Employee Leave Details[Leave Type]":"Remote Work","Employee Leave Details[Leave Duration (Days)]":"1","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-07-12","Employee Leave Details[Leave End Date]":"2024-07-12"},{"Employee Leave Details[Leave Type]":"Non-Mandatory Leave","Employee Leave Details[Leave Duration (Days)]":"1","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-07-11","Employee Leave Details[Leave End Date]":"2024-07-11"},{"Employee Leave Details[Leave Type]":"Remote Work","Employee Leave Details[Leave Duration (Days)]":"1","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-06-28","Employee Leave Details[Leave End Date]":"2024-06-28"},{"Employee Leave Details[Leave Type]":"Non-Mandatory Leave","Employee Leave Details[Leave Duration (Days)]":"1","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-06-27","Employee Leave Details[Leave End Date]":"2024-06-27"},{"Employee Leave Details[Leave Type]":"Non-Mandatory Leave","Employee Leave Details[Leave Duration (Days)]":"2","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-06-13","Employee Leave Details[Leave End Date]":"2024-06-14"},{"Employee Leave Details[Leave Type]":"Training Leave","Employee Leave Details[Leave Duration (Days)]":"5","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-05-27","Employee Leave Details[Leave End Date]":"2024-05-31"},{"Employee Leave Details[Leave Type]":"Non-Mandatory Leave","Employee Leave Details[Leave Duration (Days)]":"1","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-05-22","Employee Leave Details[Leave End Date]":"2024-05-22"},{"Employee Leave Details[Leave Type]":"Remote Work","Employee Leave Details[Leave Duration (Days)]":"1","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-05-21","Employee Leave Details[Leave End Date]":"2024-05-21"},{"Employee Leave Details[Leave Type]":"Wellbeing","Employee Leave Details[Leave Duration (Days)]":"5","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-05-13","Employee Leave Details[Leave End Date]":"2024-05-17"},{"Employee Leave Details[Leave Type]":"Non-Mandatory Leave","Employee Leave Details[Leave Duration (Days)]":"1","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-05-09","Employee Leave Details[Leave End Date]":"2024-05-09"},{"Employee Leave Details[Leave Type]":"Non-Mandatory Leave","Employee Leave Details[Leave Duration (Days)]":"1","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-05-07","Employee Leave Details[Leave End Date]":"2024-05-07"},{"Employee Leave Details[Leave Type]":"Remote Work","Employee Leave Details[Leave Duration (Days)]":"2","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-05-02","Employee Leave Details[Leave End Date]":"2024-05-03"},{"Employee Leave Details[Leave Type]":"Remote Work","Employee Leave Details[Leave Duration (Days)]":"4","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-04-16","Employee Leave Details[Leave End Date]":"2024-04-19"},{"Employee Leave Details[Leave Type]":"Remote Work","Employee Leave Details[Leave Duration (Days)]":"5","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-04-01","Employee Leave Details[Leave End Date]":"2024-04-05"},{"Employee Leave Details[Leave Type]":"Remote Work","Employee Leave Details[Leave Duration (Days)]":"5","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-03-25","Employee Leave Details[Leave End Date]":"2024-03-29"},{"Employee Leave Details[Leave Type]":"Remote Work","Employee Leave Details[Leave Duration (Days)]":"5","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-03-18","Employee Leave Details[Leave End Date]":"2024-03-22"},{"Employee Leave Details[Leave Type]":"Remote Work","Employee Leave Details[Leave Duration (Days)]":"1","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-03-08","Employee Leave Details[Leave End Date]":"2024-03-08"},{"Employee Leave Details[Leave Type]":"Wellbeing","Employee Leave Details[Leave Duration (Days)]":"4","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-03-04","Employee Leave Details[Leave End Date]":"2024-03-07"},{"Employee Leave Details[Leave Type]":"Wellbeing","Employee Leave Details[Leave Duration (Days)]":"1","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-03-01","Employee Leave Details[Leave End Date]":"2024-03-01"},{"Employee Leave Details[Leave Type]":"Wellbeing","Employee Leave Details[Leave Duration (Days)]":"4","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-02-26","Employee Leave Details[Leave End Date]":"2024-02-29"},{"Employee Leave Details[Leave Type]":"Remote Work","Employee Leave Details[Leave Duration (Days)]":"2","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-02-22","Employee Leave Details[Leave End Date]":"2024-02-23"},{"Employee Leave Details[Leave Type]":"Remote Work","Employee Leave Details[Leave Duration (Days)]":"1","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-02-12","Employee Leave Details[Leave End Date]":"2024-02-12"},{"Employee Leave Details[Leave Type]":"Remote Work","Employee Leave Details[Leave Duration (Days)]":"1","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-02-09","Employee Leave Details[Leave End Date]":"2024-02-09"},{"Employee Leave Details[Leave Type]":"Remote Work","Employee Leave Details[Leave Duration (Days)]":"1","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-02-08","Employee Leave Details[Leave End Date]":"2024-02-08"},{"Employee Leave Details[Leave Type]":"Remote Work","Employee Leave Details[Leave Duration (Days)]":"1","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-02-02","Employee Leave Details[Leave End Date]":"2024-02-02"},{"Employee Leave Details[Leave Type]":"Wellbeing","Employee Leave Details[Leave Duration (Days)]":"1","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-01-29","Employee Leave Details[Leave End Date]":"2024-01-29"},{"Employee Leave Details[Leave Type]":"Remote Work","Employee Leave Details[Leave Duration (Days)]":"1","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-01-26","Employee Leave Details[Leave End Date]":"2024-01-26"},{"Employee Leave Details[Leave Type]":"Non-Mandatory Leave","Employee Leave Details[Leave Duration (Days)]":"1","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-01-18","Employee Leave Details[Leave End Date]":"2024-01-18"},{"Employee Leave Details[Leave Type]":"Remote Work","Employee Leave Details[Leave Duration (Days)]":"1","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-01-12","Employee Leave Details[Leave End Date]":"2024-01-12"},{"Employee Leave Details[Leave Type]":"Remote Work","Employee Leave Details[Leave Duration (Days)]":"1","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-01-09","Employee Leave Details[Leave End Date]":"2024-01-09"},{"Employee Leave Details[Leave Type]":"Wellbeing","Employee Leave Details[Leave Duration (Days)]":"5","Employee Leave Details[Approval Status]":"Approved","Employee Leave Details[Leave Start Date]":"2024-01-02","Employee Leave Details[Leave End Date]":"2024-01-08"}]</v>
       </c>
       <c r="AS17" t="str">
         <v>[]</v>
@@ -3149,7 +3149,7 @@
         <v>[]</v>
       </c>
       <c r="AU17" t="str">
-        <v>[{"'Employee Objectives'[Objective Name]":"Ensure continuous updates in government and federal officials database by Q4 2023","'Employee Objectives'[Goal Plan Name]":"2023 Performance Objectives","'Employee Objectives'[Objective Description]":"The Wellbeing Risk score aims to measure the level of mental or physical risk experienced by the employee","'Employee Objectives'[Goal Weighting]":"15","'Employee Objectives'[Goal Status]":"Approved","'Employee Objectives'[Objective Status]":"APPROVED","'Employee Objectives'[Workflow State]":"COMPLETE"},{"'Employee Objectives'[Objective Name]":"Provide support in Data Management automation process up to Q4 2023","'Employee Objectives'[Goal Plan Name]":"2023 Performance Objectives","'Employee Objectives'[Objective Description]":"The Wellbeing Risk score aims to measure the level of mental or physical risk experienced by the employee","'Employee Objectives'[Goal Weighting]":"45","'Employee Objectives'[Goal Status]":"Approved","'Employee Objectives'[Objective Status]":"APPROVED","'Employee Objectives'[Workflow State]":"COMPLETE"},{"'Employee Objectives'[Objective Name]":"Ensure smooth handling of all Data Management Inquiries throughout the year","'Employee Objectives'[Goal Plan Name]":"2023 Performance Objectives","'Employee Objectives'[Objective Description]":"The Wellbeing Risk score aims to measure the level of mental or physical risk experienced by the employee","'Employee Objectives'[Goal Weighting]":"20","'Employee Objectives'[Goal Status]":"Approved","'Employee Objectives'[Objective Status]":"APPROVED","'Employee Objectives'[Workflow State]":"COMPLETE"},{"'Employee Objectives'[Objective Name]":"Processing all ADEO Correspondence throughout the year","'Employee Objectives'[Goal Plan Name]":"2023 Performance Objectives","'Employee Objectives'[Objective Description]":"The Wellbeing Risk score aims to measure the level of mental or physical risk experienced by the employee","'Employee Objectives'[Goal Weighting]":"20","'Employee Objectives'[Goal Status]":"Approved","'Employee Objectives'[Objective Status]":"APPROVED","'Employee Objectives'[Workflow State]":"COMPLETE"}]</v>
+        <v>[{"Employee Objectives[Objective Name]":"Ensure continuous updates in government and federal officials database by Q4 2023","Employee Objectives[Goal Plan Name]":"2023 Performance Objectives","Employee Objectives[Objective Description]":"The Wellbeing Risk score aims to measure the level of mental or physical risk experienced by the employee","Employee Objectives[Goal Weighting]":"15","Employee Objectives[Goal Status]":"Approved","Employee Objectives[Objective Status]":"APPROVED","Employee Objectives[Workflow State]":"COMPLETE"},{"Employee Objectives[Objective Name]":"Provide support in Data Management automation process up to Q4 2023","Employee Objectives[Goal Plan Name]":"2023 Performance Objectives","Employee Objectives[Objective Description]":"The Wellbeing Risk score aims to measure the level of mental or physical risk experienced by the employee","Employee Objectives[Goal Weighting]":"45","Employee Objectives[Goal Status]":"Approved","Employee Objectives[Objective Status]":"APPROVED","Employee Objectives[Workflow State]":"COMPLETE"},{"Employee Objectives[Objective Name]":"Ensure smooth handling of all Data Management Inquiries throughout the year","Employee Objectives[Goal Plan Name]":"2023 Performance Objectives","Employee Objectives[Objective Description]":"The Wellbeing Risk score aims to measure the level of mental or physical risk experienced by the employee","Employee Objectives[Goal Weighting]":"20","Employee Objectives[Goal Status]":"Approved","Employee Objectives[Objective Status]":"APPROVED","Employee Objectives[Workflow State]":"COMPLETE"},{"Employee Objectives[Objective Name]":"Processing all ADEO Correspondence throughout the year","Employee Objectives[Goal Plan Name]":"2023 Performance Objectives","Employee Objectives[Objective Description]":"The Wellbeing Risk score aims to measure the level of mental or physical risk experienced by the employee","Employee Objectives[Goal Weighting]":"20","Employee Objectives[Goal Status]":"Approved","Employee Objectives[Objective Status]":"APPROVED","Employee Objectives[Workflow State]":"COMPLETE"}]</v>
       </c>
       <c r="AY17" t="str">
         <v>[]</v>
